--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC32DB-598C-4425-B338-450BB3C69CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E92D3C2-683B-492F-906B-4784D9CB1643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,32 +614,26 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -647,13 +641,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -689,17 +677,29 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1011,7 +1011,8 @@
     <col min="67" max="69" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="71" max="77" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="16384" width="9.109375" style="1"/>
+    <col min="78" max="78" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:86" x14ac:dyDescent="0.3">
@@ -1023,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="33"/>
-      <c r="AQ2" s="33"/>
-      <c r="AR2" s="33"/>
-      <c r="AS2" s="33"/>
-      <c r="AT2" s="33"/>
-      <c r="AU2" s="33"/>
-      <c r="AV2" s="33"/>
-      <c r="AW2" s="33"/>
-      <c r="AX2" s="33"/>
-      <c r="AY2" s="33"/>
-      <c r="AZ2" s="33"/>
-      <c r="BA2" s="33"/>
-      <c r="BB2" s="33"/>
-      <c r="BC2" s="33"/>
-      <c r="BD2" s="33"/>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="33"/>
-      <c r="BG2" s="33"/>
-      <c r="BH2" s="33"/>
-      <c r="BI2" s="33"/>
-      <c r="BJ2" s="33"/>
-      <c r="BK2" s="33"/>
-      <c r="BL2" s="33"/>
-      <c r="BM2" s="33"/>
-      <c r="BN2" s="33"/>
-      <c r="BO2" s="33"/>
-      <c r="BP2" s="33"/>
-      <c r="BQ2" s="33"/>
-      <c r="BR2" s="33"/>
-      <c r="BS2" s="33"/>
-      <c r="BT2" s="33"/>
-      <c r="BU2" s="33"/>
-      <c r="BV2" s="33"/>
-      <c r="BW2" s="33"/>
-      <c r="BX2" s="33"/>
-      <c r="BY2" s="33"/>
-      <c r="BZ2" s="33"/>
-      <c r="CA2" s="33"/>
-      <c r="CB2" s="33"/>
-      <c r="CC2" s="33"/>
-      <c r="CD2" s="33"/>
-      <c r="CE2" s="33"/>
-      <c r="CF2" s="33"/>
-      <c r="CG2" s="33"/>
-      <c r="CH2" s="33"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="53"/>
+      <c r="BN2" s="53"/>
+      <c r="BO2" s="53"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="53"/>
+      <c r="CA2" s="53"/>
+      <c r="CB2" s="53"/>
+      <c r="CC2" s="53"/>
+      <c r="CD2" s="53"/>
+      <c r="CE2" s="53"/>
+      <c r="CF2" s="53"/>
+      <c r="CG2" s="53"/>
+      <c r="CH2" s="53"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="52">
+      <c r="B3" s="55"/>
+      <c r="C3" s="29">
         <v>2020</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29">
         <v>2021</v>
       </c>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="32">
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="30">
         <v>2022</v>
       </c>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32">
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30">
         <v>2023</v>
       </c>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32">
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
-      <c r="BD3" s="32"/>
-      <c r="BE3" s="32"/>
-      <c r="BF3" s="32"/>
-      <c r="BG3" s="32"/>
-      <c r="BH3" s="32"/>
-      <c r="BI3" s="32"/>
-      <c r="BJ3" s="32"/>
-      <c r="BK3" s="32">
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30">
         <v>2025</v>
       </c>
-      <c r="BL3" s="32"/>
-      <c r="BM3" s="32"/>
-      <c r="BN3" s="32"/>
-      <c r="BO3" s="32"/>
-      <c r="BP3" s="32"/>
-      <c r="BQ3" s="32"/>
-      <c r="BR3" s="32"/>
-      <c r="BS3" s="32"/>
-      <c r="BT3" s="32"/>
-      <c r="BU3" s="32"/>
-      <c r="BV3" s="32"/>
-      <c r="BW3" s="32">
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30">
         <v>2026</v>
       </c>
-      <c r="BX3" s="32"/>
-      <c r="BY3" s="32"/>
-      <c r="BZ3" s="32"/>
-      <c r="CA3" s="32"/>
-      <c r="CB3" s="32"/>
-      <c r="CC3" s="32"/>
-      <c r="CD3" s="32"/>
-      <c r="CE3" s="32"/>
-      <c r="CF3" s="32"/>
-      <c r="CG3" s="32"/>
-      <c r="CH3" s="32"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1478,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1710,7 +1711,7 @@
         <v>52551.71232876712</v>
       </c>
       <c r="BZ5" s="17">
-        <v>0</v>
+        <v>65558.047945205486</v>
       </c>
       <c r="CA5" s="17">
         <v>0</v>
@@ -1738,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="54"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2254,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="54"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>54942.808219178085</v>
       </c>
       <c r="BZ8" s="17">
-        <v>0</v>
+        <v>63541.438356164384</v>
       </c>
       <c r="CA8" s="17">
         <v>0</v>
@@ -2512,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>28520.376712328769</v>
       </c>
       <c r="BZ9" s="17">
-        <v>0</v>
+        <v>37692.636986301368</v>
       </c>
       <c r="CA9" s="17">
         <v>0</v>
@@ -2770,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>144750.17123287672</v>
       </c>
       <c r="BZ10" s="17">
-        <v>0</v>
+        <v>178085.10273972602</v>
       </c>
       <c r="CA10" s="17">
         <v>0</v>
@@ -3028,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3258,7 +3259,7 @@
         <v>65994.349315068495</v>
       </c>
       <c r="BZ11" s="17">
-        <v>0</v>
+        <v>68149.315068493146</v>
       </c>
       <c r="CA11" s="17">
         <v>0</v>
@@ -3286,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>24146.746575342466</v>
       </c>
       <c r="BZ12" s="17">
-        <v>0</v>
+        <v>45867.294520547948</v>
       </c>
       <c r="CA12" s="17">
         <v>0</v>
@@ -3544,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3774,7 +3775,7 @@
         <v>99722.089041095896</v>
       </c>
       <c r="BZ13" s="17">
-        <v>0</v>
+        <v>63906.849315068495</v>
       </c>
       <c r="CA13" s="17">
         <v>0</v>
@@ -3802,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v>19389.383561643837</v>
       </c>
       <c r="BZ14" s="17">
-        <v>0</v>
+        <v>28841.609589041094</v>
       </c>
       <c r="CA14" s="17">
         <v>0</v>
@@ -4060,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4290,7 +4291,7 @@
         <v>87435.101369863012</v>
       </c>
       <c r="BZ15" s="17">
-        <v>0</v>
+        <v>98770.888356164389</v>
       </c>
       <c r="CA15" s="17">
         <v>0</v>
@@ -4318,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4548,7 +4549,7 @@
         <v>90900.513698630137</v>
       </c>
       <c r="BZ16" s="17">
-        <v>0</v>
+        <v>102329.45205479451</v>
       </c>
       <c r="CA16" s="17">
         <v>0</v>
@@ -4576,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4806,7 +4807,7 @@
         <v>49405.605479452053</v>
       </c>
       <c r="BZ17" s="17">
-        <v>0</v>
+        <v>35377.706849315065</v>
       </c>
       <c r="CA17" s="17">
         <v>0</v>
@@ -4834,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>100294.6794520548</v>
       </c>
       <c r="BZ18" s="17">
-        <v>0</v>
+        <v>107348.01575342465</v>
       </c>
       <c r="CA18" s="17">
         <v>0</v>
@@ -5092,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>101758.39041095891</v>
       </c>
       <c r="BZ19" s="17">
-        <v>0</v>
+        <v>122184.24657534246</v>
       </c>
       <c r="CA19" s="17">
         <v>0</v>
@@ -5350,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5580,7 +5581,7 @@
         <v>309774.48630136985</v>
       </c>
       <c r="BZ20" s="17">
-        <v>0</v>
+        <v>414111.4726027397</v>
       </c>
       <c r="CA20" s="17">
         <v>0</v>
@@ -5608,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5838,7 +5839,7 @@
         <v>76115.92465753424</v>
       </c>
       <c r="BZ21" s="17">
-        <v>0</v>
+        <v>80014.725856164383</v>
       </c>
       <c r="CA21" s="17">
         <v>0</v>
@@ -5866,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6124,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="54"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6354,7 +6355,7 @@
         <v>55278.938356164384</v>
       </c>
       <c r="BZ23" s="17">
-        <v>0</v>
+        <v>55850.686986301371</v>
       </c>
       <c r="CA23" s="17">
         <v>0</v>
@@ -6382,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6612,7 +6613,7 @@
         <v>33567.636986301368</v>
       </c>
       <c r="BZ24" s="17">
-        <v>0</v>
+        <v>44819.006849315068</v>
       </c>
       <c r="CA24" s="17">
         <v>0</v>
@@ -6640,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6870,7 +6871,7 @@
         <v>28469.691780821919</v>
       </c>
       <c r="BZ25" s="17">
-        <v>0</v>
+        <v>30634.760273972603</v>
       </c>
       <c r="CA25" s="17">
         <v>0</v>
@@ -6898,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="54"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>37445.547945205479</v>
       </c>
       <c r="BZ26" s="17">
-        <v>0</v>
+        <v>43504.280821917811</v>
       </c>
       <c r="CA26" s="17">
         <v>0</v>
@@ -7156,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="54"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7386,7 +7387,7 @@
         <v>39991.917808219179</v>
       </c>
       <c r="BZ27" s="17">
-        <v>0</v>
+        <v>47391.952054794521</v>
       </c>
       <c r="CA27" s="17">
         <v>0</v>
@@ -7414,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="54"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7644,7 +7645,7 @@
         <v>15425.684931506848</v>
       </c>
       <c r="BZ28" s="17">
-        <v>0</v>
+        <v>39437.67123287671</v>
       </c>
       <c r="CA28" s="17">
         <v>0</v>
@@ -7672,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="54"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>47145.890410958906</v>
       </c>
       <c r="BZ29" s="17">
-        <v>0</v>
+        <v>63641.095890410958</v>
       </c>
       <c r="CA29" s="17">
         <v>0</v>
@@ -7930,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8160,7 +8161,7 @@
         <v>76803.767123287675</v>
       </c>
       <c r="BZ30" s="17">
-        <v>0</v>
+        <v>74142.294520547948</v>
       </c>
       <c r="CA30" s="17">
         <v>0</v>
@@ -8188,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8418,7 +8419,7 @@
         <v>49797.260273972606</v>
       </c>
       <c r="BZ31" s="17">
-        <v>0</v>
+        <v>56189.876712328769</v>
       </c>
       <c r="CA31" s="17">
         <v>0</v>
@@ -8446,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="54"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8704,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8962,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="54"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9192,7 +9193,7 @@
         <v>21207.429794520547</v>
       </c>
       <c r="BZ34" s="17">
-        <v>0</v>
+        <v>29834.066780821919</v>
       </c>
       <c r="CA34" s="17">
         <v>0</v>
@@ -9220,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="54"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9456,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="55"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9686,7 +9687,7 @@
         <v>13826.351027397261</v>
       </c>
       <c r="BZ36" s="17">
-        <v>0</v>
+        <v>15405.493150684932</v>
       </c>
       <c r="CA36" s="17">
         <v>0</v>
@@ -9714,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="48" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9946,7 +9947,7 @@
         <v>120299.72602739726</v>
       </c>
       <c r="BZ37" s="19">
-        <v>0</v>
+        <v>118433.1506849315</v>
       </c>
       <c r="CA37" s="19">
         <v>0</v>
@@ -9974,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10204,7 +10205,7 @@
         <v>83530.684931506854</v>
       </c>
       <c r="BZ38" s="19">
-        <v>0</v>
+        <v>88373.972602739726</v>
       </c>
       <c r="CA38" s="19">
         <v>0</v>
@@ -10232,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10490,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10748,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="28"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11006,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="28"/>
+      <c r="A42" s="49"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>37291.506849315068</v>
       </c>
       <c r="BZ42" s="19">
-        <v>0</v>
+        <v>36512.054794520547</v>
       </c>
       <c r="CA42" s="19">
         <v>0</v>
@@ -11752,7 +11753,7 @@
         <v>20262.739726027397</v>
       </c>
       <c r="BZ44" s="19">
-        <v>0</v>
+        <v>19426.849315068495</v>
       </c>
       <c r="CA44" s="19">
         <v>0</v>
@@ -12010,7 +12011,7 @@
         <v>31357.260273972603</v>
       </c>
       <c r="BZ45" s="19">
-        <v>0</v>
+        <v>37856.986301369863</v>
       </c>
       <c r="CA45" s="19">
         <v>0</v>
@@ -12038,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="50" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12298,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="30"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12456,7 +12457,7 @@
         <v>43035.41066666667</v>
       </c>
       <c r="BZ47" s="20">
-        <v>0</v>
+        <v>43386.701333333338</v>
       </c>
       <c r="CA47" s="20">
         <v>0</v>
@@ -12484,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="30"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12642,7 +12643,7 @@
         <v>7068.4319999999998</v>
       </c>
       <c r="BZ48" s="20">
-        <v>0</v>
+        <v>26340.965333333334</v>
       </c>
       <c r="CA48" s="20">
         <v>0</v>
@@ -12670,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="30"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12928,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="30"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13186,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="31"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13444,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13676,7 +13677,7 @@
         <v>39621.401349633459</v>
       </c>
       <c r="BZ52" s="21">
-        <v>0</v>
+        <v>47790.630160034823</v>
       </c>
       <c r="CA52" s="21">
         <v>0</v>
@@ -13704,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13962,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="44" t="s">
+      <c r="A54" s="40" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14194,7 +14195,7 @@
         <v>31203.386792452831</v>
       </c>
       <c r="BZ54" s="22">
-        <v>0</v>
+        <v>23863.437106918238</v>
       </c>
       <c r="CA54" s="22">
         <v>0</v>
@@ -14222,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="45"/>
+      <c r="A55" s="41"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14442,7 +14443,7 @@
         <v>23206.613207547169</v>
       </c>
       <c r="BZ55" s="22">
-        <v>0</v>
+        <v>15140.830188679243</v>
       </c>
       <c r="CA55" s="22">
         <v>0</v>
@@ -14470,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="45"/>
+      <c r="A56" s="41"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14700,7 +14701,7 @@
         <v>81961.515723270437</v>
       </c>
       <c r="BZ56" s="22">
-        <v>0</v>
+        <v>67140.729559748419</v>
       </c>
       <c r="CA56" s="22">
         <v>0</v>
@@ -14728,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45"/>
+      <c r="A57" s="41"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14986,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="45"/>
+      <c r="A58" s="41"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15244,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
+      <c r="A59" s="42"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15502,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="43" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15734,7 +15735,7 @@
         <v>11391.51</v>
       </c>
       <c r="BZ60" s="23">
-        <v>0</v>
+        <v>9481.39</v>
       </c>
       <c r="CA60" s="23">
         <v>0</v>
@@ -15762,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
+      <c r="A61" s="44"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16020,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="37" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16252,7 +16253,7 @@
         <v>74685.2</v>
       </c>
       <c r="BZ62" s="24">
-        <v>0</v>
+        <v>65494.761538461535</v>
       </c>
       <c r="CA62" s="24">
         <v>0</v>
@@ -16280,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="42"/>
+      <c r="A63" s="38"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16510,7 +16511,7 @@
         <v>77825.3</v>
       </c>
       <c r="BZ63" s="24">
-        <v>0</v>
+        <v>66703.946153846162</v>
       </c>
       <c r="CA63" s="24">
         <v>0</v>
@@ -16538,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="42"/>
+      <c r="A64" s="38"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16768,7 +16769,7 @@
         <v>54483.630769230767</v>
       </c>
       <c r="BZ64" s="24">
-        <v>0</v>
+        <v>84205.753846153835</v>
       </c>
       <c r="CA64" s="24">
         <v>0</v>
@@ -16796,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="43"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17026,7 +17027,7 @@
         <v>29489.253846153842</v>
       </c>
       <c r="BZ65" s="24">
-        <v>0</v>
+        <v>31257.13846153846</v>
       </c>
       <c r="CA65" s="24">
         <v>0</v>
@@ -17054,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="49" t="s">
+      <c r="A66" s="45" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17314,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="50"/>
+      <c r="A67" s="46"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17544,7 +17545,7 @@
         <v>73214.234332425069</v>
       </c>
       <c r="BZ67" s="25">
-        <v>0</v>
+        <v>48583.171662125336</v>
       </c>
       <c r="CA67" s="25">
         <v>0</v>
@@ -17572,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="51"/>
+      <c r="A68" s="47"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -17802,7 +17803,7 @@
         <v>73701.948228882844</v>
       </c>
       <c r="BZ68" s="25">
-        <v>0</v>
+        <v>78625.803814713901</v>
       </c>
       <c r="CA68" s="25">
         <v>0</v>
@@ -18322,7 +18323,7 @@
         <v>16987.172043010753</v>
       </c>
       <c r="BZ70" s="26">
-        <v>0</v>
+        <v>19540.892473118278</v>
       </c>
       <c r="CA70" s="26">
         <v>0</v>
@@ -18350,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="38" t="s">
+      <c r="A71" s="27" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18582,7 +18583,7 @@
         <v>56658.92</v>
       </c>
       <c r="BZ71" s="21">
-        <v>0</v>
+        <v>58890.09</v>
       </c>
       <c r="CA71" s="21">
         <v>0</v>
@@ -18610,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="39"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18868,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="39"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19098,7 +19099,7 @@
         <v>84048.37</v>
       </c>
       <c r="BZ73" s="21">
-        <v>0</v>
+        <v>72619.87</v>
       </c>
       <c r="CA73" s="21">
         <v>0</v>
@@ -19126,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="39"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19356,7 +19357,7 @@
         <v>0</v>
       </c>
       <c r="BZ74" s="21">
-        <v>0</v>
+        <v>40195.93</v>
       </c>
       <c r="CA74" s="21">
         <v>0</v>
@@ -19384,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="40"/>
+      <c r="A75" s="28"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19614,7 +19615,7 @@
         <v>33363.14</v>
       </c>
       <c r="BZ75" s="21">
-        <v>0</v>
+        <v>37595.480000000003</v>
       </c>
       <c r="CA75" s="21">
         <v>0</v>
@@ -19642,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="34" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19874,7 +19875,7 @@
         <v>48616.092913276305</v>
       </c>
       <c r="BZ76" s="26">
-        <v>0</v>
+        <v>54807.573544752762</v>
       </c>
       <c r="CA76" s="26">
         <v>0</v>
@@ -19902,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+      <c r="A77" s="35"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20132,7 +20133,7 @@
         <v>55825.460741358926</v>
       </c>
       <c r="BZ77" s="26">
-        <v>0</v>
+        <v>50643.445302176791</v>
       </c>
       <c r="CA77" s="26">
         <v>0</v>
@@ -20161,25 +20162,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
     <mergeCell ref="AA3:AL3"/>
     <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E92D3C2-683B-492F-906B-4784D9CB1643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B33CDC9-5D8D-4043-9152-21270848773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,26 +614,17 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -641,7 +632,13 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -677,6 +674,18 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -691,15 +700,6 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="53"/>
-      <c r="AS2" s="53"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="53"/>
-      <c r="BN2" s="53"/>
-      <c r="BO2" s="53"/>
-      <c r="BP2" s="53"/>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="53"/>
-      <c r="BS2" s="53"/>
-      <c r="BT2" s="53"/>
-      <c r="BU2" s="53"/>
-      <c r="BV2" s="53"/>
-      <c r="BW2" s="53"/>
-      <c r="BX2" s="53"/>
-      <c r="BY2" s="53"/>
-      <c r="BZ2" s="53"/>
-      <c r="CA2" s="53"/>
-      <c r="CB2" s="53"/>
-      <c r="CC2" s="53"/>
-      <c r="CD2" s="53"/>
-      <c r="CE2" s="53"/>
-      <c r="CF2" s="53"/>
-      <c r="CG2" s="53"/>
-      <c r="CH2" s="53"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="29">
+      <c r="B3" s="30"/>
+      <c r="C3" s="47">
         <v>2020</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29">
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47">
         <v>2021</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="30">
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="27">
         <v>2022</v>
       </c>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30">
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27">
         <v>2023</v>
       </c>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30">
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30">
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27">
         <v>2025</v>
       </c>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30">
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27">
         <v>2026</v>
       </c>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
+      <c r="BX3" s="27"/>
+      <c r="BY3" s="27"/>
+      <c r="BZ3" s="27"/>
+      <c r="CA3" s="27"/>
+      <c r="CB3" s="27"/>
+      <c r="CC3" s="27"/>
+      <c r="CD3" s="27"/>
+      <c r="CE3" s="27"/>
+      <c r="CF3" s="27"/>
+      <c r="CG3" s="27"/>
+      <c r="CH3" s="27"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="48" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
+      <c r="A28" s="49"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
+      <c r="A32" s="49"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
+      <c r="A34" s="49"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9221,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="51" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="49"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10233,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="49"/>
+      <c r="A39" s="52"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="49"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="49"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="49"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="53" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="51"/>
+      <c r="A47" s="54"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="51"/>
+      <c r="A48" s="54"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12671,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="51"/>
+      <c r="A49" s="54"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="51"/>
+      <c r="A50" s="54"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="52"/>
+      <c r="A51" s="55"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13705,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14223,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="41"/>
+      <c r="A55" s="40"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="41"/>
+      <c r="A56" s="40"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="41"/>
+      <c r="A57" s="40"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="41"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="42"/>
+      <c r="A59" s="41"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="43" t="s">
+      <c r="A60" s="42" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15763,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="44"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="36" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16281,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="38"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16539,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="38"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16797,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="39"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17055,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="45" t="s">
+      <c r="A66" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
+      <c r="A67" s="45"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="47"/>
+      <c r="A68" s="46"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18611,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>84048.37</v>
       </c>
       <c r="BZ73" s="21">
-        <v>72619.87</v>
+        <v>70560.289999999994</v>
       </c>
       <c r="CA73" s="21">
         <v>0</v>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19385,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="34" t="s">
+      <c r="A76" s="31" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19903,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="35"/>
+      <c r="A77" s="32"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20162,17 +20162,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20181,6 +20170,17 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B33CDC9-5D8D-4043-9152-21270848773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5BB35-3014-4BC9-A32E-BDD59E90CD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,17 +614,41 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,13 +656,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,32 +692,14 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="53"/>
+      <c r="BN2" s="53"/>
+      <c r="BO2" s="53"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="53"/>
+      <c r="CA2" s="53"/>
+      <c r="CB2" s="53"/>
+      <c r="CC2" s="53"/>
+      <c r="CD2" s="53"/>
+      <c r="CE2" s="53"/>
+      <c r="CF2" s="53"/>
+      <c r="CG2" s="53"/>
+      <c r="CH2" s="53"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="47">
+      <c r="B3" s="55"/>
+      <c r="C3" s="29">
         <v>2020</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29">
         <v>2021</v>
       </c>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="27">
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="30">
         <v>2022</v>
       </c>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27">
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30">
         <v>2023</v>
       </c>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27">
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27">
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30">
         <v>2025</v>
       </c>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27">
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30">
         <v>2026</v>
       </c>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-      <c r="CH3" s="27"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="49"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="49"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="49"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="49"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="49"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="49"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9221,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="52"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10233,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="52"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="52"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="52"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="36" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="54"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="54"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12671,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="54"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12895,13 +12895,13 @@
         <v>8597.010666666667</v>
       </c>
       <c r="BX49" s="20">
-        <v>0</v>
+        <v>3460.4373333333333</v>
       </c>
       <c r="BY49" s="20">
-        <v>0</v>
+        <v>4774.8026666666665</v>
       </c>
       <c r="BZ49" s="20">
-        <v>0</v>
+        <v>4357.7093333333332</v>
       </c>
       <c r="CA49" s="20">
         <v>0</v>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="54"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="55"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13705,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="35"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="45" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14223,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="40"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="40"/>
+      <c r="A57" s="46"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="40"/>
+      <c r="A58" s="46"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="41"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="42" t="s">
+      <c r="A60" s="48" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15763,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="43"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="42" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16281,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16539,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="43"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16797,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="38"/>
+      <c r="A65" s="44"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17055,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="44" t="s">
+      <c r="A66" s="50" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="45"/>
+      <c r="A67" s="51"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
+      <c r="A71" s="27" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18611,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="41"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
+      <c r="A73" s="41"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="34"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19385,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
+      <c r="A75" s="28"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="39" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19903,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="32"/>
+      <c r="A77" s="40"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20162,6 +20162,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20170,17 +20181,6 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5BB35-3014-4BC9-A32E-BDD59E90CD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6E6D77-8736-46D4-9211-01FBD657FEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,41 +614,17 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,7 +632,13 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -692,14 +674,32 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="53"/>
-      <c r="AS2" s="53"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="53"/>
-      <c r="BN2" s="53"/>
-      <c r="BO2" s="53"/>
-      <c r="BP2" s="53"/>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="53"/>
-      <c r="BS2" s="53"/>
-      <c r="BT2" s="53"/>
-      <c r="BU2" s="53"/>
-      <c r="BV2" s="53"/>
-      <c r="BW2" s="53"/>
-      <c r="BX2" s="53"/>
-      <c r="BY2" s="53"/>
-      <c r="BZ2" s="53"/>
-      <c r="CA2" s="53"/>
-      <c r="CB2" s="53"/>
-      <c r="CC2" s="53"/>
-      <c r="CD2" s="53"/>
-      <c r="CE2" s="53"/>
-      <c r="CF2" s="53"/>
-      <c r="CG2" s="53"/>
-      <c r="CH2" s="53"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="29">
+      <c r="B3" s="30"/>
+      <c r="C3" s="47">
         <v>2020</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29">
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47">
         <v>2021</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="30">
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="27">
         <v>2022</v>
       </c>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30">
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27">
         <v>2023</v>
       </c>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30">
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30">
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27">
         <v>2025</v>
       </c>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30">
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27">
         <v>2026</v>
       </c>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
+      <c r="BX3" s="27"/>
+      <c r="BY3" s="27"/>
+      <c r="BZ3" s="27"/>
+      <c r="CA3" s="27"/>
+      <c r="CB3" s="27"/>
+      <c r="CC3" s="27"/>
+      <c r="CD3" s="27"/>
+      <c r="CE3" s="27"/>
+      <c r="CF3" s="27"/>
+      <c r="CG3" s="27"/>
+      <c r="CH3" s="27"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="48" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
+      <c r="A28" s="49"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
+      <c r="A32" s="49"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
+      <c r="A34" s="49"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9221,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="51" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="35"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10233,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="35"/>
+      <c r="A39" s="52"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="35"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="35"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="35"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="53" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="54"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="54"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12671,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="54"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="54"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="55"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13705,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="45" t="s">
+      <c r="A54" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14223,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="40"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="40"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
+      <c r="A57" s="40"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="41"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="42" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15763,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="42" t="s">
+      <c r="A62" s="36" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16253,7 +16253,7 @@
         <v>74685.2</v>
       </c>
       <c r="BZ62" s="24">
-        <v>65494.761538461535</v>
+        <v>85513.846153846156</v>
       </c>
       <c r="CA62" s="24">
         <v>0</v>
@@ -16281,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="43"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16511,7 +16511,7 @@
         <v>77825.3</v>
       </c>
       <c r="BZ63" s="24">
-        <v>66703.946153846162</v>
+        <v>84109.230769230766</v>
       </c>
       <c r="CA63" s="24">
         <v>0</v>
@@ -16539,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="43"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16797,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17027,7 +17027,7 @@
         <v>29489.253846153842</v>
       </c>
       <c r="BZ65" s="24">
-        <v>31257.13846153846</v>
+        <v>44503.292307692303</v>
       </c>
       <c r="CA65" s="24">
         <v>0</v>
@@ -17055,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="51"/>
+      <c r="A67" s="45"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="46"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18611,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="41"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="41"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19385,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="31" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19903,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="40"/>
+      <c r="A77" s="32"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20162,17 +20162,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20181,6 +20170,17 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6E6D77-8736-46D4-9211-01FBD657FEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046B8D81-48EE-4DF2-A74B-D2AEF2F9884B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,17 +614,41 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,13 +656,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,32 +692,14 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="53"/>
+      <c r="BN2" s="53"/>
+      <c r="BO2" s="53"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="53"/>
+      <c r="CA2" s="53"/>
+      <c r="CB2" s="53"/>
+      <c r="CC2" s="53"/>
+      <c r="CD2" s="53"/>
+      <c r="CE2" s="53"/>
+      <c r="CF2" s="53"/>
+      <c r="CG2" s="53"/>
+      <c r="CH2" s="53"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="47">
+      <c r="B3" s="55"/>
+      <c r="C3" s="29">
         <v>2020</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29">
         <v>2021</v>
       </c>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="27">
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="30">
         <v>2022</v>
       </c>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27">
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30">
         <v>2023</v>
       </c>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27">
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27">
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30">
         <v>2025</v>
       </c>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27">
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30">
         <v>2026</v>
       </c>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-      <c r="CH3" s="27"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="49"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="49"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="49"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="49"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="49"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="49"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9221,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="52"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10233,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="52"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="52"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="52"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="36" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="54"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="54"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12671,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="54"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="54"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="55"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13705,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="35"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="45" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14223,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="40"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="40"/>
+      <c r="A57" s="46"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="40"/>
+      <c r="A58" s="46"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="41"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="42" t="s">
+      <c r="A60" s="48" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15763,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="43"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="42" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16281,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16539,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="43"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16797,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="38"/>
+      <c r="A65" s="44"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17055,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="44" t="s">
+      <c r="A66" s="50" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="45"/>
+      <c r="A67" s="51"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17545,7 +17545,7 @@
         <v>73214.234332425069</v>
       </c>
       <c r="BZ67" s="25">
-        <v>48583.171662125336</v>
+        <v>55989.539509536778</v>
       </c>
       <c r="CA67" s="25">
         <v>0</v>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
+      <c r="A71" s="27" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18611,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="41"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
+      <c r="A73" s="41"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="34"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19385,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
+      <c r="A75" s="28"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="39" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19903,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="32"/>
+      <c r="A77" s="40"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20162,6 +20162,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20170,17 +20181,6 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046B8D81-48EE-4DF2-A74B-D2AEF2F9884B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EAC5A5-2B71-4B77-BFB2-F0E788B978BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -614,41 +614,17 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,7 +632,13 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -692,14 +674,32 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1024,199 +1024,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="53"/>
-      <c r="AS2" s="53"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="53"/>
-      <c r="BN2" s="53"/>
-      <c r="BO2" s="53"/>
-      <c r="BP2" s="53"/>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="53"/>
-      <c r="BS2" s="53"/>
-      <c r="BT2" s="53"/>
-      <c r="BU2" s="53"/>
-      <c r="BV2" s="53"/>
-      <c r="BW2" s="53"/>
-      <c r="BX2" s="53"/>
-      <c r="BY2" s="53"/>
-      <c r="BZ2" s="53"/>
-      <c r="CA2" s="53"/>
-      <c r="CB2" s="53"/>
-      <c r="CC2" s="53"/>
-      <c r="CD2" s="53"/>
-      <c r="CE2" s="53"/>
-      <c r="CF2" s="53"/>
-      <c r="CG2" s="53"/>
-      <c r="CH2" s="53"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="29">
+      <c r="B3" s="30"/>
+      <c r="C3" s="47">
         <v>2020</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29">
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47">
         <v>2021</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="30">
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="27">
         <v>2022</v>
       </c>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30">
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27">
         <v>2023</v>
       </c>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30">
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30">
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27">
         <v>2025</v>
       </c>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30">
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27">
         <v>2026</v>
       </c>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
+      <c r="BX3" s="27"/>
+      <c r="BY3" s="27"/>
+      <c r="BZ3" s="27"/>
+      <c r="CA3" s="27"/>
+      <c r="CB3" s="27"/>
+      <c r="CC3" s="27"/>
+      <c r="CD3" s="27"/>
+      <c r="CE3" s="27"/>
+      <c r="CF3" s="27"/>
+      <c r="CG3" s="27"/>
+      <c r="CH3" s="27"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="48" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5609,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6383,7 +6383,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7415,7 +7415,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
+      <c r="A28" s="49"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8447,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
+      <c r="A32" s="49"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
+      <c r="A34" s="49"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9221,7 +9221,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="51" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9947,7 +9947,7 @@
         <v>120299.72602739726</v>
       </c>
       <c r="BZ37" s="19">
-        <v>118433.1506849315</v>
+        <v>107641.64383561644</v>
       </c>
       <c r="CA37" s="19">
         <v>0</v>
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="35"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10233,7 +10233,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="35"/>
+      <c r="A39" s="52"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10491,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="35"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10749,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="35"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="35"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12039,7 +12039,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="53" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="54"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="54"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12671,7 +12671,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="54"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="54"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="55"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13705,7 +13705,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13963,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="45" t="s">
+      <c r="A54" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14223,7 +14223,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="40"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="40"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
+      <c r="A57" s="40"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14987,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="41"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15503,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="42" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15763,7 +15763,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16021,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="42" t="s">
+      <c r="A62" s="36" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16281,7 +16281,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="43"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16539,7 +16539,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="43"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16797,7 +16797,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17055,7 +17055,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17315,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="51"/>
+      <c r="A67" s="45"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="46"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18611,7 +18611,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="41"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="41"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19385,7 +19385,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="31" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19903,7 +19903,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="40"/>
+      <c r="A77" s="32"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20162,17 +20162,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20181,6 +20170,17 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EAC5A5-2B71-4B77-BFB2-F0E788B978BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40152615-D869-415F-AA1D-4C52BA241A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -5581,7 +5581,7 @@
         <v>309774.48630136985</v>
       </c>
       <c r="BZ20" s="17">
-        <v>414111.4726027397</v>
+        <v>415053.76712328766</v>
       </c>
       <c r="CA20" s="17">
         <v>0</v>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40152615-D869-415F-AA1D-4C52BA241A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33A9108-2C6D-437C-9D38-8E40E5D55DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -1011,8 +1011,8 @@
     <col min="67" max="69" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="71" max="77" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="16384" width="9.109375" style="1"/>
+    <col min="78" max="79" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:86" x14ac:dyDescent="0.3">
@@ -1714,7 +1714,7 @@
         <v>65558.047945205486</v>
       </c>
       <c r="CA5" s="17">
-        <v>0</v>
+        <v>66425.684931506854</v>
       </c>
       <c r="CB5" s="17">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>63541.438356164384</v>
       </c>
       <c r="CA8" s="17">
-        <v>0</v>
+        <v>75069.520547945212</v>
       </c>
       <c r="CB8" s="17">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>37692.636986301368</v>
       </c>
       <c r="CA9" s="17">
-        <v>0</v>
+        <v>42977.226027397257</v>
       </c>
       <c r="CB9" s="17">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>178085.10273972602</v>
       </c>
       <c r="CA10" s="17">
-        <v>0</v>
+        <v>193347.26027397261</v>
       </c>
       <c r="CB10" s="17">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>45867.294520547948</v>
       </c>
       <c r="CA12" s="17">
-        <v>0</v>
+        <v>66931.414383561641</v>
       </c>
       <c r="CB12" s="17">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>63906.849315068495</v>
       </c>
       <c r="CA13" s="17">
-        <v>0</v>
+        <v>85919.997260273973</v>
       </c>
       <c r="CB13" s="17">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>28841.609589041094</v>
       </c>
       <c r="CA14" s="17">
-        <v>0</v>
+        <v>33391.095890410958</v>
       </c>
       <c r="CB14" s="17">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>98770.888356164389</v>
       </c>
       <c r="CA15" s="17">
-        <v>0</v>
+        <v>111856.1609589041</v>
       </c>
       <c r="CB15" s="17">
         <v>0</v>
@@ -4552,7 +4552,7 @@
         <v>102329.45205479451</v>
       </c>
       <c r="CA16" s="17">
-        <v>0</v>
+        <v>113849.65753424658</v>
       </c>
       <c r="CB16" s="17">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>35377.706849315065</v>
       </c>
       <c r="CA17" s="17">
-        <v>0</v>
+        <v>41084.931506849316</v>
       </c>
       <c r="CB17" s="17">
         <v>0</v>
@@ -5068,7 +5068,7 @@
         <v>107348.01575342465</v>
       </c>
       <c r="CA18" s="17">
-        <v>0</v>
+        <v>116591.58424657534</v>
       </c>
       <c r="CB18" s="17">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         <v>122184.24657534246</v>
       </c>
       <c r="CA19" s="17">
-        <v>0</v>
+        <v>138440.92465753425</v>
       </c>
       <c r="CB19" s="17">
         <v>0</v>
@@ -5584,7 +5584,7 @@
         <v>415053.76712328766</v>
       </c>
       <c r="CA20" s="17">
-        <v>0</v>
+        <v>439976.88356164383</v>
       </c>
       <c r="CB20" s="17">
         <v>0</v>
@@ -5842,7 +5842,7 @@
         <v>80014.725856164383</v>
       </c>
       <c r="CA21" s="17">
-        <v>0</v>
+        <v>93979.965068493155</v>
       </c>
       <c r="CB21" s="17">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>55850.686986301371</v>
       </c>
       <c r="CA23" s="17">
-        <v>0</v>
+        <v>70623.11643835617</v>
       </c>
       <c r="CB23" s="17">
         <v>0</v>
@@ -6616,7 +6616,7 @@
         <v>44819.006849315068</v>
       </c>
       <c r="CA24" s="17">
-        <v>0</v>
+        <v>51705.478767123284</v>
       </c>
       <c r="CB24" s="17">
         <v>0</v>
@@ -6874,7 +6874,7 @@
         <v>30634.760273972603</v>
       </c>
       <c r="CA25" s="17">
-        <v>0</v>
+        <v>34395.205479452052</v>
       </c>
       <c r="CB25" s="17">
         <v>0</v>
@@ -7132,7 +7132,7 @@
         <v>43504.280821917811</v>
       </c>
       <c r="CA26" s="17">
-        <v>0</v>
+        <v>51106.335616438359</v>
       </c>
       <c r="CB26" s="17">
         <v>0</v>
@@ -7390,7 +7390,7 @@
         <v>47391.952054794521</v>
       </c>
       <c r="CA27" s="17">
-        <v>0</v>
+        <v>56082.020547945205</v>
       </c>
       <c r="CB27" s="17">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>39437.67123287671</v>
       </c>
       <c r="CA28" s="17">
-        <v>0</v>
+        <v>62683.561643835616</v>
       </c>
       <c r="CB28" s="17">
         <v>0</v>
@@ -7906,7 +7906,7 @@
         <v>63641.095890410958</v>
       </c>
       <c r="CA29" s="17">
-        <v>0</v>
+        <v>85578.224657534243</v>
       </c>
       <c r="CB29" s="17">
         <v>0</v>
@@ -8164,7 +8164,7 @@
         <v>74142.294520547948</v>
       </c>
       <c r="CA30" s="17">
-        <v>0</v>
+        <v>79491.780821917811</v>
       </c>
       <c r="CB30" s="17">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>56189.876712328769</v>
       </c>
       <c r="CA31" s="17">
-        <v>0</v>
+        <v>70839.212328767127</v>
       </c>
       <c r="CB31" s="17">
         <v>0</v>
@@ -9196,7 +9196,7 @@
         <v>29834.066780821919</v>
       </c>
       <c r="CA34" s="17">
-        <v>0</v>
+        <v>36983.426369863017</v>
       </c>
       <c r="CB34" s="17">
         <v>0</v>
@@ -9690,7 +9690,7 @@
         <v>15405.493150684932</v>
       </c>
       <c r="CA36" s="17">
-        <v>0</v>
+        <v>21879.325342465752</v>
       </c>
       <c r="CB36" s="17">
         <v>0</v>
@@ -9950,7 +9950,7 @@
         <v>107641.64383561644</v>
       </c>
       <c r="CA37" s="19">
-        <v>0</v>
+        <v>119513.97260273973</v>
       </c>
       <c r="CB37" s="19">
         <v>0</v>
@@ -10208,7 +10208,7 @@
         <v>88373.972602739726</v>
       </c>
       <c r="CA38" s="19">
-        <v>0</v>
+        <v>86029.04109589041</v>
       </c>
       <c r="CB38" s="19">
         <v>0</v>
@@ -11240,7 +11240,7 @@
         <v>36512.054794520547</v>
       </c>
       <c r="CA42" s="19">
-        <v>0</v>
+        <v>58941.095890410958</v>
       </c>
       <c r="CB42" s="19">
         <v>0</v>
@@ -11756,7 +11756,7 @@
         <v>19426.849315068495</v>
       </c>
       <c r="CA44" s="19">
-        <v>0</v>
+        <v>20677.808219178081</v>
       </c>
       <c r="CB44" s="19">
         <v>0</v>
@@ -12014,7 +12014,7 @@
         <v>37856.986301369863</v>
       </c>
       <c r="CA45" s="19">
-        <v>0</v>
+        <v>39852.602739726026</v>
       </c>
       <c r="CB45" s="19">
         <v>0</v>
@@ -12460,7 +12460,7 @@
         <v>43386.701333333338</v>
       </c>
       <c r="CA47" s="20">
-        <v>0</v>
+        <v>42109.178666666667</v>
       </c>
       <c r="CB47" s="20">
         <v>0</v>
@@ -12646,7 +12646,7 @@
         <v>26340.965333333334</v>
       </c>
       <c r="CA48" s="20">
-        <v>0</v>
+        <v>23939.32</v>
       </c>
       <c r="CB48" s="20">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>47790.630160034823</v>
       </c>
       <c r="CA52" s="21">
-        <v>0</v>
+        <v>41910.565284835589</v>
       </c>
       <c r="CB52" s="21">
         <v>0</v>
@@ -14198,7 +14198,7 @@
         <v>23863.437106918238</v>
       </c>
       <c r="CA54" s="22">
-        <v>0</v>
+        <v>32430.716981132071</v>
       </c>
       <c r="CB54" s="22">
         <v>0</v>
@@ -14446,7 +14446,7 @@
         <v>15140.830188679243</v>
       </c>
       <c r="CA55" s="22">
-        <v>0</v>
+        <v>18415.182389937105</v>
       </c>
       <c r="CB55" s="22">
         <v>0</v>
@@ -14704,7 +14704,7 @@
         <v>67140.729559748419</v>
       </c>
       <c r="CA56" s="22">
-        <v>0</v>
+        <v>94481.427672955964</v>
       </c>
       <c r="CB56" s="22">
         <v>0</v>
@@ -15738,7 +15738,7 @@
         <v>9481.39</v>
       </c>
       <c r="CA60" s="23">
-        <v>0</v>
+        <v>11098.08</v>
       </c>
       <c r="CB60" s="23">
         <v>0</v>
@@ -16256,7 +16256,7 @@
         <v>85513.846153846156</v>
       </c>
       <c r="CA62" s="24">
-        <v>0</v>
+        <v>64901.384615384617</v>
       </c>
       <c r="CB62" s="24">
         <v>0</v>
@@ -16514,7 +16514,7 @@
         <v>84109.230769230766</v>
       </c>
       <c r="CA63" s="24">
-        <v>0</v>
+        <v>67532.038461538454</v>
       </c>
       <c r="CB63" s="24">
         <v>0</v>
@@ -16772,7 +16772,7 @@
         <v>84205.753846153835</v>
       </c>
       <c r="CA64" s="24">
-        <v>0</v>
+        <v>80250.592307692306</v>
       </c>
       <c r="CB64" s="24">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>44503.292307692303</v>
       </c>
       <c r="CA65" s="24">
-        <v>0</v>
+        <v>46203.630769230767</v>
       </c>
       <c r="CB65" s="24">
         <v>0</v>
@@ -17548,7 +17548,7 @@
         <v>55989.539509536778</v>
       </c>
       <c r="CA67" s="25">
-        <v>0</v>
+        <v>60005.125340599458</v>
       </c>
       <c r="CB67" s="25">
         <v>0</v>
@@ -17806,7 +17806,7 @@
         <v>78625.803814713901</v>
       </c>
       <c r="CA68" s="25">
-        <v>0</v>
+        <v>90823.673024523159</v>
       </c>
       <c r="CB68" s="25">
         <v>0</v>
@@ -18326,7 +18326,7 @@
         <v>19540.892473118278</v>
       </c>
       <c r="CA70" s="26">
-        <v>0</v>
+        <v>17833.860215053763</v>
       </c>
       <c r="CB70" s="26">
         <v>0</v>
@@ -18586,7 +18586,7 @@
         <v>58890.09</v>
       </c>
       <c r="CA71" s="21">
-        <v>0</v>
+        <v>76917.320000000007</v>
       </c>
       <c r="CB71" s="21">
         <v>0</v>
@@ -19102,7 +19102,7 @@
         <v>70560.289999999994</v>
       </c>
       <c r="CA73" s="21">
-        <v>0</v>
+        <v>74071.17</v>
       </c>
       <c r="CB73" s="21">
         <v>0</v>
@@ -19360,7 +19360,7 @@
         <v>40195.93</v>
       </c>
       <c r="CA74" s="21">
-        <v>0</v>
+        <v>85120.91</v>
       </c>
       <c r="CB74" s="21">
         <v>0</v>
@@ -19618,7 +19618,7 @@
         <v>37595.480000000003</v>
       </c>
       <c r="CA75" s="21">
-        <v>0</v>
+        <v>38730.949999999997</v>
       </c>
       <c r="CB75" s="21">
         <v>0</v>
@@ -19878,7 +19878,7 @@
         <v>54807.573544752762</v>
       </c>
       <c r="CA76" s="26">
-        <v>0</v>
+        <v>53875.617219556298</v>
       </c>
       <c r="CB76" s="26">
         <v>0</v>
@@ -20136,7 +20136,7 @@
         <v>50643.445302176791</v>
       </c>
       <c r="CA77" s="26">
-        <v>0</v>
+        <v>61627.908755824472</v>
       </c>
       <c r="CB77" s="26">
         <v>0</v>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33A9108-2C6D-437C-9D38-8E40E5D55DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9EA00B-C665-422C-AB7B-213B6BA83605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -562,7 +562,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -614,17 +614,41 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,13 +656,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,33 +692,23 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1011,7 +1019,8 @@
     <col min="67" max="69" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="71" max="77" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="79" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="80" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
@@ -1024,199 +1033,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="53"/>
+      <c r="BN2" s="53"/>
+      <c r="BO2" s="53"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="53"/>
+      <c r="CA2" s="53"/>
+      <c r="CB2" s="53"/>
+      <c r="CC2" s="53"/>
+      <c r="CD2" s="53"/>
+      <c r="CE2" s="53"/>
+      <c r="CF2" s="53"/>
+      <c r="CG2" s="53"/>
+      <c r="CH2" s="53"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="47">
+      <c r="B3" s="55"/>
+      <c r="C3" s="29">
         <v>2020</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29">
         <v>2021</v>
       </c>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="27">
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="30">
         <v>2022</v>
       </c>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27">
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30">
         <v>2023</v>
       </c>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27">
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27">
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30">
         <v>2025</v>
       </c>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27">
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30">
         <v>2026</v>
       </c>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-      <c r="CH3" s="27"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1479,7 +1488,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1713,7 +1722,7 @@
       <c r="BZ5" s="17">
         <v>65558.047945205486</v>
       </c>
-      <c r="CA5" s="17">
+      <c r="CA5" s="56">
         <v>66425.684931506854</v>
       </c>
       <c r="CB5" s="17">
@@ -1739,7 +1748,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1997,7 +2006,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2255,7 +2264,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2487,7 +2496,7 @@
       <c r="BZ8" s="17">
         <v>63541.438356164384</v>
       </c>
-      <c r="CA8" s="17">
+      <c r="CA8" s="56">
         <v>75069.520547945212</v>
       </c>
       <c r="CB8" s="17">
@@ -2513,7 +2522,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2745,7 +2754,7 @@
       <c r="BZ9" s="17">
         <v>37692.636986301368</v>
       </c>
-      <c r="CA9" s="17">
+      <c r="CA9" s="56">
         <v>42977.226027397257</v>
       </c>
       <c r="CB9" s="17">
@@ -2771,7 +2780,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3003,7 +3012,7 @@
       <c r="BZ10" s="17">
         <v>178085.10273972602</v>
       </c>
-      <c r="CA10" s="17">
+      <c r="CA10" s="56">
         <v>193347.26027397261</v>
       </c>
       <c r="CB10" s="17">
@@ -3029,7 +3038,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="49"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3261,8 +3270,8 @@
       <c r="BZ11" s="17">
         <v>68149.315068493146</v>
       </c>
-      <c r="CA11" s="17">
-        <v>0</v>
+      <c r="CA11" s="56">
+        <v>90423.972602739726</v>
       </c>
       <c r="CB11" s="17">
         <v>0</v>
@@ -3287,7 +3296,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="49"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3519,7 +3528,7 @@
       <c r="BZ12" s="17">
         <v>45867.294520547948</v>
       </c>
-      <c r="CA12" s="17">
+      <c r="CA12" s="56">
         <v>66931.414383561641</v>
       </c>
       <c r="CB12" s="17">
@@ -3545,7 +3554,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3777,7 +3786,7 @@
       <c r="BZ13" s="17">
         <v>63906.849315068495</v>
       </c>
-      <c r="CA13" s="17">
+      <c r="CA13" s="56">
         <v>85919.997260273973</v>
       </c>
       <c r="CB13" s="17">
@@ -3803,7 +3812,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4035,7 +4044,7 @@
       <c r="BZ14" s="17">
         <v>28841.609589041094</v>
       </c>
-      <c r="CA14" s="17">
+      <c r="CA14" s="56">
         <v>33391.095890410958</v>
       </c>
       <c r="CB14" s="17">
@@ -4061,7 +4070,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4293,7 +4302,7 @@
       <c r="BZ15" s="17">
         <v>98770.888356164389</v>
       </c>
-      <c r="CA15" s="17">
+      <c r="CA15" s="56">
         <v>111856.1609589041</v>
       </c>
       <c r="CB15" s="17">
@@ -4319,7 +4328,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4551,7 +4560,7 @@
       <c r="BZ16" s="17">
         <v>102329.45205479451</v>
       </c>
-      <c r="CA16" s="17">
+      <c r="CA16" s="56">
         <v>113849.65753424658</v>
       </c>
       <c r="CB16" s="17">
@@ -4577,7 +4586,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="49"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4809,7 +4818,7 @@
       <c r="BZ17" s="17">
         <v>35377.706849315065</v>
       </c>
-      <c r="CA17" s="17">
+      <c r="CA17" s="56">
         <v>41084.931506849316</v>
       </c>
       <c r="CB17" s="17">
@@ -4835,7 +4844,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5067,7 +5076,7 @@
       <c r="BZ18" s="17">
         <v>107348.01575342465</v>
       </c>
-      <c r="CA18" s="17">
+      <c r="CA18" s="56">
         <v>116591.58424657534</v>
       </c>
       <c r="CB18" s="17">
@@ -5093,7 +5102,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5325,7 +5334,7 @@
       <c r="BZ19" s="17">
         <v>122184.24657534246</v>
       </c>
-      <c r="CA19" s="17">
+      <c r="CA19" s="56">
         <v>138440.92465753425</v>
       </c>
       <c r="CB19" s="17">
@@ -5351,7 +5360,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="49"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5583,7 +5592,7 @@
       <c r="BZ20" s="17">
         <v>415053.76712328766</v>
       </c>
-      <c r="CA20" s="17">
+      <c r="CA20" s="56">
         <v>439976.88356164383</v>
       </c>
       <c r="CB20" s="17">
@@ -5609,7 +5618,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5841,7 +5850,7 @@
       <c r="BZ21" s="17">
         <v>80014.725856164383</v>
       </c>
-      <c r="CA21" s="17">
+      <c r="CA21" s="56">
         <v>93979.965068493155</v>
       </c>
       <c r="CB21" s="17">
@@ -5867,7 +5876,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6125,7 +6134,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6357,7 +6366,7 @@
       <c r="BZ23" s="17">
         <v>55850.686986301371</v>
       </c>
-      <c r="CA23" s="17">
+      <c r="CA23" s="56">
         <v>70623.11643835617</v>
       </c>
       <c r="CB23" s="17">
@@ -6383,7 +6392,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6615,7 +6624,7 @@
       <c r="BZ24" s="17">
         <v>44819.006849315068</v>
       </c>
-      <c r="CA24" s="17">
+      <c r="CA24" s="56">
         <v>51705.478767123284</v>
       </c>
       <c r="CB24" s="17">
@@ -6641,7 +6650,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6873,7 +6882,7 @@
       <c r="BZ25" s="17">
         <v>30634.760273972603</v>
       </c>
-      <c r="CA25" s="17">
+      <c r="CA25" s="56">
         <v>34395.205479452052</v>
       </c>
       <c r="CB25" s="17">
@@ -6899,7 +6908,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7131,7 +7140,7 @@
       <c r="BZ26" s="17">
         <v>43504.280821917811</v>
       </c>
-      <c r="CA26" s="17">
+      <c r="CA26" s="56">
         <v>51106.335616438359</v>
       </c>
       <c r="CB26" s="17">
@@ -7157,7 +7166,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7389,7 +7398,7 @@
       <c r="BZ27" s="17">
         <v>47391.952054794521</v>
       </c>
-      <c r="CA27" s="17">
+      <c r="CA27" s="56">
         <v>56082.020547945205</v>
       </c>
       <c r="CB27" s="17">
@@ -7415,7 +7424,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7647,7 +7656,7 @@
       <c r="BZ28" s="17">
         <v>39437.67123287671</v>
       </c>
-      <c r="CA28" s="17">
+      <c r="CA28" s="56">
         <v>62683.561643835616</v>
       </c>
       <c r="CB28" s="17">
@@ -7673,7 +7682,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="49"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7905,7 +7914,7 @@
       <c r="BZ29" s="17">
         <v>63641.095890410958</v>
       </c>
-      <c r="CA29" s="17">
+      <c r="CA29" s="56">
         <v>85578.224657534243</v>
       </c>
       <c r="CB29" s="17">
@@ -7931,7 +7940,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8163,7 +8172,7 @@
       <c r="BZ30" s="17">
         <v>74142.294520547948</v>
       </c>
-      <c r="CA30" s="17">
+      <c r="CA30" s="56">
         <v>79491.780821917811</v>
       </c>
       <c r="CB30" s="17">
@@ -8189,7 +8198,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8421,7 +8430,7 @@
       <c r="BZ31" s="17">
         <v>56189.876712328769</v>
       </c>
-      <c r="CA31" s="17">
+      <c r="CA31" s="56">
         <v>70839.212328767127</v>
       </c>
       <c r="CB31" s="17">
@@ -8447,7 +8456,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8679,7 +8688,7 @@
       <c r="BZ32" s="17">
         <v>0</v>
       </c>
-      <c r="CA32" s="17">
+      <c r="CA32" s="56">
         <v>0</v>
       </c>
       <c r="CB32" s="17">
@@ -8705,7 +8714,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="49"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8937,7 +8946,7 @@
       <c r="BZ33" s="17">
         <v>0</v>
       </c>
-      <c r="CA33" s="17">
+      <c r="CA33" s="56">
         <v>0</v>
       </c>
       <c r="CB33" s="17">
@@ -8963,7 +8972,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9195,7 +9204,7 @@
       <c r="BZ34" s="17">
         <v>29834.066780821919</v>
       </c>
-      <c r="CA34" s="17">
+      <c r="CA34" s="56">
         <v>36983.426369863017</v>
       </c>
       <c r="CB34" s="17">
@@ -9221,7 +9230,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9431,7 +9440,7 @@
       <c r="BZ35" s="17">
         <v>0</v>
       </c>
-      <c r="CA35" s="17">
+      <c r="CA35" s="56">
         <v>0</v>
       </c>
       <c r="CB35" s="17">
@@ -9457,7 +9466,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9689,7 +9698,7 @@
       <c r="BZ36" s="17">
         <v>15405.493150684932</v>
       </c>
-      <c r="CA36" s="17">
+      <c r="CA36" s="56">
         <v>21879.325342465752</v>
       </c>
       <c r="CB36" s="17">
@@ -9715,7 +9724,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9949,7 +9958,7 @@
       <c r="BZ37" s="19">
         <v>107641.64383561644</v>
       </c>
-      <c r="CA37" s="19">
+      <c r="CA37" s="57">
         <v>119513.97260273973</v>
       </c>
       <c r="CB37" s="19">
@@ -9975,7 +9984,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="52"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10207,7 +10216,7 @@
       <c r="BZ38" s="19">
         <v>88373.972602739726</v>
       </c>
-      <c r="CA38" s="19">
+      <c r="CA38" s="57">
         <v>86029.04109589041</v>
       </c>
       <c r="CB38" s="19">
@@ -10233,7 +10242,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10491,7 +10500,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="52"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10749,7 +10758,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="52"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11007,7 +11016,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="52"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11239,7 +11248,7 @@
       <c r="BZ42" s="19">
         <v>36512.054794520547</v>
       </c>
-      <c r="CA42" s="19">
+      <c r="CA42" s="57">
         <v>58941.095890410958</v>
       </c>
       <c r="CB42" s="19">
@@ -11755,7 +11764,7 @@
       <c r="BZ44" s="19">
         <v>19426.849315068495</v>
       </c>
-      <c r="CA44" s="19">
+      <c r="CA44" s="57">
         <v>20677.808219178081</v>
       </c>
       <c r="CB44" s="19">
@@ -12013,7 +12022,7 @@
       <c r="BZ45" s="19">
         <v>37856.986301369863</v>
       </c>
-      <c r="CA45" s="19">
+      <c r="CA45" s="57">
         <v>39852.602739726026</v>
       </c>
       <c r="CB45" s="19">
@@ -12039,7 +12048,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="36" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12299,7 +12308,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="54"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12459,7 +12468,7 @@
       <c r="BZ47" s="20">
         <v>43386.701333333338</v>
       </c>
-      <c r="CA47" s="20">
+      <c r="CA47" s="58">
         <v>42109.178666666667</v>
       </c>
       <c r="CB47" s="20">
@@ -12485,7 +12494,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="54"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12645,7 +12654,7 @@
       <c r="BZ48" s="20">
         <v>26340.965333333334</v>
       </c>
-      <c r="CA48" s="20">
+      <c r="CA48" s="58">
         <v>23939.32</v>
       </c>
       <c r="CB48" s="20">
@@ -12671,7 +12680,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="54"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12929,7 +12938,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="54"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13187,7 +13196,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="55"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13445,7 +13454,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13679,7 +13688,7 @@
       <c r="BZ52" s="21">
         <v>47790.630160034823</v>
       </c>
-      <c r="CA52" s="21">
+      <c r="CA52" s="59">
         <v>41910.565284835589</v>
       </c>
       <c r="CB52" s="21">
@@ -13705,7 +13714,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="35"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13963,7 +13972,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="45" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14197,7 +14206,7 @@
       <c r="BZ54" s="22">
         <v>23863.437106918238</v>
       </c>
-      <c r="CA54" s="22">
+      <c r="CA54" s="60">
         <v>32430.716981132071</v>
       </c>
       <c r="CB54" s="22">
@@ -14223,7 +14232,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14445,7 +14454,7 @@
       <c r="BZ55" s="22">
         <v>15140.830188679243</v>
       </c>
-      <c r="CA55" s="22">
+      <c r="CA55" s="60">
         <v>18415.182389937105</v>
       </c>
       <c r="CB55" s="22">
@@ -14471,7 +14480,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="40"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14703,7 +14712,7 @@
       <c r="BZ56" s="22">
         <v>67140.729559748419</v>
       </c>
-      <c r="CA56" s="22">
+      <c r="CA56" s="60">
         <v>94481.427672955964</v>
       </c>
       <c r="CB56" s="22">
@@ -14729,7 +14738,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="40"/>
+      <c r="A57" s="46"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14987,7 +14996,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="40"/>
+      <c r="A58" s="46"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15245,7 +15254,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="41"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15503,7 +15512,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="42" t="s">
+      <c r="A60" s="48" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15737,7 +15746,7 @@
       <c r="BZ60" s="23">
         <v>9481.39</v>
       </c>
-      <c r="CA60" s="23">
+      <c r="CA60" s="61">
         <v>11098.08</v>
       </c>
       <c r="CB60" s="23">
@@ -15763,7 +15772,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="43"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16021,7 +16030,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="42" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16255,7 +16264,7 @@
       <c r="BZ62" s="24">
         <v>85513.846153846156</v>
       </c>
-      <c r="CA62" s="24">
+      <c r="CA62" s="62">
         <v>64901.384615384617</v>
       </c>
       <c r="CB62" s="24">
@@ -16281,7 +16290,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16513,7 +16522,7 @@
       <c r="BZ63" s="24">
         <v>84109.230769230766</v>
       </c>
-      <c r="CA63" s="24">
+      <c r="CA63" s="62">
         <v>67532.038461538454</v>
       </c>
       <c r="CB63" s="24">
@@ -16539,7 +16548,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="43"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16771,7 +16780,7 @@
       <c r="BZ64" s="24">
         <v>84205.753846153835</v>
       </c>
-      <c r="CA64" s="24">
+      <c r="CA64" s="62">
         <v>80250.592307692306</v>
       </c>
       <c r="CB64" s="24">
@@ -16797,7 +16806,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="38"/>
+      <c r="A65" s="44"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17029,7 +17038,7 @@
       <c r="BZ65" s="24">
         <v>44503.292307692303</v>
       </c>
-      <c r="CA65" s="24">
+      <c r="CA65" s="62">
         <v>46203.630769230767</v>
       </c>
       <c r="CB65" s="24">
@@ -17055,7 +17064,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="44" t="s">
+      <c r="A66" s="50" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17315,7 +17324,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="45"/>
+      <c r="A67" s="51"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17547,7 +17556,7 @@
       <c r="BZ67" s="25">
         <v>55989.539509536778</v>
       </c>
-      <c r="CA67" s="25">
+      <c r="CA67" s="63">
         <v>60005.125340599458</v>
       </c>
       <c r="CB67" s="25">
@@ -17573,7 +17582,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -17805,7 +17814,7 @@
       <c r="BZ68" s="25">
         <v>78625.803814713901</v>
       </c>
-      <c r="CA68" s="25">
+      <c r="CA68" s="63">
         <v>90823.673024523159</v>
       </c>
       <c r="CB68" s="25">
@@ -18325,7 +18334,7 @@
       <c r="BZ70" s="26">
         <v>19540.892473118278</v>
       </c>
-      <c r="CA70" s="26">
+      <c r="CA70" s="4">
         <v>17833.860215053763</v>
       </c>
       <c r="CB70" s="26">
@@ -18351,7 +18360,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
+      <c r="A71" s="27" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18585,7 +18594,7 @@
       <c r="BZ71" s="21">
         <v>58890.09</v>
       </c>
-      <c r="CA71" s="21">
+      <c r="CA71" s="59">
         <v>76917.320000000007</v>
       </c>
       <c r="CB71" s="21">
@@ -18611,7 +18620,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="41"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18869,7 +18878,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
+      <c r="A73" s="41"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19101,7 +19110,7 @@
       <c r="BZ73" s="21">
         <v>70560.289999999994</v>
       </c>
-      <c r="CA73" s="21">
+      <c r="CA73" s="59">
         <v>74071.17</v>
       </c>
       <c r="CB73" s="21">
@@ -19127,7 +19136,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="34"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19359,7 +19368,7 @@
       <c r="BZ74" s="21">
         <v>40195.93</v>
       </c>
-      <c r="CA74" s="21">
+      <c r="CA74" s="59">
         <v>85120.91</v>
       </c>
       <c r="CB74" s="21">
@@ -19385,7 +19394,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
+      <c r="A75" s="28"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19617,7 +19626,7 @@
       <c r="BZ75" s="21">
         <v>37595.480000000003</v>
       </c>
-      <c r="CA75" s="21">
+      <c r="CA75" s="59">
         <v>38730.949999999997</v>
       </c>
       <c r="CB75" s="21">
@@ -19643,7 +19652,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="39" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19877,7 +19886,7 @@
       <c r="BZ76" s="26">
         <v>54807.573544752762</v>
       </c>
-      <c r="CA76" s="26">
+      <c r="CA76" s="4">
         <v>53875.617219556298</v>
       </c>
       <c r="CB76" s="26">
@@ -19903,7 +19912,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="32"/>
+      <c r="A77" s="40"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20135,7 +20144,7 @@
       <c r="BZ77" s="26">
         <v>50643.445302176791</v>
       </c>
-      <c r="CA77" s="26">
+      <c r="CA77" s="4">
         <v>61627.908755824472</v>
       </c>
       <c r="CB77" s="26">
@@ -20162,6 +20171,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20170,17 +20190,6 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9EA00B-C665-422C-AB7B-213B6BA83605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5436CDDE-4B65-4B80-9BEA-93A85305AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -553,7 +553,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -614,49 +616,36 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -692,23 +681,36 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1033,199 +1035,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="53"/>
-      <c r="AS2" s="53"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="53"/>
-      <c r="BN2" s="53"/>
-      <c r="BO2" s="53"/>
-      <c r="BP2" s="53"/>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="53"/>
-      <c r="BS2" s="53"/>
-      <c r="BT2" s="53"/>
-      <c r="BU2" s="53"/>
-      <c r="BV2" s="53"/>
-      <c r="BW2" s="53"/>
-      <c r="BX2" s="53"/>
-      <c r="BY2" s="53"/>
-      <c r="BZ2" s="53"/>
-      <c r="CA2" s="53"/>
-      <c r="CB2" s="53"/>
-      <c r="CC2" s="53"/>
-      <c r="CD2" s="53"/>
-      <c r="CE2" s="53"/>
-      <c r="CF2" s="53"/>
-      <c r="CG2" s="53"/>
-      <c r="CH2" s="53"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="36"/>
+      <c r="AS2" s="36"/>
+      <c r="AT2" s="36"/>
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="36"/>
+      <c r="BB2" s="36"/>
+      <c r="BC2" s="36"/>
+      <c r="BD2" s="36"/>
+      <c r="BE2" s="36"/>
+      <c r="BF2" s="36"/>
+      <c r="BG2" s="36"/>
+      <c r="BH2" s="36"/>
+      <c r="BI2" s="36"/>
+      <c r="BJ2" s="36"/>
+      <c r="BK2" s="36"/>
+      <c r="BL2" s="36"/>
+      <c r="BM2" s="36"/>
+      <c r="BN2" s="36"/>
+      <c r="BO2" s="36"/>
+      <c r="BP2" s="36"/>
+      <c r="BQ2" s="36"/>
+      <c r="BR2" s="36"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="36"/>
+      <c r="BU2" s="36"/>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="36"/>
+      <c r="BX2" s="36"/>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="36"/>
+      <c r="CA2" s="36"/>
+      <c r="CB2" s="36"/>
+      <c r="CC2" s="36"/>
+      <c r="CD2" s="36"/>
+      <c r="CE2" s="36"/>
+      <c r="CF2" s="36"/>
+      <c r="CG2" s="36"/>
+      <c r="CH2" s="36"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="29">
+      <c r="B3" s="38"/>
+      <c r="C3" s="54">
         <v>2020</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29">
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54">
         <v>2021</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="30">
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="35">
         <v>2022</v>
       </c>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30">
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35">
         <v>2023</v>
       </c>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30">
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="35"/>
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30">
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BD3" s="35"/>
+      <c r="BE3" s="35"/>
+      <c r="BF3" s="35"/>
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BI3" s="35"/>
+      <c r="BJ3" s="35"/>
+      <c r="BK3" s="35">
         <v>2025</v>
       </c>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30">
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="35"/>
+      <c r="BN3" s="35"/>
+      <c r="BO3" s="35"/>
+      <c r="BP3" s="35"/>
+      <c r="BQ3" s="35"/>
+      <c r="BR3" s="35"/>
+      <c r="BS3" s="35"/>
+      <c r="BT3" s="35"/>
+      <c r="BU3" s="35"/>
+      <c r="BV3" s="35"/>
+      <c r="BW3" s="35">
         <v>2026</v>
       </c>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
+      <c r="BX3" s="35"/>
+      <c r="BY3" s="35"/>
+      <c r="BZ3" s="35"/>
+      <c r="CA3" s="35"/>
+      <c r="CB3" s="35"/>
+      <c r="CC3" s="35"/>
+      <c r="CD3" s="35"/>
+      <c r="CE3" s="35"/>
+      <c r="CF3" s="35"/>
+      <c r="CG3" s="35"/>
+      <c r="CH3" s="35"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1488,7 +1490,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="55" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1722,7 +1724,7 @@
       <c r="BZ5" s="17">
         <v>65558.047945205486</v>
       </c>
-      <c r="CA5" s="56">
+      <c r="CA5" s="27">
         <v>66425.684931506854</v>
       </c>
       <c r="CB5" s="17">
@@ -1748,7 +1750,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="56"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2006,7 +2008,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2264,7 +2266,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
+      <c r="A8" s="56"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2496,7 +2498,7 @@
       <c r="BZ8" s="17">
         <v>63541.438356164384</v>
       </c>
-      <c r="CA8" s="56">
+      <c r="CA8" s="27">
         <v>75069.520547945212</v>
       </c>
       <c r="CB8" s="17">
@@ -2522,7 +2524,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2754,7 +2756,7 @@
       <c r="BZ9" s="17">
         <v>37692.636986301368</v>
       </c>
-      <c r="CA9" s="56">
+      <c r="CA9" s="27">
         <v>42977.226027397257</v>
       </c>
       <c r="CB9" s="17">
@@ -2780,7 +2782,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3012,7 +3014,7 @@
       <c r="BZ10" s="17">
         <v>178085.10273972602</v>
       </c>
-      <c r="CA10" s="56">
+      <c r="CA10" s="27">
         <v>193347.26027397261</v>
       </c>
       <c r="CB10" s="17">
@@ -3038,7 +3040,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3270,7 +3272,7 @@
       <c r="BZ11" s="17">
         <v>68149.315068493146</v>
       </c>
-      <c r="CA11" s="56">
+      <c r="CA11" s="27">
         <v>90423.972602739726</v>
       </c>
       <c r="CB11" s="17">
@@ -3296,7 +3298,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
+      <c r="A12" s="56"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3528,7 +3530,7 @@
       <c r="BZ12" s="17">
         <v>45867.294520547948</v>
       </c>
-      <c r="CA12" s="56">
+      <c r="CA12" s="27">
         <v>66931.414383561641</v>
       </c>
       <c r="CB12" s="17">
@@ -3554,7 +3556,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3786,7 +3788,7 @@
       <c r="BZ13" s="17">
         <v>63906.849315068495</v>
       </c>
-      <c r="CA13" s="56">
+      <c r="CA13" s="27">
         <v>85919.997260273973</v>
       </c>
       <c r="CB13" s="17">
@@ -3812,7 +3814,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
+      <c r="A14" s="56"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4044,7 +4046,7 @@
       <c r="BZ14" s="17">
         <v>28841.609589041094</v>
       </c>
-      <c r="CA14" s="56">
+      <c r="CA14" s="27">
         <v>33391.095890410958</v>
       </c>
       <c r="CB14" s="17">
@@ -4070,7 +4072,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4302,7 +4304,7 @@
       <c r="BZ15" s="17">
         <v>98770.888356164389</v>
       </c>
-      <c r="CA15" s="56">
+      <c r="CA15" s="27">
         <v>111856.1609589041</v>
       </c>
       <c r="CB15" s="17">
@@ -4328,7 +4330,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="56"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4560,7 +4562,7 @@
       <c r="BZ16" s="17">
         <v>102329.45205479451</v>
       </c>
-      <c r="CA16" s="56">
+      <c r="CA16" s="27">
         <v>113849.65753424658</v>
       </c>
       <c r="CB16" s="17">
@@ -4586,7 +4588,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4818,7 +4820,7 @@
       <c r="BZ17" s="17">
         <v>35377.706849315065</v>
       </c>
-      <c r="CA17" s="56">
+      <c r="CA17" s="27">
         <v>41084.931506849316</v>
       </c>
       <c r="CB17" s="17">
@@ -4844,7 +4846,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
+      <c r="A18" s="56"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5076,7 +5078,7 @@
       <c r="BZ18" s="17">
         <v>107348.01575342465</v>
       </c>
-      <c r="CA18" s="56">
+      <c r="CA18" s="27">
         <v>116591.58424657534</v>
       </c>
       <c r="CB18" s="17">
@@ -5102,7 +5104,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5334,7 +5336,7 @@
       <c r="BZ19" s="17">
         <v>122184.24657534246</v>
       </c>
-      <c r="CA19" s="56">
+      <c r="CA19" s="27">
         <v>138440.92465753425</v>
       </c>
       <c r="CB19" s="17">
@@ -5360,7 +5362,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="56"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5592,7 +5594,7 @@
       <c r="BZ20" s="17">
         <v>415053.76712328766</v>
       </c>
-      <c r="CA20" s="56">
+      <c r="CA20" s="27">
         <v>439976.88356164383</v>
       </c>
       <c r="CB20" s="17">
@@ -5618,7 +5620,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5850,7 +5852,7 @@
       <c r="BZ21" s="17">
         <v>80014.725856164383</v>
       </c>
-      <c r="CA21" s="56">
+      <c r="CA21" s="27">
         <v>93979.965068493155</v>
       </c>
       <c r="CB21" s="17">
@@ -5876,7 +5878,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6134,7 +6136,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6366,7 +6368,7 @@
       <c r="BZ23" s="17">
         <v>55850.686986301371</v>
       </c>
-      <c r="CA23" s="56">
+      <c r="CA23" s="27">
         <v>70623.11643835617</v>
       </c>
       <c r="CB23" s="17">
@@ -6392,7 +6394,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
+      <c r="A24" s="56"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6624,7 +6626,7 @@
       <c r="BZ24" s="17">
         <v>44819.006849315068</v>
       </c>
-      <c r="CA24" s="56">
+      <c r="CA24" s="27">
         <v>51705.478767123284</v>
       </c>
       <c r="CB24" s="17">
@@ -6650,7 +6652,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6882,7 +6884,7 @@
       <c r="BZ25" s="17">
         <v>30634.760273972603</v>
       </c>
-      <c r="CA25" s="56">
+      <c r="CA25" s="27">
         <v>34395.205479452052</v>
       </c>
       <c r="CB25" s="17">
@@ -6908,7 +6910,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7140,7 +7142,7 @@
       <c r="BZ26" s="17">
         <v>43504.280821917811</v>
       </c>
-      <c r="CA26" s="56">
+      <c r="CA26" s="27">
         <v>51106.335616438359</v>
       </c>
       <c r="CB26" s="17">
@@ -7166,7 +7168,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7398,7 +7400,7 @@
       <c r="BZ27" s="17">
         <v>47391.952054794521</v>
       </c>
-      <c r="CA27" s="56">
+      <c r="CA27" s="27">
         <v>56082.020547945205</v>
       </c>
       <c r="CB27" s="17">
@@ -7424,7 +7426,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
+      <c r="A28" s="56"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7656,7 +7658,7 @@
       <c r="BZ28" s="17">
         <v>39437.67123287671</v>
       </c>
-      <c r="CA28" s="56">
+      <c r="CA28" s="27">
         <v>62683.561643835616</v>
       </c>
       <c r="CB28" s="17">
@@ -7682,7 +7684,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
+      <c r="A29" s="56"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7914,7 +7916,7 @@
       <c r="BZ29" s="17">
         <v>63641.095890410958</v>
       </c>
-      <c r="CA29" s="56">
+      <c r="CA29" s="27">
         <v>85578.224657534243</v>
       </c>
       <c r="CB29" s="17">
@@ -7940,7 +7942,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
+      <c r="A30" s="56"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8172,7 +8174,7 @@
       <c r="BZ30" s="17">
         <v>74142.294520547948</v>
       </c>
-      <c r="CA30" s="56">
+      <c r="CA30" s="27">
         <v>79491.780821917811</v>
       </c>
       <c r="CB30" s="17">
@@ -8198,7 +8200,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
+      <c r="A31" s="56"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8430,7 +8432,7 @@
       <c r="BZ31" s="17">
         <v>56189.876712328769</v>
       </c>
-      <c r="CA31" s="56">
+      <c r="CA31" s="27">
         <v>70839.212328767127</v>
       </c>
       <c r="CB31" s="17">
@@ -8456,7 +8458,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
+      <c r="A32" s="56"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8688,7 +8690,7 @@
       <c r="BZ32" s="17">
         <v>0</v>
       </c>
-      <c r="CA32" s="56">
+      <c r="CA32" s="27">
         <v>0</v>
       </c>
       <c r="CB32" s="17">
@@ -8714,7 +8716,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8946,7 +8948,7 @@
       <c r="BZ33" s="17">
         <v>0</v>
       </c>
-      <c r="CA33" s="56">
+      <c r="CA33" s="27">
         <v>0</v>
       </c>
       <c r="CB33" s="17">
@@ -8972,7 +8974,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9204,7 +9206,7 @@
       <c r="BZ34" s="17">
         <v>29834.066780821919</v>
       </c>
-      <c r="CA34" s="56">
+      <c r="CA34" s="27">
         <v>36983.426369863017</v>
       </c>
       <c r="CB34" s="17">
@@ -9230,7 +9232,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9440,7 +9442,7 @@
       <c r="BZ35" s="17">
         <v>0</v>
       </c>
-      <c r="CA35" s="56">
+      <c r="CA35" s="27">
         <v>0</v>
       </c>
       <c r="CB35" s="17">
@@ -9466,7 +9468,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
+      <c r="A36" s="57"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9698,7 +9700,7 @@
       <c r="BZ36" s="17">
         <v>15405.493150684932</v>
       </c>
-      <c r="CA36" s="56">
+      <c r="CA36" s="27">
         <v>21879.325342465752</v>
       </c>
       <c r="CB36" s="17">
@@ -9724,7 +9726,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="58" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9958,7 +9960,7 @@
       <c r="BZ37" s="19">
         <v>107641.64383561644</v>
       </c>
-      <c r="CA37" s="57">
+      <c r="CA37" s="28">
         <v>119513.97260273973</v>
       </c>
       <c r="CB37" s="19">
@@ -9984,7 +9986,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="35"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10216,7 +10218,7 @@
       <c r="BZ38" s="19">
         <v>88373.972602739726</v>
       </c>
-      <c r="CA38" s="57">
+      <c r="CA38" s="28">
         <v>86029.04109589041</v>
       </c>
       <c r="CB38" s="19">
@@ -10242,7 +10244,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="35"/>
+      <c r="A39" s="59"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10500,7 +10502,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="35"/>
+      <c r="A40" s="59"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10758,7 +10760,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="35"/>
+      <c r="A41" s="59"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11016,7 +11018,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="35"/>
+      <c r="A42" s="59"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11248,7 +11250,7 @@
       <c r="BZ42" s="19">
         <v>36512.054794520547</v>
       </c>
-      <c r="CA42" s="57">
+      <c r="CA42" s="28">
         <v>58941.095890410958</v>
       </c>
       <c r="CB42" s="19">
@@ -11764,7 +11766,7 @@
       <c r="BZ44" s="19">
         <v>19426.849315068495</v>
       </c>
-      <c r="CA44" s="57">
+      <c r="CA44" s="28">
         <v>20677.808219178081</v>
       </c>
       <c r="CB44" s="19">
@@ -12022,7 +12024,7 @@
       <c r="BZ45" s="19">
         <v>37856.986301369863</v>
       </c>
-      <c r="CA45" s="57">
+      <c r="CA45" s="28">
         <v>39852.602739726026</v>
       </c>
       <c r="CB45" s="19">
@@ -12048,7 +12050,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="60" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12308,7 +12310,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="61"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12468,7 +12470,7 @@
       <c r="BZ47" s="20">
         <v>43386.701333333338</v>
       </c>
-      <c r="CA47" s="58">
+      <c r="CA47" s="29">
         <v>42109.178666666667</v>
       </c>
       <c r="CB47" s="20">
@@ -12494,7 +12496,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="61"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12654,7 +12656,7 @@
       <c r="BZ48" s="20">
         <v>26340.965333333334</v>
       </c>
-      <c r="CA48" s="58">
+      <c r="CA48" s="29">
         <v>23939.32</v>
       </c>
       <c r="CB48" s="20">
@@ -12680,7 +12682,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="61"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12938,7 +12940,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="61"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13196,7 +13198,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13454,7 +13456,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="40" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13688,7 +13690,7 @@
       <c r="BZ52" s="21">
         <v>47790.630160034823</v>
       </c>
-      <c r="CA52" s="59">
+      <c r="CA52" s="30">
         <v>41910.565284835589</v>
       </c>
       <c r="CB52" s="21">
@@ -13714,7 +13716,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
+      <c r="A53" s="42"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13972,7 +13974,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="45" t="s">
+      <c r="A54" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14206,7 +14208,7 @@
       <c r="BZ54" s="22">
         <v>23863.437106918238</v>
       </c>
-      <c r="CA54" s="60">
+      <c r="CA54" s="31">
         <v>32430.716981132071</v>
       </c>
       <c r="CB54" s="22">
@@ -14232,7 +14234,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="47"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14454,7 +14456,7 @@
       <c r="BZ55" s="22">
         <v>15140.830188679243</v>
       </c>
-      <c r="CA55" s="60">
+      <c r="CA55" s="31">
         <v>18415.182389937105</v>
       </c>
       <c r="CB55" s="22">
@@ -14480,7 +14482,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14712,7 +14714,7 @@
       <c r="BZ56" s="22">
         <v>67140.729559748419</v>
       </c>
-      <c r="CA56" s="60">
+      <c r="CA56" s="31">
         <v>94481.427672955964</v>
       </c>
       <c r="CB56" s="22">
@@ -14738,7 +14740,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14996,7 +14998,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
+      <c r="A58" s="47"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15254,7 +15256,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="48"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15512,7 +15514,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="49" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15746,7 +15748,7 @@
       <c r="BZ60" s="23">
         <v>9481.39</v>
       </c>
-      <c r="CA60" s="61">
+      <c r="CA60" s="32">
         <v>11098.08</v>
       </c>
       <c r="CB60" s="23">
@@ -15772,7 +15774,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="50"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16030,7 +16032,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="42" t="s">
+      <c r="A62" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16264,8 +16266,8 @@
       <c r="BZ62" s="24">
         <v>85513.846153846156</v>
       </c>
-      <c r="CA62" s="62">
-        <v>64901.384615384617</v>
+      <c r="CA62" s="33">
+        <v>86111.38461538461</v>
       </c>
       <c r="CB62" s="24">
         <v>0</v>
@@ -16290,7 +16292,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="43"/>
+      <c r="A63" s="44"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16522,8 +16524,8 @@
       <c r="BZ63" s="24">
         <v>84109.230769230766</v>
       </c>
-      <c r="CA63" s="62">
-        <v>67532.038461538454</v>
+      <c r="CA63" s="33">
+        <v>84565.88461538461</v>
       </c>
       <c r="CB63" s="24">
         <v>0</v>
@@ -16548,7 +16550,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="43"/>
+      <c r="A64" s="44"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16780,7 +16782,7 @@
       <c r="BZ64" s="24">
         <v>84205.753846153835</v>
       </c>
-      <c r="CA64" s="62">
+      <c r="CA64" s="33">
         <v>80250.592307692306</v>
       </c>
       <c r="CB64" s="24">
@@ -16806,7 +16808,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
+      <c r="A65" s="45"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17038,8 +17040,8 @@
       <c r="BZ65" s="24">
         <v>44503.292307692303</v>
       </c>
-      <c r="CA65" s="62">
-        <v>46203.630769230767</v>
+      <c r="CA65" s="33">
+        <v>58605.169230769228</v>
       </c>
       <c r="CB65" s="24">
         <v>0</v>
@@ -17064,7 +17066,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="51" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17324,7 +17326,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="51"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17556,7 +17558,7 @@
       <c r="BZ67" s="25">
         <v>55989.539509536778</v>
       </c>
-      <c r="CA67" s="63">
+      <c r="CA67" s="34">
         <v>60005.125340599458</v>
       </c>
       <c r="CB67" s="25">
@@ -17582,7 +17584,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -17814,7 +17816,7 @@
       <c r="BZ68" s="25">
         <v>78625.803814713901</v>
       </c>
-      <c r="CA68" s="63">
+      <c r="CA68" s="34">
         <v>90823.673024523159</v>
       </c>
       <c r="CB68" s="25">
@@ -18360,7 +18362,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18594,7 +18596,7 @@
       <c r="BZ71" s="21">
         <v>58890.09</v>
       </c>
-      <c r="CA71" s="59">
+      <c r="CA71" s="30">
         <v>76917.320000000007</v>
       </c>
       <c r="CB71" s="21">
@@ -19110,7 +19112,7 @@
       <c r="BZ73" s="21">
         <v>70560.289999999994</v>
       </c>
-      <c r="CA73" s="59">
+      <c r="CA73" s="30">
         <v>74071.17</v>
       </c>
       <c r="CB73" s="21">
@@ -19368,7 +19370,7 @@
       <c r="BZ74" s="21">
         <v>40195.93</v>
       </c>
-      <c r="CA74" s="59">
+      <c r="CA74" s="30">
         <v>85120.91</v>
       </c>
       <c r="CB74" s="21">
@@ -19394,7 +19396,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
+      <c r="A75" s="42"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19626,7 +19628,7 @@
       <c r="BZ75" s="21">
         <v>37595.480000000003</v>
       </c>
-      <c r="CA75" s="59">
+      <c r="CA75" s="30">
         <v>38730.949999999997</v>
       </c>
       <c r="CB75" s="21">
@@ -19912,7 +19914,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="40"/>
+      <c r="A77" s="63"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20171,17 +20173,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20190,6 +20181,17 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5436CDDE-4B65-4B80-9BEA-93A85305AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB762CAA-BDBD-4C8F-A5C1-E64D4A28ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -624,28 +624,49 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -681,35 +702,14 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1035,199 +1035,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="36"/>
-      <c r="AK2" s="36"/>
-      <c r="AL2" s="36"/>
-      <c r="AM2" s="36"/>
-      <c r="AN2" s="36"/>
-      <c r="AO2" s="36"/>
-      <c r="AP2" s="36"/>
-      <c r="AQ2" s="36"/>
-      <c r="AR2" s="36"/>
-      <c r="AS2" s="36"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="36"/>
-      <c r="AV2" s="36"/>
-      <c r="AW2" s="36"/>
-      <c r="AX2" s="36"/>
-      <c r="AY2" s="36"/>
-      <c r="AZ2" s="36"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="36"/>
-      <c r="BC2" s="36"/>
-      <c r="BD2" s="36"/>
-      <c r="BE2" s="36"/>
-      <c r="BF2" s="36"/>
-      <c r="BG2" s="36"/>
-      <c r="BH2" s="36"/>
-      <c r="BI2" s="36"/>
-      <c r="BJ2" s="36"/>
-      <c r="BK2" s="36"/>
-      <c r="BL2" s="36"/>
-      <c r="BM2" s="36"/>
-      <c r="BN2" s="36"/>
-      <c r="BO2" s="36"/>
-      <c r="BP2" s="36"/>
-      <c r="BQ2" s="36"/>
-      <c r="BR2" s="36"/>
-      <c r="BS2" s="36"/>
-      <c r="BT2" s="36"/>
-      <c r="BU2" s="36"/>
-      <c r="BV2" s="36"/>
-      <c r="BW2" s="36"/>
-      <c r="BX2" s="36"/>
-      <c r="BY2" s="36"/>
-      <c r="BZ2" s="36"/>
-      <c r="CA2" s="36"/>
-      <c r="CB2" s="36"/>
-      <c r="CC2" s="36"/>
-      <c r="CD2" s="36"/>
-      <c r="CE2" s="36"/>
-      <c r="CF2" s="36"/>
-      <c r="CG2" s="36"/>
-      <c r="CH2" s="36"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="61"/>
+      <c r="AH2" s="61"/>
+      <c r="AI2" s="61"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="61"/>
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="61"/>
+      <c r="AV2" s="61"/>
+      <c r="AW2" s="61"/>
+      <c r="AX2" s="61"/>
+      <c r="AY2" s="61"/>
+      <c r="AZ2" s="61"/>
+      <c r="BA2" s="61"/>
+      <c r="BB2" s="61"/>
+      <c r="BC2" s="61"/>
+      <c r="BD2" s="61"/>
+      <c r="BE2" s="61"/>
+      <c r="BF2" s="61"/>
+      <c r="BG2" s="61"/>
+      <c r="BH2" s="61"/>
+      <c r="BI2" s="61"/>
+      <c r="BJ2" s="61"/>
+      <c r="BK2" s="61"/>
+      <c r="BL2" s="61"/>
+      <c r="BM2" s="61"/>
+      <c r="BN2" s="61"/>
+      <c r="BO2" s="61"/>
+      <c r="BP2" s="61"/>
+      <c r="BQ2" s="61"/>
+      <c r="BR2" s="61"/>
+      <c r="BS2" s="61"/>
+      <c r="BT2" s="61"/>
+      <c r="BU2" s="61"/>
+      <c r="BV2" s="61"/>
+      <c r="BW2" s="61"/>
+      <c r="BX2" s="61"/>
+      <c r="BY2" s="61"/>
+      <c r="BZ2" s="61"/>
+      <c r="CA2" s="61"/>
+      <c r="CB2" s="61"/>
+      <c r="CC2" s="61"/>
+      <c r="CD2" s="61"/>
+      <c r="CE2" s="61"/>
+      <c r="CF2" s="61"/>
+      <c r="CG2" s="61"/>
+      <c r="CH2" s="61"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="54">
+      <c r="B3" s="63"/>
+      <c r="C3" s="37">
         <v>2020</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54">
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37">
         <v>2021</v>
       </c>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="35">
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="38">
         <v>2022</v>
       </c>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35">
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38">
         <v>2023</v>
       </c>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35">
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="38"/>
+      <c r="AP3" s="38"/>
+      <c r="AQ3" s="38"/>
+      <c r="AR3" s="38"/>
+      <c r="AS3" s="38"/>
+      <c r="AT3" s="38"/>
+      <c r="AU3" s="38"/>
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="38"/>
+      <c r="AX3" s="38"/>
+      <c r="AY3" s="38">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
-      <c r="BJ3" s="35"/>
-      <c r="BK3" s="35">
+      <c r="AZ3" s="38"/>
+      <c r="BA3" s="38"/>
+      <c r="BB3" s="38"/>
+      <c r="BC3" s="38"/>
+      <c r="BD3" s="38"/>
+      <c r="BE3" s="38"/>
+      <c r="BF3" s="38"/>
+      <c r="BG3" s="38"/>
+      <c r="BH3" s="38"/>
+      <c r="BI3" s="38"/>
+      <c r="BJ3" s="38"/>
+      <c r="BK3" s="38">
         <v>2025</v>
       </c>
-      <c r="BL3" s="35"/>
-      <c r="BM3" s="35"/>
-      <c r="BN3" s="35"/>
-      <c r="BO3" s="35"/>
-      <c r="BP3" s="35"/>
-      <c r="BQ3" s="35"/>
-      <c r="BR3" s="35"/>
-      <c r="BS3" s="35"/>
-      <c r="BT3" s="35"/>
-      <c r="BU3" s="35"/>
-      <c r="BV3" s="35"/>
-      <c r="BW3" s="35">
+      <c r="BL3" s="38"/>
+      <c r="BM3" s="38"/>
+      <c r="BN3" s="38"/>
+      <c r="BO3" s="38"/>
+      <c r="BP3" s="38"/>
+      <c r="BQ3" s="38"/>
+      <c r="BR3" s="38"/>
+      <c r="BS3" s="38"/>
+      <c r="BT3" s="38"/>
+      <c r="BU3" s="38"/>
+      <c r="BV3" s="38"/>
+      <c r="BW3" s="38">
         <v>2026</v>
       </c>
-      <c r="BX3" s="35"/>
-      <c r="BY3" s="35"/>
-      <c r="BZ3" s="35"/>
-      <c r="CA3" s="35"/>
-      <c r="CB3" s="35"/>
-      <c r="CC3" s="35"/>
-      <c r="CD3" s="35"/>
-      <c r="CE3" s="35"/>
-      <c r="CF3" s="35"/>
-      <c r="CG3" s="35"/>
-      <c r="CH3" s="35"/>
+      <c r="BX3" s="38"/>
+      <c r="BY3" s="38"/>
+      <c r="BZ3" s="38"/>
+      <c r="CA3" s="38"/>
+      <c r="CB3" s="38"/>
+      <c r="CC3" s="38"/>
+      <c r="CD3" s="38"/>
+      <c r="CE3" s="38"/>
+      <c r="CF3" s="38"/>
+      <c r="CG3" s="38"/>
+      <c r="CH3" s="38"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1490,7 +1490,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1750,7 +1750,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2008,7 +2008,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2266,7 +2266,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2524,7 +2524,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="56"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2782,7 +2782,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3040,7 +3040,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="56"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3298,7 +3298,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3556,7 +3556,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3814,7 +3814,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="56"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4072,7 +4072,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4330,7 +4330,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4588,7 +4588,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4846,7 +4846,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5104,7 +5104,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="56"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5620,7 +5620,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="56"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5878,7 +5878,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="56"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6136,7 +6136,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="56"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6394,7 +6394,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="56"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6652,7 +6652,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6910,7 +6910,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="56"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7168,7 +7168,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7426,7 +7426,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="56"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7684,7 +7684,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
+      <c r="A29" s="40"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7942,7 +7942,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="56"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8200,7 +8200,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8458,7 +8458,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8716,7 +8716,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="56"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8974,7 +8974,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9232,7 +9232,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9468,7 +9468,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="57"/>
+      <c r="A36" s="41"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9726,7 +9726,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="58" t="s">
+      <c r="A37" s="42" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9986,7 +9986,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="59"/>
+      <c r="A38" s="43"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10244,7 +10244,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="59"/>
+      <c r="A39" s="43"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10502,7 +10502,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="59"/>
+      <c r="A40" s="43"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10760,7 +10760,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
+      <c r="A41" s="43"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11018,7 +11018,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="59"/>
+      <c r="A42" s="43"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -12050,7 +12050,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="60" t="s">
+      <c r="A46" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -12310,7 +12310,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="61"/>
+      <c r="A47" s="45"/>
       <c r="B47" s="11" t="s">
         <v>46</v>
       </c>
@@ -12496,7 +12496,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="61"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
@@ -12682,7 +12682,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="61"/>
+      <c r="A49" s="45"/>
       <c r="B49" s="11" t="s">
         <v>48</v>
       </c>
@@ -12940,7 +12940,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="61"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="11" t="s">
         <v>49</v>
       </c>
@@ -13198,7 +13198,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="62"/>
+      <c r="A51" s="46"/>
       <c r="B51" s="11" t="s">
         <v>50</v>
       </c>
@@ -13456,7 +13456,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="35" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -13716,7 +13716,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="42"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="12" t="s">
         <v>53</v>
       </c>
@@ -13974,7 +13974,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="53" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -14234,7 +14234,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="47"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
@@ -14482,7 +14482,7 @@
       </c>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="47"/>
+      <c r="A56" s="54"/>
       <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
@@ -14740,7 +14740,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="54"/>
       <c r="B57" s="13" t="s">
         <v>58</v>
       </c>
@@ -14998,7 +14998,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="47"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="13" t="s">
         <v>59</v>
       </c>
@@ -15256,7 +15256,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="48"/>
+      <c r="A59" s="55"/>
       <c r="B59" s="13" t="s">
         <v>60</v>
       </c>
@@ -15514,7 +15514,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49" t="s">
+      <c r="A60" s="56" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -15774,7 +15774,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="50"/>
+      <c r="A61" s="57"/>
       <c r="B61" s="14" t="s">
         <v>85</v>
       </c>
@@ -16032,7 +16032,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="50" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -16292,7 +16292,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="44"/>
+      <c r="A63" s="51"/>
       <c r="B63" s="15" t="s">
         <v>65</v>
       </c>
@@ -16550,7 +16550,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="44"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="15" t="s">
         <v>66</v>
       </c>
@@ -16808,7 +16808,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="45"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
@@ -17066,7 +17066,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="51" t="s">
+      <c r="A66" s="58" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -17326,7 +17326,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="59"/>
       <c r="B67" s="16" t="s">
         <v>69</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>55989.539509536778</v>
       </c>
       <c r="CA67" s="34">
-        <v>60005.125340599458</v>
+        <v>67598.885558583104</v>
       </c>
       <c r="CB67" s="25">
         <v>0</v>
@@ -17584,7 +17584,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="53"/>
+      <c r="A68" s="60"/>
       <c r="B68" s="16" t="s">
         <v>70</v>
       </c>
@@ -18362,7 +18362,7 @@
       </c>
     </row>
     <row r="71" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="35" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -18622,7 +18622,7 @@
       </c>
     </row>
     <row r="72" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="41"/>
+      <c r="A72" s="49"/>
       <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
@@ -18880,7 +18880,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="41"/>
+      <c r="A73" s="49"/>
       <c r="B73" s="12" t="s">
         <v>78</v>
       </c>
@@ -19113,7 +19113,7 @@
         <v>70560.289999999994</v>
       </c>
       <c r="CA73" s="30">
-        <v>74071.17</v>
+        <v>79305.31</v>
       </c>
       <c r="CB73" s="21">
         <v>0</v>
@@ -19138,7 +19138,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="49"/>
       <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
@@ -19396,7 +19396,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="42"/>
+      <c r="A75" s="36"/>
       <c r="B75" s="12" t="s">
         <v>80</v>
       </c>
@@ -19654,7 +19654,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="47" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
@@ -19914,7 +19914,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="63"/>
+      <c r="A77" s="48"/>
       <c r="B77" s="5" t="s">
         <v>83</v>
       </c>
@@ -20173,6 +20173,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:A68"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
@@ -20181,17 +20192,6 @@
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A37:A42"/>
     <mergeCell ref="A46:A51"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81CCEAD-F7FB-4248-93CC-31CCF6B03600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC176C36-4732-4963-B103-889368045F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,22 +627,28 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -652,6 +658,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -687,35 +708,14 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="61"/>
+      <c r="AH2" s="61"/>
+      <c r="AI2" s="61"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="61"/>
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="61"/>
+      <c r="AV2" s="61"/>
+      <c r="AW2" s="61"/>
+      <c r="AX2" s="61"/>
+      <c r="AY2" s="61"/>
+      <c r="AZ2" s="61"/>
+      <c r="BA2" s="61"/>
+      <c r="BB2" s="61"/>
+      <c r="BC2" s="61"/>
+      <c r="BD2" s="61"/>
+      <c r="BE2" s="61"/>
+      <c r="BF2" s="61"/>
+      <c r="BG2" s="61"/>
+      <c r="BH2" s="61"/>
+      <c r="BI2" s="61"/>
+      <c r="BJ2" s="61"/>
+      <c r="BK2" s="61"/>
+      <c r="BL2" s="61"/>
+      <c r="BM2" s="61"/>
+      <c r="BN2" s="61"/>
+      <c r="BO2" s="61"/>
+      <c r="BP2" s="61"/>
+      <c r="BQ2" s="61"/>
+      <c r="BR2" s="61"/>
+      <c r="BS2" s="61"/>
+      <c r="BT2" s="61"/>
+      <c r="BU2" s="61"/>
+      <c r="BV2" s="61"/>
+      <c r="BW2" s="61"/>
+      <c r="BX2" s="61"/>
+      <c r="BY2" s="61"/>
+      <c r="BZ2" s="61"/>
+      <c r="CA2" s="61"/>
+      <c r="CB2" s="61"/>
+      <c r="CC2" s="61"/>
+      <c r="CD2" s="61"/>
+      <c r="CE2" s="61"/>
+      <c r="CF2" s="61"/>
+      <c r="CG2" s="61"/>
+      <c r="CH2" s="61"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="54">
+      <c r="B3" s="63"/>
+      <c r="C3" s="34">
         <v>2020</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54">
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34">
         <v>2021</v>
       </c>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="34">
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="35">
         <v>2022</v>
       </c>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34">
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35">
         <v>2023</v>
       </c>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
-      <c r="AP3" s="34"/>
-      <c r="AQ3" s="34"/>
-      <c r="AR3" s="34"/>
-      <c r="AS3" s="34"/>
-      <c r="AT3" s="34"/>
-      <c r="AU3" s="34"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="34"/>
-      <c r="AX3" s="34"/>
-      <c r="AY3" s="34">
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="35"/>
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="34"/>
-      <c r="BA3" s="34"/>
-      <c r="BB3" s="34"/>
-      <c r="BC3" s="34"/>
-      <c r="BD3" s="34"/>
-      <c r="BE3" s="34"/>
-      <c r="BF3" s="34"/>
-      <c r="BG3" s="34"/>
-      <c r="BH3" s="34"/>
-      <c r="BI3" s="34"/>
-      <c r="BJ3" s="34"/>
-      <c r="BK3" s="34">
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BD3" s="35"/>
+      <c r="BE3" s="35"/>
+      <c r="BF3" s="35"/>
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BI3" s="35"/>
+      <c r="BJ3" s="35"/>
+      <c r="BK3" s="35">
         <v>2025</v>
       </c>
-      <c r="BL3" s="34"/>
-      <c r="BM3" s="34"/>
-      <c r="BN3" s="34"/>
-      <c r="BO3" s="34"/>
-      <c r="BP3" s="34"/>
-      <c r="BQ3" s="34"/>
-      <c r="BR3" s="34"/>
-      <c r="BS3" s="34"/>
-      <c r="BT3" s="34"/>
-      <c r="BU3" s="34"/>
-      <c r="BV3" s="34"/>
-      <c r="BW3" s="34">
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="35"/>
+      <c r="BN3" s="35"/>
+      <c r="BO3" s="35"/>
+      <c r="BP3" s="35"/>
+      <c r="BQ3" s="35"/>
+      <c r="BR3" s="35"/>
+      <c r="BS3" s="35"/>
+      <c r="BT3" s="35"/>
+      <c r="BU3" s="35"/>
+      <c r="BV3" s="35"/>
+      <c r="BW3" s="35">
         <v>2026</v>
       </c>
-      <c r="BX3" s="34"/>
-      <c r="BY3" s="34"/>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="34"/>
-      <c r="CB3" s="34"/>
-      <c r="CC3" s="34"/>
-      <c r="CD3" s="34"/>
-      <c r="CE3" s="34"/>
-      <c r="CF3" s="34"/>
-      <c r="CG3" s="34"/>
-      <c r="CH3" s="34"/>
+      <c r="BX3" s="35"/>
+      <c r="BY3" s="35"/>
+      <c r="BZ3" s="35"/>
+      <c r="CA3" s="35"/>
+      <c r="CB3" s="35"/>
+      <c r="CC3" s="35"/>
+      <c r="CD3" s="35"/>
+      <c r="CE3" s="35"/>
+      <c r="CF3" s="35"/>
+      <c r="CG3" s="35"/>
+      <c r="CH3" s="35"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="36" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="56"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="56"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>66931.414383561641</v>
       </c>
       <c r="CB12" s="16">
-        <v>0</v>
+        <v>61519.683561643833</v>
       </c>
       <c r="CC12" s="16">
         <v>0</v>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="56"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="56"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="56"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>93979.965068493155</v>
       </c>
       <c r="CB21" s="16">
-        <v>0</v>
+        <v>80990.068493150684</v>
       </c>
       <c r="CC21" s="16">
         <v>0</v>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="56"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="56"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="56"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="56"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="56"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>62683.561643835616</v>
       </c>
       <c r="CB28" s="16">
-        <v>0</v>
+        <v>49379.794520547948</v>
       </c>
       <c r="CC28" s="16">
         <v>0</v>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="56"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="56"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="57"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="58" t="s">
+      <c r="A37" s="45" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="59"/>
+      <c r="A38" s="46"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="59"/>
+      <c r="A39" s="46"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="59"/>
+      <c r="A40" s="46"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="59"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="59"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="59"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
+      <c r="A45" s="46"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="63"/>
+      <c r="A46" s="47"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="39" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="61"/>
+      <c r="A48" s="40"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="61"/>
+      <c r="A49" s="40"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="61"/>
+      <c r="A50" s="40"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="61"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
+      <c r="A52" s="41"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="42" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="41"/>
+      <c r="A54" s="43"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42"/>
+      <c r="A55" s="44"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14475,7 +14475,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="53" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14735,7 +14735,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="54"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14983,7 +14983,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="47"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15241,7 +15241,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="54"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15499,7 +15499,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="47"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15757,7 +15757,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16015,7 +16015,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="56" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16275,7 +16275,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+      <c r="A63" s="57"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16533,7 +16533,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="43" t="s">
+      <c r="A64" s="50" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16793,7 +16793,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17051,7 +17051,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="44"/>
+      <c r="A66" s="51"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17309,7 +17309,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="45"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17567,7 +17567,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="51" t="s">
+      <c r="A68" s="58" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17827,7 +17827,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="52"/>
+      <c r="A69" s="59"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18085,7 +18085,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="53"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18863,7 +18863,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="42" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19123,7 +19123,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="43"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19381,7 +19381,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
+      <c r="A75" s="43"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19639,7 +19639,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
+      <c r="A76" s="43"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19897,7 +19897,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="42"/>
+      <c r="A77" s="44"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20155,7 +20155,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="38" t="s">
+      <c r="A78" s="48" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20415,7 +20415,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="39"/>
+      <c r="A79" s="49"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20674,11 +20674,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
-    <mergeCell ref="A5:A36"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A37:A46"/>
@@ -20688,11 +20688,11 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
+    <mergeCell ref="A5:A36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahmoud\Desktop\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC176C36-4732-4963-B103-889368045F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADD560E-483C-4654-B043-DEDCC8B46B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,20 +627,17 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,14 +705,17 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
-      <c r="AR2" s="61"/>
-      <c r="AS2" s="61"/>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="61"/>
-      <c r="AV2" s="61"/>
-      <c r="AW2" s="61"/>
-      <c r="AX2" s="61"/>
-      <c r="AY2" s="61"/>
-      <c r="AZ2" s="61"/>
-      <c r="BA2" s="61"/>
-      <c r="BB2" s="61"/>
-      <c r="BC2" s="61"/>
-      <c r="BD2" s="61"/>
-      <c r="BE2" s="61"/>
-      <c r="BF2" s="61"/>
-      <c r="BG2" s="61"/>
-      <c r="BH2" s="61"/>
-      <c r="BI2" s="61"/>
-      <c r="BJ2" s="61"/>
-      <c r="BK2" s="61"/>
-      <c r="BL2" s="61"/>
-      <c r="BM2" s="61"/>
-      <c r="BN2" s="61"/>
-      <c r="BO2" s="61"/>
-      <c r="BP2" s="61"/>
-      <c r="BQ2" s="61"/>
-      <c r="BR2" s="61"/>
-      <c r="BS2" s="61"/>
-      <c r="BT2" s="61"/>
-      <c r="BU2" s="61"/>
-      <c r="BV2" s="61"/>
-      <c r="BW2" s="61"/>
-      <c r="BX2" s="61"/>
-      <c r="BY2" s="61"/>
-      <c r="BZ2" s="61"/>
-      <c r="CA2" s="61"/>
-      <c r="CB2" s="61"/>
-      <c r="CC2" s="61"/>
-      <c r="CD2" s="61"/>
-      <c r="CE2" s="61"/>
-      <c r="CF2" s="61"/>
-      <c r="CG2" s="61"/>
-      <c r="CH2" s="61"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="35"/>
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="35"/>
+      <c r="BL2" s="35"/>
+      <c r="BM2" s="35"/>
+      <c r="BN2" s="35"/>
+      <c r="BO2" s="35"/>
+      <c r="BP2" s="35"/>
+      <c r="BQ2" s="35"/>
+      <c r="BR2" s="35"/>
+      <c r="BS2" s="35"/>
+      <c r="BT2" s="35"/>
+      <c r="BU2" s="35"/>
+      <c r="BV2" s="35"/>
+      <c r="BW2" s="35"/>
+      <c r="BX2" s="35"/>
+      <c r="BY2" s="35"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="35"/>
+      <c r="CC2" s="35"/>
+      <c r="CD2" s="35"/>
+      <c r="CE2" s="35"/>
+      <c r="CF2" s="35"/>
+      <c r="CG2" s="35"/>
+      <c r="CH2" s="35"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="34">
+      <c r="B3" s="37"/>
+      <c r="C3" s="60">
         <v>2020</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34">
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60">
         <v>2021</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="35">
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="34">
         <v>2022</v>
       </c>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35">
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="34"/>
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34">
         <v>2023</v>
       </c>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35">
+      <c r="AN3" s="34"/>
+      <c r="AO3" s="34"/>
+      <c r="AP3" s="34"/>
+      <c r="AQ3" s="34"/>
+      <c r="AR3" s="34"/>
+      <c r="AS3" s="34"/>
+      <c r="AT3" s="34"/>
+      <c r="AU3" s="34"/>
+      <c r="AV3" s="34"/>
+      <c r="AW3" s="34"/>
+      <c r="AX3" s="34"/>
+      <c r="AY3" s="34">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
-      <c r="BJ3" s="35"/>
-      <c r="BK3" s="35">
+      <c r="AZ3" s="34"/>
+      <c r="BA3" s="34"/>
+      <c r="BB3" s="34"/>
+      <c r="BC3" s="34"/>
+      <c r="BD3" s="34"/>
+      <c r="BE3" s="34"/>
+      <c r="BF3" s="34"/>
+      <c r="BG3" s="34"/>
+      <c r="BH3" s="34"/>
+      <c r="BI3" s="34"/>
+      <c r="BJ3" s="34"/>
+      <c r="BK3" s="34">
         <v>2025</v>
       </c>
-      <c r="BL3" s="35"/>
-      <c r="BM3" s="35"/>
-      <c r="BN3" s="35"/>
-      <c r="BO3" s="35"/>
-      <c r="BP3" s="35"/>
-      <c r="BQ3" s="35"/>
-      <c r="BR3" s="35"/>
-      <c r="BS3" s="35"/>
-      <c r="BT3" s="35"/>
-      <c r="BU3" s="35"/>
-      <c r="BV3" s="35"/>
-      <c r="BW3" s="35">
+      <c r="BL3" s="34"/>
+      <c r="BM3" s="34"/>
+      <c r="BN3" s="34"/>
+      <c r="BO3" s="34"/>
+      <c r="BP3" s="34"/>
+      <c r="BQ3" s="34"/>
+      <c r="BR3" s="34"/>
+      <c r="BS3" s="34"/>
+      <c r="BT3" s="34"/>
+      <c r="BU3" s="34"/>
+      <c r="BV3" s="34"/>
+      <c r="BW3" s="34">
         <v>2026</v>
       </c>
-      <c r="BX3" s="35"/>
-      <c r="BY3" s="35"/>
-      <c r="BZ3" s="35"/>
-      <c r="CA3" s="35"/>
-      <c r="CB3" s="35"/>
-      <c r="CC3" s="35"/>
-      <c r="CD3" s="35"/>
-      <c r="CE3" s="35"/>
-      <c r="CF3" s="35"/>
-      <c r="CG3" s="35"/>
-      <c r="CH3" s="35"/>
+      <c r="BX3" s="34"/>
+      <c r="BY3" s="34"/>
+      <c r="BZ3" s="34"/>
+      <c r="CA3" s="34"/>
+      <c r="CB3" s="34"/>
+      <c r="CC3" s="34"/>
+      <c r="CD3" s="34"/>
+      <c r="CE3" s="34"/>
+      <c r="CF3" s="34"/>
+      <c r="CG3" s="34"/>
+      <c r="CH3" s="34"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="61" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="62"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
+      <c r="A39" s="45"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
+      <c r="A40" s="45"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
+      <c r="A42" s="45"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
+      <c r="A43" s="45"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
+      <c r="A44" s="45"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
+      <c r="A45" s="45"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="47"/>
+      <c r="A46" s="46"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39" t="s">
+      <c r="A47" s="38" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="40"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="41"/>
+      <c r="A52" s="40"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="41" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="43"/>
+      <c r="A54" s="42"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="44"/>
+      <c r="A55" s="43"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14475,7 +14475,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="53" t="s">
+      <c r="A56" s="52" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14735,7 +14735,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="54"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14983,7 +14983,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="54"/>
+      <c r="A58" s="53"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15241,7 +15241,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="54"/>
+      <c r="A59" s="53"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15499,7 +15499,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="54"/>
+      <c r="A60" s="53"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15757,7 +15757,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="55"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16015,7 +16015,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="55" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16275,7 +16275,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="57"/>
+      <c r="A63" s="56"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16533,7 +16533,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="50" t="s">
+      <c r="A64" s="49" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16771,7 +16771,7 @@
         <v>86111.38461538461</v>
       </c>
       <c r="CB64" s="23">
-        <v>63418.86153846154</v>
+        <v>76976.553846153853</v>
       </c>
       <c r="CC64" s="23">
         <v>0</v>
@@ -16793,7 +16793,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="51"/>
+      <c r="A65" s="50"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17029,7 +17029,7 @@
         <v>84565.88461538461</v>
       </c>
       <c r="CB65" s="23">
-        <v>66778.507692307685</v>
+        <v>82994.661538461529</v>
       </c>
       <c r="CC65" s="23">
         <v>0</v>
@@ -17051,7 +17051,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="51"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17309,7 +17309,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="51"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17545,7 +17545,7 @@
         <v>58605.169230769228</v>
       </c>
       <c r="CB67" s="23">
-        <v>36144.276923076919</v>
+        <v>46026.584615384614</v>
       </c>
       <c r="CC67" s="23">
         <v>0</v>
@@ -17567,7 +17567,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="58" t="s">
+      <c r="A68" s="57" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17827,7 +17827,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="59"/>
+      <c r="A69" s="58"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18085,7 +18085,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
+      <c r="A70" s="59"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18863,7 +18863,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="42" t="s">
+      <c r="A73" s="41" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19123,7 +19123,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="43"/>
+      <c r="A74" s="42"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19381,7 +19381,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="43"/>
+      <c r="A75" s="42"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19639,7 +19639,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="43"/>
+      <c r="A76" s="42"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19897,7 +19897,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="44"/>
+      <c r="A77" s="43"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20155,7 +20155,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="48" t="s">
+      <c r="A78" s="47" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20415,7 +20415,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
+      <c r="A79" s="48"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20674,11 +20674,7 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A37:A46"/>
@@ -20688,11 +20684,15 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="O3:Z3"/>
     <mergeCell ref="AA3:AL3"/>
     <mergeCell ref="AM3:AX3"/>
-    <mergeCell ref="A5:A36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADD560E-483C-4654-B043-DEDCC8B46B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B79A67-E8AB-4863-9DE2-889F7C14525B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,17 +627,14 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -705,16 +702,19 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1029,8 +1029,8 @@
     <col min="71" max="77" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="78" max="78" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="81" max="16384" width="9.109375" style="1"/>
+    <col min="80" max="81" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="82" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:86" x14ac:dyDescent="0.3">
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="60"/>
+      <c r="AT2" s="60"/>
+      <c r="AU2" s="60"/>
+      <c r="AV2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="60"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="60"/>
+      <c r="BB2" s="60"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="60"/>
+      <c r="BE2" s="60"/>
+      <c r="BF2" s="60"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="60"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="60"/>
+      <c r="BL2" s="60"/>
+      <c r="BM2" s="60"/>
+      <c r="BN2" s="60"/>
+      <c r="BO2" s="60"/>
+      <c r="BP2" s="60"/>
+      <c r="BQ2" s="60"/>
+      <c r="BR2" s="60"/>
+      <c r="BS2" s="60"/>
+      <c r="BT2" s="60"/>
+      <c r="BU2" s="60"/>
+      <c r="BV2" s="60"/>
+      <c r="BW2" s="60"/>
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="60"/>
+      <c r="BZ2" s="60"/>
+      <c r="CA2" s="60"/>
+      <c r="CB2" s="60"/>
+      <c r="CC2" s="60"/>
+      <c r="CD2" s="60"/>
+      <c r="CE2" s="60"/>
+      <c r="CF2" s="60"/>
+      <c r="CG2" s="60"/>
+      <c r="CH2" s="60"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="60">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63">
         <v>2020</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63">
         <v>2021</v>
       </c>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="60"/>
-      <c r="AA3" s="34">
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="59">
         <v>2022</v>
       </c>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34">
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="59"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59">
         <v>2023</v>
       </c>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
-      <c r="AP3" s="34"/>
-      <c r="AQ3" s="34"/>
-      <c r="AR3" s="34"/>
-      <c r="AS3" s="34"/>
-      <c r="AT3" s="34"/>
-      <c r="AU3" s="34"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="34"/>
-      <c r="AX3" s="34"/>
-      <c r="AY3" s="34">
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59"/>
+      <c r="AT3" s="59"/>
+      <c r="AU3" s="59"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="59"/>
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="59">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="34"/>
-      <c r="BA3" s="34"/>
-      <c r="BB3" s="34"/>
-      <c r="BC3" s="34"/>
-      <c r="BD3" s="34"/>
-      <c r="BE3" s="34"/>
-      <c r="BF3" s="34"/>
-      <c r="BG3" s="34"/>
-      <c r="BH3" s="34"/>
-      <c r="BI3" s="34"/>
-      <c r="BJ3" s="34"/>
-      <c r="BK3" s="34">
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="59"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="59"/>
+      <c r="BJ3" s="59"/>
+      <c r="BK3" s="59">
         <v>2025</v>
       </c>
-      <c r="BL3" s="34"/>
-      <c r="BM3" s="34"/>
-      <c r="BN3" s="34"/>
-      <c r="BO3" s="34"/>
-      <c r="BP3" s="34"/>
-      <c r="BQ3" s="34"/>
-      <c r="BR3" s="34"/>
-      <c r="BS3" s="34"/>
-      <c r="BT3" s="34"/>
-      <c r="BU3" s="34"/>
-      <c r="BV3" s="34"/>
-      <c r="BW3" s="34">
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="59"/>
+      <c r="BO3" s="59"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="59"/>
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59">
         <v>2026</v>
       </c>
-      <c r="BX3" s="34"/>
-      <c r="BY3" s="34"/>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="34"/>
-      <c r="CB3" s="34"/>
-      <c r="CC3" s="34"/>
-      <c r="CD3" s="34"/>
-      <c r="CE3" s="34"/>
-      <c r="CF3" s="34"/>
-      <c r="CG3" s="34"/>
-      <c r="CH3" s="34"/>
+      <c r="BX3" s="59"/>
+      <c r="BY3" s="59"/>
+      <c r="BZ3" s="59"/>
+      <c r="CA3" s="59"/>
+      <c r="CB3" s="59"/>
+      <c r="CC3" s="59"/>
+      <c r="CD3" s="59"/>
+      <c r="CE3" s="59"/>
+      <c r="CF3" s="59"/>
+      <c r="CG3" s="59"/>
+      <c r="CH3" s="59"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="34" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1738,7 +1738,7 @@
         <v>53432.020547945205</v>
       </c>
       <c r="CC5" s="16">
-        <v>0</v>
+        <v>62554.965753424658</v>
       </c>
       <c r="CD5" s="16">
         <v>0</v>
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="62"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="62"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>67305.308219178085</v>
       </c>
       <c r="CC8" s="16">
-        <v>0</v>
+        <v>68751.027397260274</v>
       </c>
       <c r="CD8" s="16">
         <v>0</v>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="62"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>35381.678082191778</v>
       </c>
       <c r="CC9" s="16">
-        <v>0</v>
+        <v>41147.431506849316</v>
       </c>
       <c r="CD9" s="16">
         <v>0</v>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="62"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>191886.64383561644</v>
       </c>
       <c r="CC10" s="16">
-        <v>0</v>
+        <v>210062.5</v>
       </c>
       <c r="CD10" s="16">
         <v>0</v>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="62"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>75494.006849315076</v>
       </c>
       <c r="CC11" s="16">
-        <v>0</v>
+        <v>84218.493150684924</v>
       </c>
       <c r="CD11" s="16">
         <v>0</v>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="62"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>61519.683561643833</v>
       </c>
       <c r="CC12" s="16">
-        <v>0</v>
+        <v>62303.801369863017</v>
       </c>
       <c r="CD12" s="16">
         <v>0</v>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="62"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>73539.554794520547</v>
       </c>
       <c r="CC13" s="16">
-        <v>0</v>
+        <v>103117.45890410959</v>
       </c>
       <c r="CD13" s="16">
         <v>0</v>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="62"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>30981.678082191782</v>
       </c>
       <c r="CC14" s="16">
-        <v>0</v>
+        <v>32166.780821917808</v>
       </c>
       <c r="CD14" s="16">
         <v>0</v>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="62"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>100191.77671232876</v>
       </c>
       <c r="CC15" s="16">
-        <v>0</v>
+        <v>90777.739726027401</v>
       </c>
       <c r="CD15" s="16">
         <v>0</v>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="62"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>97541.952054794514</v>
       </c>
       <c r="CC16" s="16">
-        <v>0</v>
+        <v>105414.72602739726</v>
       </c>
       <c r="CD16" s="16">
         <v>0</v>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="62"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>37001.706849315065</v>
       </c>
       <c r="CC17" s="16">
-        <v>0</v>
+        <v>38955.641780821919</v>
       </c>
       <c r="CD17" s="16">
         <v>0</v>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="62"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>111737.20205479451</v>
       </c>
       <c r="CC18" s="16">
-        <v>0</v>
+        <v>114085.75410958905</v>
       </c>
       <c r="CD18" s="16">
         <v>0</v>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="62"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>119495.37671232877</v>
       </c>
       <c r="CC19" s="16">
-        <v>0</v>
+        <v>126609.41780821918</v>
       </c>
       <c r="CD19" s="16">
         <v>0</v>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>369665.58219178085</v>
       </c>
       <c r="CC20" s="16">
-        <v>0</v>
+        <v>366443.15068493149</v>
       </c>
       <c r="CD20" s="16">
         <v>0</v>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="62"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>80990.068493150684</v>
       </c>
       <c r="CC21" s="16">
-        <v>0</v>
+        <v>84432.704794520541</v>
       </c>
       <c r="CD21" s="16">
         <v>0</v>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="62"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>57680.307534246575</v>
       </c>
       <c r="CC23" s="16">
-        <v>0</v>
+        <v>69478.254109589048</v>
       </c>
       <c r="CD23" s="16">
         <v>0</v>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="62"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="62"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>30754.790410958904</v>
       </c>
       <c r="CC25" s="16">
-        <v>0</v>
+        <v>35209.417808219179</v>
       </c>
       <c r="CD25" s="16">
         <v>0</v>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="62"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>47218.835616438359</v>
       </c>
       <c r="CC26" s="16">
-        <v>0</v>
+        <v>42843.150684931505</v>
       </c>
       <c r="CD26" s="16">
         <v>0</v>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="62"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>34647.602739726026</v>
       </c>
       <c r="CC27" s="16">
-        <v>0</v>
+        <v>45435.102739726026</v>
       </c>
       <c r="CD27" s="16">
         <v>0</v>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="62"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>49379.794520547948</v>
       </c>
       <c r="CC28" s="16">
-        <v>0</v>
+        <v>60148.972602739726</v>
       </c>
       <c r="CD28" s="16">
         <v>0</v>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="62"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>79903.239041095891</v>
       </c>
       <c r="CC29" s="16">
-        <v>0</v>
+        <v>81861.614383561639</v>
       </c>
       <c r="CD29" s="16">
         <v>0</v>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="62"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>70148.630136986307</v>
       </c>
       <c r="CC30" s="16">
-        <v>0</v>
+        <v>80272.431506849316</v>
       </c>
       <c r="CD30" s="16">
         <v>0</v>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="62"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>69697.260273972599</v>
       </c>
       <c r="CC31" s="16">
-        <v>0</v>
+        <v>75653.880821917803</v>
       </c>
       <c r="CD31" s="16">
         <v>0</v>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="62"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="62"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="62"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>29483.31506849315</v>
       </c>
       <c r="CC34" s="16">
-        <v>0</v>
+        <v>32329.357876712329</v>
       </c>
       <c r="CD34" s="16">
         <v>0</v>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="62"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="63"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>19268.476027397261</v>
       </c>
       <c r="CC36" s="16">
-        <v>0</v>
+        <v>17728.530821917808</v>
       </c>
       <c r="CD36" s="16">
         <v>0</v>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="44" t="s">
+      <c r="A37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="45"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="45"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="45"/>
+      <c r="A44" s="44"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="45"/>
+      <c r="A45" s="44"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
+      <c r="A46" s="45"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="37" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>30426.765333333333</v>
       </c>
       <c r="CC48" s="19">
-        <v>0</v>
+        <v>32989.565333333332</v>
       </c>
       <c r="CD48" s="19">
         <v>0</v>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>21680.743999999999</v>
       </c>
       <c r="CC49" s="19">
-        <v>0</v>
+        <v>22108.373333333333</v>
       </c>
       <c r="CD49" s="19">
         <v>0</v>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="40"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="41" t="s">
+      <c r="A53" s="40" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14106,7 +14106,7 @@
         <v>30750.141156221107</v>
       </c>
       <c r="CC53" s="20">
-        <v>0</v>
+        <v>87.826834147606405</v>
       </c>
       <c r="CD53" s="20">
         <v>0</v>
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="42"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="43"/>
+      <c r="A55" s="42"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14467,7 +14467,9 @@
       <c r="CB55" s="20">
         <v>273.33333333333337</v>
       </c>
-      <c r="CC55" s="20"/>
+      <c r="CC55" s="20">
+        <v>29377.333333333336</v>
+      </c>
       <c r="CD55" s="20"/>
       <c r="CE55" s="20"/>
       <c r="CF55" s="20"/>
@@ -14475,7 +14477,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="51" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14716,7 +14718,7 @@
         <v>25312.25471698113</v>
       </c>
       <c r="CC56" s="21">
-        <v>0</v>
+        <v>29502.185534591194</v>
       </c>
       <c r="CD56" s="21">
         <v>0</v>
@@ -14735,7 +14737,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="53"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14964,7 +14966,7 @@
         <v>15513.308176100629</v>
       </c>
       <c r="CC57" s="21">
-        <v>0</v>
+        <v>14882.443396226414</v>
       </c>
       <c r="CD57" s="21">
         <v>0</v>
@@ -14983,7 +14985,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="53"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15222,7 +15224,7 @@
         <v>76960.584905660377</v>
       </c>
       <c r="CC58" s="21">
-        <v>0</v>
+        <v>81483.584905660377</v>
       </c>
       <c r="CD58" s="21">
         <v>0</v>
@@ -15241,7 +15243,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="53"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15499,7 +15501,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="53"/>
+      <c r="A60" s="52"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15757,7 +15759,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="54"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16015,7 +16017,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="54" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16256,7 +16258,7 @@
         <v>7622.04</v>
       </c>
       <c r="CC62" s="22">
-        <v>0</v>
+        <v>8870.3700000000008</v>
       </c>
       <c r="CD62" s="22">
         <v>0</v>
@@ -16275,7 +16277,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="56"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16533,7 +16535,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="48" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16774,7 +16776,7 @@
         <v>76976.553846153853</v>
       </c>
       <c r="CC64" s="23">
-        <v>0</v>
+        <v>70295.38461538461</v>
       </c>
       <c r="CD64" s="23">
         <v>0</v>
@@ -16793,7 +16795,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="50"/>
+      <c r="A65" s="49"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17032,7 +17034,7 @@
         <v>82994.661538461529</v>
       </c>
       <c r="CC65" s="23">
-        <v>0</v>
+        <v>76239.269230769234</v>
       </c>
       <c r="CD65" s="23">
         <v>0</v>
@@ -17051,7 +17053,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="50"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17309,7 +17311,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="51"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17548,7 +17550,7 @@
         <v>46026.584615384614</v>
       </c>
       <c r="CC67" s="23">
-        <v>0</v>
+        <v>42025.484615384608</v>
       </c>
       <c r="CD67" s="23">
         <v>0</v>
@@ -17567,7 +17569,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="57" t="s">
+      <c r="A68" s="56" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17827,7 +17829,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="58"/>
+      <c r="A69" s="57"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18085,7 +18087,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="59"/>
+      <c r="A70" s="58"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18324,7 +18326,7 @@
         <v>69919.247956403269</v>
       </c>
       <c r="CC70" s="24">
-        <v>0</v>
+        <v>64654.019073569485</v>
       </c>
       <c r="CD70" s="24">
         <v>0</v>
@@ -18844,7 +18846,7 @@
         <v>17031.623655913976</v>
       </c>
       <c r="CC72" s="25">
-        <v>0</v>
+        <v>23120.107526881719</v>
       </c>
       <c r="CD72" s="25">
         <v>0</v>
@@ -18863,7 +18865,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="41" t="s">
+      <c r="A73" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19104,7 +19106,7 @@
         <v>68265.039999999994</v>
       </c>
       <c r="CC73" s="20">
-        <v>0</v>
+        <v>73453</v>
       </c>
       <c r="CD73" s="20">
         <v>0</v>
@@ -19123,7 +19125,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="42"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19381,7 +19383,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="42"/>
+      <c r="A75" s="41"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19620,7 +19622,7 @@
         <v>84962.46</v>
       </c>
       <c r="CC75" s="20">
-        <v>0</v>
+        <v>77438.83</v>
       </c>
       <c r="CD75" s="20">
         <v>0</v>
@@ -19639,7 +19641,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="42"/>
+      <c r="A76" s="41"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19878,7 +19880,7 @@
         <v>82508.56</v>
       </c>
       <c r="CC76" s="20">
-        <v>0</v>
+        <v>69595.259999999995</v>
       </c>
       <c r="CD76" s="20">
         <v>0</v>
@@ -19897,7 +19899,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="43"/>
+      <c r="A77" s="42"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20136,7 +20138,7 @@
         <v>32477.05</v>
       </c>
       <c r="CC77" s="20">
-        <v>0</v>
+        <v>34555.99</v>
       </c>
       <c r="CD77" s="20">
         <v>0</v>
@@ -20155,7 +20157,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="47" t="s">
+      <c r="A78" s="46" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20396,7 +20398,7 @@
         <v>54609.541692746367</v>
       </c>
       <c r="CC78" s="25">
-        <v>0</v>
+        <v>51720.376938590998</v>
       </c>
       <c r="CD78" s="25">
         <v>0</v>
@@ -20415,7 +20417,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="48"/>
+      <c r="A79" s="47"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20654,7 +20656,7 @@
         <v>54712.330481952849</v>
       </c>
       <c r="CC79" s="25">
-        <v>0</v>
+        <v>60053.779817789837</v>
       </c>
       <c r="CD79" s="25">
         <v>0</v>
@@ -20674,6 +20676,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20684,15 +20695,6 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B79A67-E8AB-4863-9DE2-889F7C14525B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612A1B83-16FC-40F1-92BA-97707BAAB98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,6 +627,21 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -700,21 +715,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="60"/>
-      <c r="AU2" s="60"/>
-      <c r="AV2" s="60"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="60"/>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="60"/>
-      <c r="BE2" s="60"/>
-      <c r="BF2" s="60"/>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="60"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="60"/>
-      <c r="BK2" s="60"/>
-      <c r="BL2" s="60"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
-      <c r="BO2" s="60"/>
-      <c r="BP2" s="60"/>
-      <c r="BQ2" s="60"/>
-      <c r="BR2" s="60"/>
-      <c r="BS2" s="60"/>
-      <c r="BT2" s="60"/>
-      <c r="BU2" s="60"/>
-      <c r="BV2" s="60"/>
-      <c r="BW2" s="60"/>
-      <c r="BX2" s="60"/>
-      <c r="BY2" s="60"/>
-      <c r="BZ2" s="60"/>
-      <c r="CA2" s="60"/>
-      <c r="CB2" s="60"/>
-      <c r="CC2" s="60"/>
-      <c r="CD2" s="60"/>
-      <c r="CE2" s="60"/>
-      <c r="CF2" s="60"/>
-      <c r="CG2" s="60"/>
-      <c r="CH2" s="60"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="35"/>
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="35"/>
+      <c r="BL2" s="35"/>
+      <c r="BM2" s="35"/>
+      <c r="BN2" s="35"/>
+      <c r="BO2" s="35"/>
+      <c r="BP2" s="35"/>
+      <c r="BQ2" s="35"/>
+      <c r="BR2" s="35"/>
+      <c r="BS2" s="35"/>
+      <c r="BT2" s="35"/>
+      <c r="BU2" s="35"/>
+      <c r="BV2" s="35"/>
+      <c r="BW2" s="35"/>
+      <c r="BX2" s="35"/>
+      <c r="BY2" s="35"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="35"/>
+      <c r="CC2" s="35"/>
+      <c r="CD2" s="35"/>
+      <c r="CE2" s="35"/>
+      <c r="CF2" s="35"/>
+      <c r="CG2" s="35"/>
+      <c r="CH2" s="35"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63">
+      <c r="B3" s="37"/>
+      <c r="C3" s="38">
         <v>2020</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63">
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38">
         <v>2021</v>
       </c>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="59">
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="34">
         <v>2022</v>
       </c>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59">
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="34"/>
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34">
         <v>2023</v>
       </c>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="59">
+      <c r="AN3" s="34"/>
+      <c r="AO3" s="34"/>
+      <c r="AP3" s="34"/>
+      <c r="AQ3" s="34"/>
+      <c r="AR3" s="34"/>
+      <c r="AS3" s="34"/>
+      <c r="AT3" s="34"/>
+      <c r="AU3" s="34"/>
+      <c r="AV3" s="34"/>
+      <c r="AW3" s="34"/>
+      <c r="AX3" s="34"/>
+      <c r="AY3" s="34">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59">
+      <c r="AZ3" s="34"/>
+      <c r="BA3" s="34"/>
+      <c r="BB3" s="34"/>
+      <c r="BC3" s="34"/>
+      <c r="BD3" s="34"/>
+      <c r="BE3" s="34"/>
+      <c r="BF3" s="34"/>
+      <c r="BG3" s="34"/>
+      <c r="BH3" s="34"/>
+      <c r="BI3" s="34"/>
+      <c r="BJ3" s="34"/>
+      <c r="BK3" s="34">
         <v>2025</v>
       </c>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="59"/>
-      <c r="BN3" s="59"/>
-      <c r="BO3" s="59"/>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="59"/>
-      <c r="BR3" s="59"/>
-      <c r="BS3" s="59"/>
-      <c r="BT3" s="59"/>
-      <c r="BU3" s="59"/>
-      <c r="BV3" s="59"/>
-      <c r="BW3" s="59">
+      <c r="BL3" s="34"/>
+      <c r="BM3" s="34"/>
+      <c r="BN3" s="34"/>
+      <c r="BO3" s="34"/>
+      <c r="BP3" s="34"/>
+      <c r="BQ3" s="34"/>
+      <c r="BR3" s="34"/>
+      <c r="BS3" s="34"/>
+      <c r="BT3" s="34"/>
+      <c r="BU3" s="34"/>
+      <c r="BV3" s="34"/>
+      <c r="BW3" s="34">
         <v>2026</v>
       </c>
-      <c r="BX3" s="59"/>
-      <c r="BY3" s="59"/>
-      <c r="BZ3" s="59"/>
-      <c r="CA3" s="59"/>
-      <c r="CB3" s="59"/>
-      <c r="CC3" s="59"/>
-      <c r="CD3" s="59"/>
-      <c r="CE3" s="59"/>
-      <c r="CF3" s="59"/>
-      <c r="CG3" s="59"/>
-      <c r="CH3" s="59"/>
+      <c r="BX3" s="34"/>
+      <c r="BY3" s="34"/>
+      <c r="BZ3" s="34"/>
+      <c r="CA3" s="34"/>
+      <c r="CB3" s="34"/>
+      <c r="CC3" s="34"/>
+      <c r="CD3" s="34"/>
+      <c r="CE3" s="34"/>
+      <c r="CF3" s="34"/>
+      <c r="CG3" s="34"/>
+      <c r="CH3" s="34"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="35"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="35"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>43653.766438356164</v>
       </c>
       <c r="CC24" s="16">
-        <v>0</v>
+        <v>44897.243150684932</v>
       </c>
       <c r="CD24" s="16">
         <v>0</v>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="35"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="35"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="35"/>
+      <c r="A29" s="40"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="35"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="35"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="35"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="35"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="35"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
+      <c r="A36" s="41"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="48" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="44"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="44"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="44"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="44"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="44"/>
+      <c r="A42" s="49"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="44"/>
+      <c r="A43" s="49"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="44"/>
+      <c r="A44" s="49"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="44"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="45"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="43"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="43"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="43"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
+      <c r="A52" s="44"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="41"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42"/>
+      <c r="A55" s="47"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14477,7 +14477,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="51" t="s">
+      <c r="A56" s="56" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14737,7 +14737,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
+      <c r="A57" s="57"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14985,7 +14985,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="52"/>
+      <c r="A58" s="57"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15243,7 +15243,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="52"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15501,7 +15501,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="52"/>
+      <c r="A60" s="57"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15759,7 +15759,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="53"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16017,7 +16017,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="59" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16277,7 +16277,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
+      <c r="A63" s="60"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16535,7 +16535,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="53" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16795,7 +16795,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="49"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17053,7 +17053,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="49"/>
+      <c r="A66" s="54"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17311,7 +17311,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="50"/>
+      <c r="A67" s="55"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17569,7 +17569,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="61" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17829,7 +17829,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="57"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18068,7 +18068,7 @@
         <v>50576.880108991827</v>
       </c>
       <c r="CC69" s="24">
-        <v>0</v>
+        <v>38526.08174386921</v>
       </c>
       <c r="CD69" s="24">
         <v>0</v>
@@ -18087,7 +18087,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="58"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18865,7 +18865,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="45" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19125,7 +19125,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="46"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19383,7 +19383,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
+      <c r="A75" s="46"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19622,7 +19622,7 @@
         <v>84962.46</v>
       </c>
       <c r="CC75" s="20">
-        <v>77438.83</v>
+        <v>84700.91</v>
       </c>
       <c r="CD75" s="20">
         <v>0</v>
@@ -19641,7 +19641,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
+      <c r="A76" s="46"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19899,7 +19899,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="42"/>
+      <c r="A77" s="47"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20157,7 +20157,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="51" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20417,7 +20417,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="47"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20676,15 +20676,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20695,6 +20686,15 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612A1B83-16FC-40F1-92BA-97707BAAB98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F06DE-2EC7-400A-9948-5CE13CBCC619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,21 +627,6 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -715,6 +700,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="60"/>
+      <c r="AT2" s="60"/>
+      <c r="AU2" s="60"/>
+      <c r="AV2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="60"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="60"/>
+      <c r="BB2" s="60"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="60"/>
+      <c r="BE2" s="60"/>
+      <c r="BF2" s="60"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="60"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="60"/>
+      <c r="BL2" s="60"/>
+      <c r="BM2" s="60"/>
+      <c r="BN2" s="60"/>
+      <c r="BO2" s="60"/>
+      <c r="BP2" s="60"/>
+      <c r="BQ2" s="60"/>
+      <c r="BR2" s="60"/>
+      <c r="BS2" s="60"/>
+      <c r="BT2" s="60"/>
+      <c r="BU2" s="60"/>
+      <c r="BV2" s="60"/>
+      <c r="BW2" s="60"/>
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="60"/>
+      <c r="BZ2" s="60"/>
+      <c r="CA2" s="60"/>
+      <c r="CB2" s="60"/>
+      <c r="CC2" s="60"/>
+      <c r="CD2" s="60"/>
+      <c r="CE2" s="60"/>
+      <c r="CF2" s="60"/>
+      <c r="CG2" s="60"/>
+      <c r="CH2" s="60"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63">
         <v>2020</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63">
         <v>2021</v>
       </c>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="34">
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="59">
         <v>2022</v>
       </c>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34">
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="59"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59">
         <v>2023</v>
       </c>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
-      <c r="AP3" s="34"/>
-      <c r="AQ3" s="34"/>
-      <c r="AR3" s="34"/>
-      <c r="AS3" s="34"/>
-      <c r="AT3" s="34"/>
-      <c r="AU3" s="34"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="34"/>
-      <c r="AX3" s="34"/>
-      <c r="AY3" s="34">
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59"/>
+      <c r="AT3" s="59"/>
+      <c r="AU3" s="59"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="59"/>
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="59">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="34"/>
-      <c r="BA3" s="34"/>
-      <c r="BB3" s="34"/>
-      <c r="BC3" s="34"/>
-      <c r="BD3" s="34"/>
-      <c r="BE3" s="34"/>
-      <c r="BF3" s="34"/>
-      <c r="BG3" s="34"/>
-      <c r="BH3" s="34"/>
-      <c r="BI3" s="34"/>
-      <c r="BJ3" s="34"/>
-      <c r="BK3" s="34">
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="59"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="59"/>
+      <c r="BJ3" s="59"/>
+      <c r="BK3" s="59">
         <v>2025</v>
       </c>
-      <c r="BL3" s="34"/>
-      <c r="BM3" s="34"/>
-      <c r="BN3" s="34"/>
-      <c r="BO3" s="34"/>
-      <c r="BP3" s="34"/>
-      <c r="BQ3" s="34"/>
-      <c r="BR3" s="34"/>
-      <c r="BS3" s="34"/>
-      <c r="BT3" s="34"/>
-      <c r="BU3" s="34"/>
-      <c r="BV3" s="34"/>
-      <c r="BW3" s="34">
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="59"/>
+      <c r="BO3" s="59"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="59"/>
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59">
         <v>2026</v>
       </c>
-      <c r="BX3" s="34"/>
-      <c r="BY3" s="34"/>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="34"/>
-      <c r="CB3" s="34"/>
-      <c r="CC3" s="34"/>
-      <c r="CD3" s="34"/>
-      <c r="CE3" s="34"/>
-      <c r="CF3" s="34"/>
-      <c r="CG3" s="34"/>
-      <c r="CH3" s="34"/>
+      <c r="BX3" s="59"/>
+      <c r="BY3" s="59"/>
+      <c r="BZ3" s="59"/>
+      <c r="CA3" s="59"/>
+      <c r="CB3" s="59"/>
+      <c r="CC3" s="59"/>
+      <c r="CD3" s="59"/>
+      <c r="CE3" s="59"/>
+      <c r="CF3" s="59"/>
+      <c r="CG3" s="59"/>
+      <c r="CH3" s="59"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="34" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="40"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="40"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="41"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9974,7 +9974,7 @@
         <v>97848.767123287675</v>
       </c>
       <c r="CC37" s="18">
-        <v>0</v>
+        <v>93776.438356164392</v>
       </c>
       <c r="CD37" s="18">
         <v>0</v>
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="49"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>58251.780821917811</v>
       </c>
       <c r="CC38" s="18">
-        <v>0</v>
+        <v>49477.534246575342</v>
       </c>
       <c r="CD38" s="18">
         <v>0</v>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="49"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="49"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="49"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="49"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>39532.602739726026</v>
       </c>
       <c r="CC42" s="18">
-        <v>0</v>
+        <v>30762.739726027397</v>
       </c>
       <c r="CD42" s="18">
         <v>0</v>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="49"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="49"/>
+      <c r="A44" s="44"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>17993.150684931508</v>
       </c>
       <c r="CC44" s="18">
-        <v>0</v>
+        <v>16513.972602739726</v>
       </c>
       <c r="CD44" s="18">
         <v>0</v>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="49"/>
+      <c r="A45" s="44"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>30604.657534246577</v>
       </c>
       <c r="CC45" s="18">
-        <v>0</v>
+        <v>25460</v>
       </c>
       <c r="CD45" s="18">
         <v>0</v>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
+      <c r="A46" s="45"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>7940.5479452054797</v>
       </c>
       <c r="CC46" s="18">
-        <v>0</v>
+        <v>15635.616438356165</v>
       </c>
       <c r="CD46" s="18">
         <v>0</v>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="42" t="s">
+      <c r="A47" s="37" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="43"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="43"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="43"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="43"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="44"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="40" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="47"/>
+      <c r="A55" s="42"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14477,7 +14477,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="51" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14737,7 +14737,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="57"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14985,7 +14985,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="57"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15243,7 +15243,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="57"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15501,7 +15501,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="57"/>
+      <c r="A60" s="52"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15759,7 +15759,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="58"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16017,7 +16017,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="59" t="s">
+      <c r="A62" s="54" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16277,7 +16277,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="60"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16535,7 +16535,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="53" t="s">
+      <c r="A64" s="48" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16795,7 +16795,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="54"/>
+      <c r="A65" s="49"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17053,7 +17053,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="54"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17311,7 +17311,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="55"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17569,7 +17569,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="56" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17829,7 +17829,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="62"/>
+      <c r="A69" s="57"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18087,7 +18087,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="63"/>
+      <c r="A70" s="58"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18865,7 +18865,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19125,7 +19125,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19383,7 +19383,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
+      <c r="A75" s="41"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19641,7 +19641,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
+      <c r="A76" s="41"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19899,7 +19899,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="47"/>
+      <c r="A77" s="42"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20157,7 +20157,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="51" t="s">
+      <c r="A78" s="46" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20417,7 +20417,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="52"/>
+      <c r="A79" s="47"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20676,6 +20676,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20686,15 +20695,6 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F06DE-2EC7-400A-9948-5CE13CBCC619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9122587-DF83-4415-83D6-C83AAF43E9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -627,6 +627,21 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -700,21 +715,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1042,199 +1042,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="60"/>
-      <c r="AU2" s="60"/>
-      <c r="AV2" s="60"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="60"/>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="60"/>
-      <c r="BE2" s="60"/>
-      <c r="BF2" s="60"/>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="60"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="60"/>
-      <c r="BK2" s="60"/>
-      <c r="BL2" s="60"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
-      <c r="BO2" s="60"/>
-      <c r="BP2" s="60"/>
-      <c r="BQ2" s="60"/>
-      <c r="BR2" s="60"/>
-      <c r="BS2" s="60"/>
-      <c r="BT2" s="60"/>
-      <c r="BU2" s="60"/>
-      <c r="BV2" s="60"/>
-      <c r="BW2" s="60"/>
-      <c r="BX2" s="60"/>
-      <c r="BY2" s="60"/>
-      <c r="BZ2" s="60"/>
-      <c r="CA2" s="60"/>
-      <c r="CB2" s="60"/>
-      <c r="CC2" s="60"/>
-      <c r="CD2" s="60"/>
-      <c r="CE2" s="60"/>
-      <c r="CF2" s="60"/>
-      <c r="CG2" s="60"/>
-      <c r="CH2" s="60"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="35"/>
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="35"/>
+      <c r="BL2" s="35"/>
+      <c r="BM2" s="35"/>
+      <c r="BN2" s="35"/>
+      <c r="BO2" s="35"/>
+      <c r="BP2" s="35"/>
+      <c r="BQ2" s="35"/>
+      <c r="BR2" s="35"/>
+      <c r="BS2" s="35"/>
+      <c r="BT2" s="35"/>
+      <c r="BU2" s="35"/>
+      <c r="BV2" s="35"/>
+      <c r="BW2" s="35"/>
+      <c r="BX2" s="35"/>
+      <c r="BY2" s="35"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="35"/>
+      <c r="CC2" s="35"/>
+      <c r="CD2" s="35"/>
+      <c r="CE2" s="35"/>
+      <c r="CF2" s="35"/>
+      <c r="CG2" s="35"/>
+      <c r="CH2" s="35"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63">
+      <c r="B3" s="37"/>
+      <c r="C3" s="38">
         <v>2020</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63">
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38">
         <v>2021</v>
       </c>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="59">
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="34">
         <v>2022</v>
       </c>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59">
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="34"/>
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34">
         <v>2023</v>
       </c>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="59">
+      <c r="AN3" s="34"/>
+      <c r="AO3" s="34"/>
+      <c r="AP3" s="34"/>
+      <c r="AQ3" s="34"/>
+      <c r="AR3" s="34"/>
+      <c r="AS3" s="34"/>
+      <c r="AT3" s="34"/>
+      <c r="AU3" s="34"/>
+      <c r="AV3" s="34"/>
+      <c r="AW3" s="34"/>
+      <c r="AX3" s="34"/>
+      <c r="AY3" s="34">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59">
+      <c r="AZ3" s="34"/>
+      <c r="BA3" s="34"/>
+      <c r="BB3" s="34"/>
+      <c r="BC3" s="34"/>
+      <c r="BD3" s="34"/>
+      <c r="BE3" s="34"/>
+      <c r="BF3" s="34"/>
+      <c r="BG3" s="34"/>
+      <c r="BH3" s="34"/>
+      <c r="BI3" s="34"/>
+      <c r="BJ3" s="34"/>
+      <c r="BK3" s="34">
         <v>2025</v>
       </c>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="59"/>
-      <c r="BN3" s="59"/>
-      <c r="BO3" s="59"/>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="59"/>
-      <c r="BR3" s="59"/>
-      <c r="BS3" s="59"/>
-      <c r="BT3" s="59"/>
-      <c r="BU3" s="59"/>
-      <c r="BV3" s="59"/>
-      <c r="BW3" s="59">
+      <c r="BL3" s="34"/>
+      <c r="BM3" s="34"/>
+      <c r="BN3" s="34"/>
+      <c r="BO3" s="34"/>
+      <c r="BP3" s="34"/>
+      <c r="BQ3" s="34"/>
+      <c r="BR3" s="34"/>
+      <c r="BS3" s="34"/>
+      <c r="BT3" s="34"/>
+      <c r="BU3" s="34"/>
+      <c r="BV3" s="34"/>
+      <c r="BW3" s="34">
         <v>2026</v>
       </c>
-      <c r="BX3" s="59"/>
-      <c r="BY3" s="59"/>
-      <c r="BZ3" s="59"/>
-      <c r="CA3" s="59"/>
-      <c r="CB3" s="59"/>
-      <c r="CC3" s="59"/>
-      <c r="CD3" s="59"/>
-      <c r="CE3" s="59"/>
-      <c r="CF3" s="59"/>
-      <c r="CG3" s="59"/>
-      <c r="CH3" s="59"/>
+      <c r="BX3" s="34"/>
+      <c r="BY3" s="34"/>
+      <c r="BZ3" s="34"/>
+      <c r="CA3" s="34"/>
+      <c r="CB3" s="34"/>
+      <c r="CC3" s="34"/>
+      <c r="CD3" s="34"/>
+      <c r="CE3" s="34"/>
+      <c r="CF3" s="34"/>
+      <c r="CG3" s="34"/>
+      <c r="CH3" s="34"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4853,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="35"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5885,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="35"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6401,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="35"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="35"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="35"/>
+      <c r="A29" s="40"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="35"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="35"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8723,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="35"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="35"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="35"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9475,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
+      <c r="A36" s="41"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="48" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="44"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="44"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10509,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="44"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="44"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11025,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="44"/>
+      <c r="A42" s="49"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="44"/>
+      <c r="A43" s="49"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11541,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="44"/>
+      <c r="A44" s="49"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="44"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12057,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="45"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="43"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="43"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="43"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
+      <c r="A52" s="44"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13865,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14125,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="41"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14383,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42"/>
+      <c r="A55" s="47"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14477,7 +14477,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="51" t="s">
+      <c r="A56" s="56" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14737,7 +14737,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
+      <c r="A57" s="57"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14985,7 +14985,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="52"/>
+      <c r="A58" s="57"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15243,7 +15243,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="52"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15501,7 +15501,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="52"/>
+      <c r="A60" s="57"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15759,7 +15759,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="53"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16017,7 +16017,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="59" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16277,7 +16277,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
+      <c r="A63" s="60"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16535,7 +16535,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="53" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16776,7 +16776,7 @@
         <v>76976.553846153853</v>
       </c>
       <c r="CC64" s="23">
-        <v>70295.38461538461</v>
+        <v>95519.230769230766</v>
       </c>
       <c r="CD64" s="23">
         <v>0</v>
@@ -16795,7 +16795,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="49"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>82994.661538461529</v>
       </c>
       <c r="CC65" s="23">
-        <v>76239.269230769234</v>
+        <v>95461.538461538454</v>
       </c>
       <c r="CD65" s="23">
         <v>0</v>
@@ -17053,7 +17053,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="49"/>
+      <c r="A66" s="54"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17311,7 +17311,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="50"/>
+      <c r="A67" s="55"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17550,7 +17550,7 @@
         <v>46026.584615384614</v>
       </c>
       <c r="CC67" s="23">
-        <v>42025.484615384608</v>
+        <v>55020.869230769233</v>
       </c>
       <c r="CD67" s="23">
         <v>0</v>
@@ -17569,7 +17569,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="61" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17829,7 +17829,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="57"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18068,7 +18068,7 @@
         <v>50576.880108991827</v>
       </c>
       <c r="CC69" s="24">
-        <v>38526.08174386921</v>
+        <v>42925.108991825611</v>
       </c>
       <c r="CD69" s="24">
         <v>0</v>
@@ -18087,7 +18087,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="58"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18865,7 +18865,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="45" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19125,7 +19125,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="46"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19383,7 +19383,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
+      <c r="A75" s="46"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19641,7 +19641,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
+      <c r="A76" s="46"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19899,7 +19899,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="42"/>
+      <c r="A77" s="47"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20157,7 +20157,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="51" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20417,7 +20417,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="47"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20676,15 +20676,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20695,6 +20686,15 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9122587-DF83-4415-83D6-C83AAF43E9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AE8BB9-A336-4EAC-B1E2-C9F37765E5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly sales" sheetId="1" r:id="rId1"/>
+    <sheet name="Monthly Balances" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="121">
   <si>
     <t>Monthly Sales USD</t>
   </si>
@@ -343,16 +344,98 @@
   <si>
     <t>Cube Mall</t>
   </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Iraq (main)</t>
+  </si>
+  <si>
+    <t>Erbil</t>
+  </si>
+  <si>
+    <t>Sulaimaniah</t>
+  </si>
+  <si>
+    <t>Riyadh</t>
+  </si>
+  <si>
+    <t>Madinah</t>
+  </si>
+  <si>
+    <t>UAE</t>
+  </si>
+  <si>
+    <t>Dubai &amp; Abu Dhabi</t>
+  </si>
+  <si>
+    <t>Sharjah</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>change location in Aug.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixed number monthly (2000$) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support life time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing support Life time </t>
+  </si>
+  <si>
+    <t>No access on their data ( With HQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partnership with HQ </t>
+  </si>
+  <si>
+    <t>Support from Mr. Adnan ( No connections)</t>
+  </si>
+  <si>
+    <t>New opening support  ( 3 month )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New opening support  ( start pay within Aug Due ) </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="mmm\.yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,8 +487,19 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="MS Sans Serif"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,6 +564,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8102E"/>
       </patternFill>
     </fill>
   </fills>
@@ -565,12 +664,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -627,21 +727,6 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -717,10 +802,32 @@
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{F15DF585-8608-45E3-B4B8-39FE711C8B6A}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1042,199 +1149,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="60"/>
+      <c r="AT2" s="60"/>
+      <c r="AU2" s="60"/>
+      <c r="AV2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="60"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="60"/>
+      <c r="BB2" s="60"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="60"/>
+      <c r="BE2" s="60"/>
+      <c r="BF2" s="60"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="60"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="60"/>
+      <c r="BL2" s="60"/>
+      <c r="BM2" s="60"/>
+      <c r="BN2" s="60"/>
+      <c r="BO2" s="60"/>
+      <c r="BP2" s="60"/>
+      <c r="BQ2" s="60"/>
+      <c r="BR2" s="60"/>
+      <c r="BS2" s="60"/>
+      <c r="BT2" s="60"/>
+      <c r="BU2" s="60"/>
+      <c r="BV2" s="60"/>
+      <c r="BW2" s="60"/>
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="60"/>
+      <c r="BZ2" s="60"/>
+      <c r="CA2" s="60"/>
+      <c r="CB2" s="60"/>
+      <c r="CC2" s="60"/>
+      <c r="CD2" s="60"/>
+      <c r="CE2" s="60"/>
+      <c r="CF2" s="60"/>
+      <c r="CG2" s="60"/>
+      <c r="CH2" s="60"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63">
         <v>2020</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63">
         <v>2021</v>
       </c>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="34">
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="59">
         <v>2022</v>
       </c>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34">
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="59"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59">
         <v>2023</v>
       </c>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
-      <c r="AP3" s="34"/>
-      <c r="AQ3" s="34"/>
-      <c r="AR3" s="34"/>
-      <c r="AS3" s="34"/>
-      <c r="AT3" s="34"/>
-      <c r="AU3" s="34"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="34"/>
-      <c r="AX3" s="34"/>
-      <c r="AY3" s="34">
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59"/>
+      <c r="AT3" s="59"/>
+      <c r="AU3" s="59"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="59"/>
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="59">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="34"/>
-      <c r="BA3" s="34"/>
-      <c r="BB3" s="34"/>
-      <c r="BC3" s="34"/>
-      <c r="BD3" s="34"/>
-      <c r="BE3" s="34"/>
-      <c r="BF3" s="34"/>
-      <c r="BG3" s="34"/>
-      <c r="BH3" s="34"/>
-      <c r="BI3" s="34"/>
-      <c r="BJ3" s="34"/>
-      <c r="BK3" s="34">
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="59"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="59"/>
+      <c r="BJ3" s="59"/>
+      <c r="BK3" s="59">
         <v>2025</v>
       </c>
-      <c r="BL3" s="34"/>
-      <c r="BM3" s="34"/>
-      <c r="BN3" s="34"/>
-      <c r="BO3" s="34"/>
-      <c r="BP3" s="34"/>
-      <c r="BQ3" s="34"/>
-      <c r="BR3" s="34"/>
-      <c r="BS3" s="34"/>
-      <c r="BT3" s="34"/>
-      <c r="BU3" s="34"/>
-      <c r="BV3" s="34"/>
-      <c r="BW3" s="34">
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="59"/>
+      <c r="BO3" s="59"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="59"/>
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59">
         <v>2026</v>
       </c>
-      <c r="BX3" s="34"/>
-      <c r="BY3" s="34"/>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="34"/>
-      <c r="CB3" s="34"/>
-      <c r="CC3" s="34"/>
-      <c r="CD3" s="34"/>
-      <c r="CE3" s="34"/>
-      <c r="CF3" s="34"/>
-      <c r="CG3" s="34"/>
-      <c r="CH3" s="34"/>
+      <c r="BX3" s="59"/>
+      <c r="BY3" s="59"/>
+      <c r="BZ3" s="59"/>
+      <c r="CA3" s="59"/>
+      <c r="CB3" s="59"/>
+      <c r="CC3" s="59"/>
+      <c r="CD3" s="59"/>
+      <c r="CE3" s="59"/>
+      <c r="CF3" s="59"/>
+      <c r="CG3" s="59"/>
+      <c r="CH3" s="59"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1497,7 +1604,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="34" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1757,7 +1864,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2122,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2380,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2531,7 +2638,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2896,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3047,7 +3154,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3305,7 +3412,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3670,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3821,7 +3928,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4186,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4444,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4595,7 +4702,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4853,7 +4960,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5218,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5369,7 +5476,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5734,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5992,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="40"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6143,7 +6250,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6401,7 +6508,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6659,7 +6766,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -6917,7 +7024,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7282,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,7 +7540,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7798,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -7949,7 +8056,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8207,7 +8314,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8465,7 +8572,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8830,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -8981,7 +9088,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9239,7 +9346,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="40"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9582,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="41"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9733,7 +9840,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -9993,7 +10100,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="49"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10251,7 +10358,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="49"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10509,7 +10616,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="49"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10874,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="49"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11025,7 +11132,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="49"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11283,7 +11390,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="49"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11541,7 +11648,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="49"/>
+      <c r="A44" s="44"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11799,7 +11906,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="49"/>
+      <c r="A45" s="44"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12057,7 +12164,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
+      <c r="A46" s="45"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12315,7 +12422,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="42" t="s">
+      <c r="A47" s="37" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12575,7 +12682,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="43"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12833,7 +12940,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="43"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13091,7 +13198,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="43"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13349,7 +13456,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="43"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13607,7 +13714,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="44"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13865,7 +13972,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="40" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14125,7 +14232,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14490,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="47"/>
+      <c r="A55" s="42"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14477,7 +14584,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="51" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14737,7 +14844,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="57"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -14985,7 +15092,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="57"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15243,7 +15350,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="57"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15501,7 +15608,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="57"/>
+      <c r="A60" s="52"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15759,7 +15866,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="58"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16017,7 +16124,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="59" t="s">
+      <c r="A62" s="54" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16277,7 +16384,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="60"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16535,7 +16642,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="53" t="s">
+      <c r="A64" s="48" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16795,7 +16902,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="54"/>
+      <c r="A65" s="49"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17053,7 +17160,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="54"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17311,7 +17418,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="55"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17569,7 +17676,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="56" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17829,7 +17936,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="62"/>
+      <c r="A69" s="57"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18087,7 +18194,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="63"/>
+      <c r="A70" s="58"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18865,7 +18972,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19125,7 +19232,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
+      <c r="A74" s="41"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19383,7 +19490,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
+      <c r="A75" s="41"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19641,7 +19748,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
+      <c r="A76" s="41"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -19899,7 +20006,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="47"/>
+      <c r="A77" s="42"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20157,7 +20264,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="51" t="s">
+      <c r="A78" s="46" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20417,7 +20524,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="52"/>
+      <c r="A79" s="47"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20676,6 +20783,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20686,15 +20802,6 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>
@@ -20703,4 +20810,1372 @@
   </colBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83A008A-D3FB-44D0-A8A5-D2A6B1ECE786}">
+  <dimension ref="A1:X21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.109375" customWidth="1"/>
+    <col min="23" max="23" width="9.5546875" customWidth="1"/>
+    <col min="24" max="24" width="29.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="65">
+        <v>45658</v>
+      </c>
+      <c r="D1" s="65">
+        <v>45689</v>
+      </c>
+      <c r="E1" s="65">
+        <v>45717</v>
+      </c>
+      <c r="F1" s="65">
+        <v>45748</v>
+      </c>
+      <c r="G1" s="65">
+        <v>45778</v>
+      </c>
+      <c r="H1" s="65">
+        <v>45809</v>
+      </c>
+      <c r="I1" s="65">
+        <v>45839</v>
+      </c>
+      <c r="J1" s="65">
+        <v>45870</v>
+      </c>
+      <c r="K1" s="65">
+        <v>45901</v>
+      </c>
+      <c r="L1" s="65">
+        <v>45931</v>
+      </c>
+      <c r="M1" s="65">
+        <v>45962</v>
+      </c>
+      <c r="N1" s="65">
+        <v>45992</v>
+      </c>
+      <c r="O1" s="65">
+        <v>46023</v>
+      </c>
+      <c r="P1" s="65">
+        <v>46054</v>
+      </c>
+      <c r="Q1" s="65">
+        <v>46082</v>
+      </c>
+      <c r="R1" s="65">
+        <v>46113</v>
+      </c>
+      <c r="S1" s="65">
+        <v>46143</v>
+      </c>
+      <c r="T1" s="65">
+        <v>46174</v>
+      </c>
+      <c r="U1" s="65">
+        <v>46204</v>
+      </c>
+      <c r="V1" s="65">
+        <v>46235</v>
+      </c>
+      <c r="W1" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="X1" s="64" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1">
+        <v>110331.25</v>
+      </c>
+      <c r="D2" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>116507</v>
+      </c>
+      <c r="F2" s="1">
+        <v>102639.75</v>
+      </c>
+      <c r="G2" s="1">
+        <v>143385</v>
+      </c>
+      <c r="H2" s="1">
+        <v>145075.70000000001</v>
+      </c>
+      <c r="I2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="J2" s="1">
+        <v>189220</v>
+      </c>
+      <c r="K2" s="1">
+        <v>122665</v>
+      </c>
+      <c r="L2" s="1">
+        <v>82522</v>
+      </c>
+      <c r="M2" s="1">
+        <v>82815</v>
+      </c>
+      <c r="N2" s="1">
+        <v>38086.15</v>
+      </c>
+      <c r="O2" s="1">
+        <v>39483.699999999997</v>
+      </c>
+      <c r="P2" s="1">
+        <v>37586.400000000001</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>69435.5</v>
+      </c>
+      <c r="R2" s="1">
+        <v>70150</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1121161</v>
+      </c>
+      <c r="T2" s="1">
+        <v>70150</v>
+      </c>
+      <c r="U2" s="1">
+        <v>118455.3</v>
+      </c>
+      <c r="V2" s="1">
+        <v>118455.3</v>
+      </c>
+      <c r="W2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>3500</v>
+      </c>
+      <c r="N3" s="1">
+        <v>5077</v>
+      </c>
+      <c r="O3" s="1">
+        <v>6572</v>
+      </c>
+      <c r="P3" s="1">
+        <v>8657</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>10241</v>
+      </c>
+      <c r="R3" s="1">
+        <v>11301</v>
+      </c>
+      <c r="S3" s="1">
+        <v>12980</v>
+      </c>
+      <c r="T3" s="1">
+        <v>15024</v>
+      </c>
+      <c r="U3" s="1">
+        <v>18115</v>
+      </c>
+      <c r="V3" s="1">
+        <v>18115</v>
+      </c>
+      <c r="W3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2962</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3687</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4417.9277564102567</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5242.9277564102567</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6257.9277564102567</v>
+      </c>
+      <c r="H4" s="1">
+        <v>7157.9277564102567</v>
+      </c>
+      <c r="I4" s="1">
+        <v>7987.9277564102567</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8887.9277564102558</v>
+      </c>
+      <c r="K4" s="1">
+        <v>9667.9277564102558</v>
+      </c>
+      <c r="L4" s="1">
+        <v>10427.927756410256</v>
+      </c>
+      <c r="M4" s="1">
+        <v>11242.927756410256</v>
+      </c>
+      <c r="N4" s="1">
+        <v>11992.927756410256</v>
+      </c>
+      <c r="O4" s="1">
+        <v>12718.165855725325</v>
+      </c>
+      <c r="P4" s="1">
+        <v>13289.43957147875</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>13980.757122848612</v>
+      </c>
+      <c r="R4" s="1">
+        <v>14751.031780382858</v>
+      </c>
+      <c r="S4" s="1">
+        <v>15844.998047506146</v>
+      </c>
+      <c r="T4" s="1">
+        <v>16808.421848876009</v>
+      </c>
+      <c r="U4" s="1">
+        <v>17694.848389971899</v>
+      </c>
+      <c r="V4" s="1">
+        <v>17694.848389971899</v>
+      </c>
+      <c r="W4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8607</v>
+      </c>
+      <c r="F5" s="1">
+        <v>15080</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8414</v>
+      </c>
+      <c r="H5" s="1">
+        <v>16997</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15548</v>
+      </c>
+      <c r="J5" s="1">
+        <v>12719</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10070</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>4104</v>
+      </c>
+      <c r="N5" s="1">
+        <v>12517</v>
+      </c>
+      <c r="O5" s="1">
+        <v>19748</v>
+      </c>
+      <c r="P5" s="1">
+        <v>18721</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>16959</v>
+      </c>
+      <c r="R5" s="1">
+        <v>12989</v>
+      </c>
+      <c r="S5" s="1">
+        <v>23133</v>
+      </c>
+      <c r="T5" s="1">
+        <v>21367</v>
+      </c>
+      <c r="U5" s="1">
+        <v>27760</v>
+      </c>
+      <c r="V5" s="1">
+        <v>27760</v>
+      </c>
+      <c r="W5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="D6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="E6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="F6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="G6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="H6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="I6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="J6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="K6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="L6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="M6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="N6" s="1">
+        <v>18625</v>
+      </c>
+      <c r="O6" s="1">
+        <v>19205</v>
+      </c>
+      <c r="P6" s="1">
+        <v>23630</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>26140</v>
+      </c>
+      <c r="R6" s="1">
+        <v>29630</v>
+      </c>
+      <c r="S6" s="1">
+        <v>33000</v>
+      </c>
+      <c r="T6" s="1">
+        <v>36700</v>
+      </c>
+      <c r="U6" s="1">
+        <v>38300</v>
+      </c>
+      <c r="V6" s="1">
+        <v>38300</v>
+      </c>
+      <c r="W6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3202.25</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3812.25</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4242.25</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4822.25</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3487.25</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4067.25</v>
+      </c>
+      <c r="I7" s="1">
+        <v>4742.25</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5209.5092000000004</v>
+      </c>
+      <c r="K7" s="1">
+        <v>5621.7698666666674</v>
+      </c>
+      <c r="L7" s="1">
+        <v>6038.6761333333343</v>
+      </c>
+      <c r="M7" s="1">
+        <v>6495.1561333333339</v>
+      </c>
+      <c r="N7" s="1">
+        <v>6883.238933333334</v>
+      </c>
+      <c r="O7" s="1">
+        <v>7283.3089333333337</v>
+      </c>
+      <c r="P7" s="1">
+        <v>7713.159466666667</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>7886.1813333333339</v>
+      </c>
+      <c r="R7" s="1">
+        <v>8124.9214666666676</v>
+      </c>
+      <c r="S7" s="1">
+        <v>8342.8069333333351</v>
+      </c>
+      <c r="T7" s="1">
+        <v>8342.8069333333351</v>
+      </c>
+      <c r="U7" s="1">
+        <v>8342.8069333333351</v>
+      </c>
+      <c r="V7" s="1">
+        <v>8342.8069333333351</v>
+      </c>
+      <c r="W7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="1">
+        <v>42980</v>
+      </c>
+      <c r="D8" s="1">
+        <v>44194</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45210.085599999999</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45915.085599999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>47000.085599999999</v>
+      </c>
+      <c r="H8" s="1">
+        <v>47880.085599999999</v>
+      </c>
+      <c r="I8" s="1">
+        <v>48695.085599999999</v>
+      </c>
+      <c r="J8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="K8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="L8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="M8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="N8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="O8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="P8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="R8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="S8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="T8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="U8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="V8" s="1">
+        <v>48858.535199999998</v>
+      </c>
+      <c r="W8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1">
+        <v>27900</v>
+      </c>
+      <c r="D9" s="1">
+        <v>29230</v>
+      </c>
+      <c r="E9" s="1">
+        <v>31780</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20870</v>
+      </c>
+      <c r="G9" s="1">
+        <v>22450</v>
+      </c>
+      <c r="H9" s="1">
+        <v>24000</v>
+      </c>
+      <c r="I9" s="1">
+        <v>25280</v>
+      </c>
+      <c r="J9" s="1">
+        <v>26350</v>
+      </c>
+      <c r="K9" s="1">
+        <v>27900</v>
+      </c>
+      <c r="L9" s="1">
+        <v>29480</v>
+      </c>
+      <c r="M9" s="1">
+        <v>24500</v>
+      </c>
+      <c r="N9" s="1">
+        <v>28400</v>
+      </c>
+      <c r="O9" s="1">
+        <v>29800</v>
+      </c>
+      <c r="P9" s="1">
+        <v>31740</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>34100</v>
+      </c>
+      <c r="R9" s="1">
+        <v>36100</v>
+      </c>
+      <c r="S9" s="1">
+        <v>37600</v>
+      </c>
+      <c r="T9" s="1">
+        <v>37600</v>
+      </c>
+      <c r="U9" s="1">
+        <v>37600</v>
+      </c>
+      <c r="V9" s="1">
+        <v>37600</v>
+      </c>
+      <c r="W9" t="s">
+        <v>110</v>
+      </c>
+      <c r="X9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4000</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P10" s="1">
+        <v>4000</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="T10" s="1">
+        <v>4000</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>110</v>
+      </c>
+      <c r="X10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
+        <v>110</v>
+      </c>
+      <c r="X11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4521</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6582</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>6870</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5780</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>6541</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>3250</v>
+      </c>
+      <c r="T12" s="1">
+        <v>7150</v>
+      </c>
+      <c r="U12" s="1">
+        <v>12000</v>
+      </c>
+      <c r="V12" s="1">
+        <v>12000</v>
+      </c>
+      <c r="W12" t="s">
+        <v>110</v>
+      </c>
+      <c r="X12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" t="s">
+        <v>110</v>
+      </c>
+      <c r="X13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2670</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3548</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2546</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3546</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>4000</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>3548</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>4568</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>3350</v>
+      </c>
+      <c r="S14" s="1">
+        <v>5890</v>
+      </c>
+      <c r="T14" s="1">
+        <v>8035</v>
+      </c>
+      <c r="U14" s="1">
+        <v>10170</v>
+      </c>
+      <c r="V14" s="1">
+        <v>10170</v>
+      </c>
+      <c r="W14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="1">
+        <v>42882.997995912105</v>
+      </c>
+      <c r="D16" s="1">
+        <v>43877.877724001104</v>
+      </c>
+      <c r="E16" s="1">
+        <v>44966.2935518511</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45953.994751755024</v>
+      </c>
+      <c r="G16" s="1">
+        <v>47030.64040651275</v>
+      </c>
+      <c r="H16" s="1">
+        <v>48071.716562021749</v>
+      </c>
+      <c r="I16" s="1">
+        <v>49064.47312097175</v>
+      </c>
+      <c r="J16" s="1">
+        <v>49437.777584971751</v>
+      </c>
+      <c r="K16" s="1">
+        <v>50680.181504221749</v>
+      </c>
+      <c r="L16" s="1">
+        <v>52104.495522202495</v>
+      </c>
+      <c r="M16" s="1">
+        <v>53615.263354316296</v>
+      </c>
+      <c r="N16" s="1">
+        <v>53889.408820066295</v>
+      </c>
+      <c r="O16" s="1">
+        <v>55582.514301179777</v>
+      </c>
+      <c r="P16" s="1">
+        <v>56719.448043585275</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>57640.930864457849</v>
+      </c>
+      <c r="R16" s="1">
+        <v>58700.942305615026</v>
+      </c>
+      <c r="S16" s="1">
+        <v>59074.24676961502</v>
+      </c>
+      <c r="T16" s="1">
+        <v>60041.658871900545</v>
+      </c>
+      <c r="U16" s="1">
+        <v>60965.553006295275</v>
+      </c>
+      <c r="V16" s="1">
+        <v>62219.72</v>
+      </c>
+      <c r="W16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>5511</v>
+      </c>
+      <c r="O17" s="1">
+        <v>8442</v>
+      </c>
+      <c r="P17" s="1">
+        <v>10576</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>12555</v>
+      </c>
+      <c r="R17" s="1">
+        <v>15388</v>
+      </c>
+      <c r="S17" s="1">
+        <v>18332</v>
+      </c>
+      <c r="T17" s="1">
+        <v>22178</v>
+      </c>
+      <c r="U17" s="1">
+        <v>25780</v>
+      </c>
+      <c r="V17" s="1">
+        <v>28120</v>
+      </c>
+      <c r="W17" t="s">
+        <v>110</v>
+      </c>
+      <c r="X17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1">
+        <v>1802.67</v>
+      </c>
+      <c r="N18" s="1">
+        <v>3904</v>
+      </c>
+      <c r="O18" s="1">
+        <v>6060</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>6457</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>7493</v>
+      </c>
+      <c r="T18" s="1">
+        <v>11700</v>
+      </c>
+      <c r="U18" s="1">
+        <v>15900</v>
+      </c>
+      <c r="V18" s="1">
+        <v>15900</v>
+      </c>
+      <c r="W18" t="s">
+        <v>110</v>
+      </c>
+      <c r="X18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1">
+        <v>433.18549999999999</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>2101.3425000000002</v>
+      </c>
+      <c r="R19" s="1">
+        <v>3981.1165000000005</v>
+      </c>
+      <c r="S19" s="1">
+        <v>5917.6640000000007</v>
+      </c>
+      <c r="T19" s="1">
+        <v>7541.5165000000006</v>
+      </c>
+      <c r="U19" s="1">
+        <v>9269.3160000000007</v>
+      </c>
+      <c r="V19" s="1">
+        <v>9269.3160000000007</v>
+      </c>
+      <c r="W19" t="s">
+        <v>110</v>
+      </c>
+      <c r="X19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1">
+        <v>2009.7965000000002</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6265</v>
+      </c>
+      <c r="T20" s="1">
+        <v>8381</v>
+      </c>
+      <c r="U20" s="1">
+        <v>11860</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" t="s">
+        <v>110</v>
+      </c>
+      <c r="X20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>8040</v>
+      </c>
+      <c r="V21" s="1"/>
+      <c r="W21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="W2:W21" xr:uid="{0326A413-F596-489B-94D3-4E4E39BBB911}">
+      <formula1>"Active,Stopped,Closed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AE8BB9-A336-4EAC-B1E2-C9F37765E5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A187BD54-8756-4626-BADE-2F615E240922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly sales" sheetId="1" r:id="rId1"/>
@@ -727,6 +727,27 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -801,27 +822,6 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1149,199 +1149,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="60"/>
-      <c r="AU2" s="60"/>
-      <c r="AV2" s="60"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="60"/>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="60"/>
-      <c r="BE2" s="60"/>
-      <c r="BF2" s="60"/>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="60"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="60"/>
-      <c r="BK2" s="60"/>
-      <c r="BL2" s="60"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
-      <c r="BO2" s="60"/>
-      <c r="BP2" s="60"/>
-      <c r="BQ2" s="60"/>
-      <c r="BR2" s="60"/>
-      <c r="BS2" s="60"/>
-      <c r="BT2" s="60"/>
-      <c r="BU2" s="60"/>
-      <c r="BV2" s="60"/>
-      <c r="BW2" s="60"/>
-      <c r="BX2" s="60"/>
-      <c r="BY2" s="60"/>
-      <c r="BZ2" s="60"/>
-      <c r="CA2" s="60"/>
-      <c r="CB2" s="60"/>
-      <c r="CC2" s="60"/>
-      <c r="CD2" s="60"/>
-      <c r="CE2" s="60"/>
-      <c r="CF2" s="60"/>
-      <c r="CG2" s="60"/>
-      <c r="CH2" s="60"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="37"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="37"/>
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="37"/>
+      <c r="AQ2" s="37"/>
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="37"/>
+      <c r="AU2" s="37"/>
+      <c r="AV2" s="37"/>
+      <c r="AW2" s="37"/>
+      <c r="AX2" s="37"/>
+      <c r="AY2" s="37"/>
+      <c r="AZ2" s="37"/>
+      <c r="BA2" s="37"/>
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="37"/>
+      <c r="BE2" s="37"/>
+      <c r="BF2" s="37"/>
+      <c r="BG2" s="37"/>
+      <c r="BH2" s="37"/>
+      <c r="BI2" s="37"/>
+      <c r="BJ2" s="37"/>
+      <c r="BK2" s="37"/>
+      <c r="BL2" s="37"/>
+      <c r="BM2" s="37"/>
+      <c r="BN2" s="37"/>
+      <c r="BO2" s="37"/>
+      <c r="BP2" s="37"/>
+      <c r="BQ2" s="37"/>
+      <c r="BR2" s="37"/>
+      <c r="BS2" s="37"/>
+      <c r="BT2" s="37"/>
+      <c r="BU2" s="37"/>
+      <c r="BV2" s="37"/>
+      <c r="BW2" s="37"/>
+      <c r="BX2" s="37"/>
+      <c r="BY2" s="37"/>
+      <c r="BZ2" s="37"/>
+      <c r="CA2" s="37"/>
+      <c r="CB2" s="37"/>
+      <c r="CC2" s="37"/>
+      <c r="CD2" s="37"/>
+      <c r="CE2" s="37"/>
+      <c r="CF2" s="37"/>
+      <c r="CG2" s="37"/>
+      <c r="CH2" s="37"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40">
         <v>2020</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40">
         <v>2021</v>
       </c>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="59">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="36">
         <v>2022</v>
       </c>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59">
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36">
         <v>2023</v>
       </c>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="59">
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59">
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="36"/>
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BI3" s="36"/>
+      <c r="BJ3" s="36"/>
+      <c r="BK3" s="36">
         <v>2025</v>
       </c>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="59"/>
-      <c r="BN3" s="59"/>
-      <c r="BO3" s="59"/>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="59"/>
-      <c r="BR3" s="59"/>
-      <c r="BS3" s="59"/>
-      <c r="BT3" s="59"/>
-      <c r="BU3" s="59"/>
-      <c r="BV3" s="59"/>
-      <c r="BW3" s="59">
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="36"/>
+      <c r="BO3" s="36"/>
+      <c r="BP3" s="36"/>
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BS3" s="36"/>
+      <c r="BT3" s="36"/>
+      <c r="BU3" s="36"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36">
         <v>2026</v>
       </c>
-      <c r="BX3" s="59"/>
-      <c r="BY3" s="59"/>
-      <c r="BZ3" s="59"/>
-      <c r="CA3" s="59"/>
-      <c r="CB3" s="59"/>
-      <c r="CC3" s="59"/>
-      <c r="CD3" s="59"/>
-      <c r="CE3" s="59"/>
-      <c r="CF3" s="59"/>
-      <c r="CG3" s="59"/>
-      <c r="CH3" s="59"/>
+      <c r="BX3" s="36"/>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="36"/>
+      <c r="CA3" s="36"/>
+      <c r="CB3" s="36"/>
+      <c r="CC3" s="36"/>
+      <c r="CD3" s="36"/>
+      <c r="CE3" s="36"/>
+      <c r="CF3" s="36"/>
+      <c r="CG3" s="36"/>
+      <c r="CH3" s="36"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1604,7 +1604,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="41" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1864,7 +1864,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2122,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="42"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2638,7 +2638,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="42"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3154,7 +3154,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3670,7 +3670,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3928,7 +3928,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4186,7 +4186,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4702,7 +4702,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4960,7 +4960,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5218,7 +5218,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5476,7 +5476,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="35"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +5734,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5992,7 +5992,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6250,7 +6250,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="35"/>
+      <c r="A23" s="42"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6508,7 +6508,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35"/>
+      <c r="A24" s="42"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6766,7 +6766,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35"/>
+      <c r="A25" s="42"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -7024,7 +7024,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
+      <c r="A26" s="42"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7282,7 +7282,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="35"/>
+      <c r="A27" s="42"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="35"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="35"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -8056,7 +8056,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="35"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8314,7 +8314,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8572,7 +8572,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="35"/>
+      <c r="A32" s="42"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8830,7 +8830,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="35"/>
+      <c r="A33" s="42"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -9088,7 +9088,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="35"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9346,7 +9346,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="35"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9582,7 +9582,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9840,7 +9840,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="50" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -10081,7 +10081,7 @@
         <v>97848.767123287675</v>
       </c>
       <c r="CC37" s="18">
-        <v>93776.438356164392</v>
+        <v>89915.068493150684</v>
       </c>
       <c r="CD37" s="18">
         <v>0</v>
@@ -10100,7 +10100,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="44"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10358,7 +10358,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="44"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10616,7 +10616,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="44"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10874,7 +10874,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="44"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11132,7 +11132,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="44"/>
+      <c r="A42" s="51"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11390,7 +11390,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="44"/>
+      <c r="A43" s="51"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11648,7 +11648,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="44"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11906,7 +11906,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="44"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12164,7 +12164,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="45"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12422,7 +12422,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12682,7 +12682,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12940,7 +12940,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="45"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13198,7 +13198,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13456,7 +13456,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="45"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13714,7 +13714,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
+      <c r="A52" s="46"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13972,7 +13972,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14232,7 +14232,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="41"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14490,7 +14490,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42"/>
+      <c r="A55" s="49"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14584,7 +14584,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="51" t="s">
+      <c r="A56" s="58" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14844,7 +14844,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
+      <c r="A57" s="59"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -15092,7 +15092,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="52"/>
+      <c r="A58" s="59"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15350,7 +15350,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="52"/>
+      <c r="A59" s="59"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15608,7 +15608,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="52"/>
+      <c r="A60" s="59"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15866,7 +15866,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="53"/>
+      <c r="A61" s="60"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16124,7 +16124,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="61" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16384,7 +16384,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16642,7 +16642,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="55" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16902,7 +16902,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="49"/>
+      <c r="A65" s="56"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17160,7 +17160,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="49"/>
+      <c r="A66" s="56"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17418,7 +17418,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="50"/>
+      <c r="A67" s="57"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17676,7 +17676,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="63" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17936,7 +17936,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="57"/>
+      <c r="A69" s="64"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18194,7 +18194,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="58"/>
+      <c r="A70" s="65"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18972,7 +18972,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="47" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19232,7 +19232,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41"/>
+      <c r="A74" s="48"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19490,7 +19490,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
+      <c r="A75" s="48"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19748,7 +19748,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
+      <c r="A76" s="48"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -20006,7 +20006,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="42"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20264,7 +20264,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="53" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20524,7 +20524,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="47"/>
+      <c r="A79" s="54"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20783,15 +20783,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20802,6 +20793,15 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>
@@ -20832,76 +20832,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="65">
+      <c r="C1" s="35">
         <v>45658</v>
       </c>
-      <c r="D1" s="65">
+      <c r="D1" s="35">
         <v>45689</v>
       </c>
-      <c r="E1" s="65">
+      <c r="E1" s="35">
         <v>45717</v>
       </c>
-      <c r="F1" s="65">
+      <c r="F1" s="35">
         <v>45748</v>
       </c>
-      <c r="G1" s="65">
+      <c r="G1" s="35">
         <v>45778</v>
       </c>
-      <c r="H1" s="65">
+      <c r="H1" s="35">
         <v>45809</v>
       </c>
-      <c r="I1" s="65">
+      <c r="I1" s="35">
         <v>45839</v>
       </c>
-      <c r="J1" s="65">
+      <c r="J1" s="35">
         <v>45870</v>
       </c>
-      <c r="K1" s="65">
+      <c r="K1" s="35">
         <v>45901</v>
       </c>
-      <c r="L1" s="65">
+      <c r="L1" s="35">
         <v>45931</v>
       </c>
-      <c r="M1" s="65">
+      <c r="M1" s="35">
         <v>45962</v>
       </c>
-      <c r="N1" s="65">
+      <c r="N1" s="35">
         <v>45992</v>
       </c>
-      <c r="O1" s="65">
+      <c r="O1" s="35">
         <v>46023</v>
       </c>
-      <c r="P1" s="65">
+      <c r="P1" s="35">
         <v>46054</v>
       </c>
-      <c r="Q1" s="65">
+      <c r="Q1" s="35">
         <v>46082</v>
       </c>
-      <c r="R1" s="65">
+      <c r="R1" s="35">
         <v>46113</v>
       </c>
-      <c r="S1" s="65">
+      <c r="S1" s="35">
         <v>46143</v>
       </c>
-      <c r="T1" s="65">
+      <c r="T1" s="35">
         <v>46174</v>
       </c>
-      <c r="U1" s="65">
+      <c r="U1" s="35">
         <v>46204</v>
       </c>
-      <c r="V1" s="65">
+      <c r="V1" s="35">
         <v>46235</v>
       </c>
-      <c r="W1" s="64" t="s">
+      <c r="W1" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="X1" s="64" t="s">
+      <c r="X1" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
         <v>27760</v>
       </c>
       <c r="V5" s="1">
-        <v>27760</v>
+        <v>27623</v>
       </c>
       <c r="W5" t="s">
         <v>110</v>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7B1DF2-E7E9-4F13-934A-214250A29F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D37699F-7E1B-4AB9-A2AC-DD8132B0CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B1B892D3-C8DC-437F-A938-CC0527360C32}"/>
   </bookViews>
@@ -733,6 +733,21 @@
     <xf numFmtId="165" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,21 +821,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1149,199 +1149,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="62"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="62"/>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="62"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="62"/>
-      <c r="AI2" s="62"/>
-      <c r="AJ2" s="62"/>
-      <c r="AK2" s="62"/>
-      <c r="AL2" s="62"/>
-      <c r="AM2" s="62"/>
-      <c r="AN2" s="62"/>
-      <c r="AO2" s="62"/>
-      <c r="AP2" s="62"/>
-      <c r="AQ2" s="62"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="62"/>
-      <c r="AT2" s="62"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="62"/>
-      <c r="AW2" s="62"/>
-      <c r="AX2" s="62"/>
-      <c r="AY2" s="62"/>
-      <c r="AZ2" s="62"/>
-      <c r="BA2" s="62"/>
-      <c r="BB2" s="62"/>
-      <c r="BC2" s="62"/>
-      <c r="BD2" s="62"/>
-      <c r="BE2" s="62"/>
-      <c r="BF2" s="62"/>
-      <c r="BG2" s="62"/>
-      <c r="BH2" s="62"/>
-      <c r="BI2" s="62"/>
-      <c r="BJ2" s="62"/>
-      <c r="BK2" s="62"/>
-      <c r="BL2" s="62"/>
-      <c r="BM2" s="62"/>
-      <c r="BN2" s="62"/>
-      <c r="BO2" s="62"/>
-      <c r="BP2" s="62"/>
-      <c r="BQ2" s="62"/>
-      <c r="BR2" s="62"/>
-      <c r="BS2" s="62"/>
-      <c r="BT2" s="62"/>
-      <c r="BU2" s="62"/>
-      <c r="BV2" s="62"/>
-      <c r="BW2" s="62"/>
-      <c r="BX2" s="62"/>
-      <c r="BY2" s="62"/>
-      <c r="BZ2" s="62"/>
-      <c r="CA2" s="62"/>
-      <c r="CB2" s="62"/>
-      <c r="CC2" s="62"/>
-      <c r="CD2" s="62"/>
-      <c r="CE2" s="62"/>
-      <c r="CF2" s="62"/>
-      <c r="CG2" s="62"/>
-      <c r="CH2" s="62"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="37"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="37"/>
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="37"/>
+      <c r="AQ2" s="37"/>
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="37"/>
+      <c r="AU2" s="37"/>
+      <c r="AV2" s="37"/>
+      <c r="AW2" s="37"/>
+      <c r="AX2" s="37"/>
+      <c r="AY2" s="37"/>
+      <c r="AZ2" s="37"/>
+      <c r="BA2" s="37"/>
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="37"/>
+      <c r="BE2" s="37"/>
+      <c r="BF2" s="37"/>
+      <c r="BG2" s="37"/>
+      <c r="BH2" s="37"/>
+      <c r="BI2" s="37"/>
+      <c r="BJ2" s="37"/>
+      <c r="BK2" s="37"/>
+      <c r="BL2" s="37"/>
+      <c r="BM2" s="37"/>
+      <c r="BN2" s="37"/>
+      <c r="BO2" s="37"/>
+      <c r="BP2" s="37"/>
+      <c r="BQ2" s="37"/>
+      <c r="BR2" s="37"/>
+      <c r="BS2" s="37"/>
+      <c r="BT2" s="37"/>
+      <c r="BU2" s="37"/>
+      <c r="BV2" s="37"/>
+      <c r="BW2" s="37"/>
+      <c r="BX2" s="37"/>
+      <c r="BY2" s="37"/>
+      <c r="BZ2" s="37"/>
+      <c r="CA2" s="37"/>
+      <c r="CB2" s="37"/>
+      <c r="CC2" s="37"/>
+      <c r="CD2" s="37"/>
+      <c r="CE2" s="37"/>
+      <c r="CF2" s="37"/>
+      <c r="CG2" s="37"/>
+      <c r="CH2" s="37"/>
     </row>
     <row r="3" spans="1:86" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40">
         <v>2020</v>
       </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40">
         <v>2021</v>
       </c>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="61">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="36">
         <v>2022</v>
       </c>
-      <c r="AB3" s="61"/>
-      <c r="AC3" s="61"/>
-      <c r="AD3" s="61"/>
-      <c r="AE3" s="61"/>
-      <c r="AF3" s="61"/>
-      <c r="AG3" s="61"/>
-      <c r="AH3" s="61"/>
-      <c r="AI3" s="61"/>
-      <c r="AJ3" s="61"/>
-      <c r="AK3" s="61"/>
-      <c r="AL3" s="61"/>
-      <c r="AM3" s="61">
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36">
         <v>2023</v>
       </c>
-      <c r="AN3" s="61"/>
-      <c r="AO3" s="61"/>
-      <c r="AP3" s="61"/>
-      <c r="AQ3" s="61"/>
-      <c r="AR3" s="61"/>
-      <c r="AS3" s="61"/>
-      <c r="AT3" s="61"/>
-      <c r="AU3" s="61"/>
-      <c r="AV3" s="61"/>
-      <c r="AW3" s="61"/>
-      <c r="AX3" s="61"/>
-      <c r="AY3" s="61">
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="61"/>
-      <c r="BA3" s="61"/>
-      <c r="BB3" s="61"/>
-      <c r="BC3" s="61"/>
-      <c r="BD3" s="61"/>
-      <c r="BE3" s="61"/>
-      <c r="BF3" s="61"/>
-      <c r="BG3" s="61"/>
-      <c r="BH3" s="61"/>
-      <c r="BI3" s="61"/>
-      <c r="BJ3" s="61"/>
-      <c r="BK3" s="61">
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="36"/>
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BI3" s="36"/>
+      <c r="BJ3" s="36"/>
+      <c r="BK3" s="36">
         <v>2025</v>
       </c>
-      <c r="BL3" s="61"/>
-      <c r="BM3" s="61"/>
-      <c r="BN3" s="61"/>
-      <c r="BO3" s="61"/>
-      <c r="BP3" s="61"/>
-      <c r="BQ3" s="61"/>
-      <c r="BR3" s="61"/>
-      <c r="BS3" s="61"/>
-      <c r="BT3" s="61"/>
-      <c r="BU3" s="61"/>
-      <c r="BV3" s="61"/>
-      <c r="BW3" s="61">
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="36"/>
+      <c r="BO3" s="36"/>
+      <c r="BP3" s="36"/>
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BS3" s="36"/>
+      <c r="BT3" s="36"/>
+      <c r="BU3" s="36"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36">
         <v>2026</v>
       </c>
-      <c r="BX3" s="61"/>
-      <c r="BY3" s="61"/>
-      <c r="BZ3" s="61"/>
-      <c r="CA3" s="61"/>
-      <c r="CB3" s="61"/>
-      <c r="CC3" s="61"/>
-      <c r="CD3" s="61"/>
-      <c r="CE3" s="61"/>
-      <c r="CF3" s="61"/>
-      <c r="CG3" s="61"/>
-      <c r="CH3" s="61"/>
+      <c r="BX3" s="36"/>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="36"/>
+      <c r="CA3" s="36"/>
+      <c r="CB3" s="36"/>
+      <c r="CC3" s="36"/>
+      <c r="CD3" s="36"/>
+      <c r="CE3" s="36"/>
+      <c r="CF3" s="36"/>
+      <c r="CG3" s="36"/>
+      <c r="CH3" s="36"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1604,7 +1604,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="41" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1864,7 +1864,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2122,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="42"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -2638,7 +2638,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+      <c r="A9" s="42"/>
       <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3154,7 +3154,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -3670,7 +3670,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -3928,7 +3928,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4186,7 +4186,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
@@ -4702,7 +4702,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
@@ -4960,7 +4960,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
@@ -5218,7 +5218,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5476,7 +5476,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +5734,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -5992,7 +5992,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="8" t="s">
         <v>21</v>
       </c>
@@ -6250,7 +6250,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="42"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
       </c>
@@ -6508,7 +6508,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="42"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
       </c>
@@ -6766,7 +6766,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="42"/>
       <c r="B25" s="8" t="s">
         <v>24</v>
       </c>
@@ -7024,7 +7024,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="42"/>
       <c r="B26" s="8" t="s">
         <v>25</v>
       </c>
@@ -7282,7 +7282,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="42"/>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="8" t="s">
         <v>28</v>
       </c>
@@ -8056,7 +8056,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
@@ -8314,7 +8314,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="8" t="s">
         <v>30</v>
       </c>
@@ -8572,7 +8572,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="42"/>
       <c r="B32" s="8" t="s">
         <v>31</v>
       </c>
@@ -8830,7 +8830,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="42"/>
       <c r="B33" s="8" t="s">
         <v>32</v>
       </c>
@@ -9088,7 +9088,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="8" t="s">
         <v>33</v>
       </c>
@@ -9346,7 +9346,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="8" t="s">
         <v>34</v>
       </c>
@@ -9582,7 +9582,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="8" t="s">
         <v>35</v>
       </c>
@@ -9840,7 +9840,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="50" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -10100,7 +10100,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -10358,7 +10358,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="9" t="s">
         <v>39</v>
       </c>
@@ -10616,7 +10616,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="9" t="s">
         <v>40</v>
       </c>
@@ -10874,7 +10874,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="9" t="s">
         <v>41</v>
       </c>
@@ -11132,7 +11132,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
+      <c r="A42" s="51"/>
       <c r="B42" s="9" t="s">
         <v>42</v>
       </c>
@@ -11390,7 +11390,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
+      <c r="A43" s="51"/>
       <c r="B43" s="9" t="s">
         <v>43</v>
       </c>
@@ -11648,7 +11648,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="9" t="s">
         <v>87</v>
       </c>
@@ -11906,7 +11906,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
@@ -12164,7 +12164,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="47"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="9" t="s">
         <v>92</v>
       </c>
@@ -12422,7 +12422,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39" t="s">
+      <c r="A47" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12682,7 +12682,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="10" t="s">
         <v>46</v>
       </c>
@@ -12940,7 +12940,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+      <c r="A49" s="45"/>
       <c r="B49" s="10" t="s">
         <v>47</v>
       </c>
@@ -13198,7 +13198,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="40"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="10" t="s">
         <v>48</v>
       </c>
@@ -13456,7 +13456,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="45"/>
       <c r="B51" s="10" t="s">
         <v>49</v>
       </c>
@@ -13714,7 +13714,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="41"/>
+      <c r="A52" s="46"/>
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -13972,7 +13972,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14232,7 +14232,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="43"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
@@ -14490,7 +14490,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="44"/>
+      <c r="A55" s="49"/>
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -14586,7 +14586,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="53" t="s">
+      <c r="A56" s="58" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14846,7 +14846,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="54"/>
+      <c r="A57" s="59"/>
       <c r="B57" s="12" t="s">
         <v>56</v>
       </c>
@@ -15094,7 +15094,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="54"/>
+      <c r="A58" s="59"/>
       <c r="B58" s="12" t="s">
         <v>57</v>
       </c>
@@ -15352,7 +15352,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="54"/>
+      <c r="A59" s="59"/>
       <c r="B59" s="12" t="s">
         <v>58</v>
       </c>
@@ -15610,7 +15610,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="54"/>
+      <c r="A60" s="59"/>
       <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
@@ -15868,7 +15868,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="55"/>
+      <c r="A61" s="60"/>
       <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
@@ -16126,7 +16126,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="61" t="s">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16386,7 +16386,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="57"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="13" t="s">
         <v>85</v>
       </c>
@@ -16644,7 +16644,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="50" t="s">
+      <c r="A64" s="55" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16888,7 +16888,7 @@
         <v>95519.230769230766</v>
       </c>
       <c r="CD64" s="23">
-        <v>71821.084615384621</v>
+        <v>99213.846153846156</v>
       </c>
       <c r="CE64" s="23">
         <v>0</v>
@@ -16904,7 +16904,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="51"/>
+      <c r="A65" s="56"/>
       <c r="B65" s="14" t="s">
         <v>65</v>
       </c>
@@ -17146,7 +17146,7 @@
         <v>95461.538461538454</v>
       </c>
       <c r="CD65" s="23">
-        <v>84073.992307692301</v>
+        <v>108016.92307692308</v>
       </c>
       <c r="CE65" s="23">
         <v>0</v>
@@ -17162,7 +17162,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="51"/>
+      <c r="A66" s="56"/>
       <c r="B66" s="14" t="s">
         <v>66</v>
       </c>
@@ -17420,7 +17420,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="57"/>
       <c r="B67" s="14" t="s">
         <v>84</v>
       </c>
@@ -17662,7 +17662,7 @@
         <v>55020.869230769233</v>
       </c>
       <c r="CD67" s="23">
-        <v>35205.461538461539</v>
+        <v>48487.769230769227</v>
       </c>
       <c r="CE67" s="23">
         <v>0</v>
@@ -17678,7 +17678,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="58" t="s">
+      <c r="A68" s="63" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17938,7 +17938,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="59"/>
+      <c r="A69" s="64"/>
       <c r="B69" s="15" t="s">
         <v>69</v>
       </c>
@@ -18196,7 +18196,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
+      <c r="A70" s="65"/>
       <c r="B70" s="15" t="s">
         <v>70</v>
       </c>
@@ -18974,7 +18974,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="42" t="s">
+      <c r="A73" s="47" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19234,7 +19234,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="43"/>
+      <c r="A74" s="48"/>
       <c r="B74" s="11" t="s">
         <v>77</v>
       </c>
@@ -19492,7 +19492,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="43"/>
+      <c r="A75" s="48"/>
       <c r="B75" s="11" t="s">
         <v>78</v>
       </c>
@@ -19750,7 +19750,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="43"/>
+      <c r="A76" s="48"/>
       <c r="B76" s="11" t="s">
         <v>79</v>
       </c>
@@ -20008,7 +20008,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="44"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
@@ -20266,7 +20266,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="48" t="s">
+      <c r="A78" s="53" t="s">
         <v>81</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20526,7 +20526,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
+      <c r="A79" s="54"/>
       <c r="B79" s="5" t="s">
         <v>83</v>
       </c>
@@ -20785,15 +20785,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A5:A36"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -20804,6 +20795,15 @@
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A68:A70"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>

--- a/sales_data.xlsx.xlsx
+++ b/sales_data.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop 2025+2026\2025\خطط تطوير\AI\final\تحليل شهري\Claude + GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777189B0-F9B2-4F71-8029-408A65B8664B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76448F74-22A7-4B2A-9533-810DABC9AE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly sales" sheetId="1" r:id="rId1"/>
@@ -713,32 +713,23 @@
     <xf numFmtId="165" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -747,14 +738,23 @@
     <xf numFmtId="44" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1087,199 +1087,199 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="52"/>
-      <c r="AM2" s="52"/>
-      <c r="AN2" s="52"/>
-      <c r="AO2" s="52"/>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="52"/>
-      <c r="BA2" s="52"/>
-      <c r="BB2" s="52"/>
-      <c r="BC2" s="52"/>
-      <c r="BD2" s="52"/>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="52"/>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="52"/>
-      <c r="BO2" s="52"/>
-      <c r="BP2" s="52"/>
-      <c r="BQ2" s="52"/>
-      <c r="BR2" s="52"/>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="52"/>
-      <c r="BU2" s="52"/>
-      <c r="BV2" s="52"/>
-      <c r="BW2" s="52"/>
-      <c r="BX2" s="52"/>
-      <c r="BY2" s="52"/>
-      <c r="BZ2" s="52"/>
-      <c r="CA2" s="52"/>
-      <c r="CB2" s="52"/>
-      <c r="CC2" s="52"/>
-      <c r="CD2" s="52"/>
-      <c r="CE2" s="52"/>
-      <c r="CF2" s="52"/>
-      <c r="CG2" s="52"/>
-      <c r="CH2" s="52"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="37"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="37"/>
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="37"/>
+      <c r="AQ2" s="37"/>
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="37"/>
+      <c r="AU2" s="37"/>
+      <c r="AV2" s="37"/>
+      <c r="AW2" s="37"/>
+      <c r="AX2" s="37"/>
+      <c r="AY2" s="37"/>
+      <c r="AZ2" s="37"/>
+      <c r="BA2" s="37"/>
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="37"/>
+      <c r="BE2" s="37"/>
+      <c r="BF2" s="37"/>
+      <c r="BG2" s="37"/>
+      <c r="BH2" s="37"/>
+      <c r="BI2" s="37"/>
+      <c r="BJ2" s="37"/>
+      <c r="BK2" s="37"/>
+      <c r="BL2" s="37"/>
+      <c r="BM2" s="37"/>
+      <c r="BN2" s="37"/>
+      <c r="BO2" s="37"/>
+      <c r="BP2" s="37"/>
+      <c r="BQ2" s="37"/>
+      <c r="BR2" s="37"/>
+      <c r="BS2" s="37"/>
+      <c r="BT2" s="37"/>
+      <c r="BU2" s="37"/>
+      <c r="BV2" s="37"/>
+      <c r="BW2" s="37"/>
+      <c r="BX2" s="37"/>
+      <c r="BY2" s="37"/>
+      <c r="BZ2" s="37"/>
+      <c r="CA2" s="37"/>
+      <c r="CB2" s="37"/>
+      <c r="CC2" s="37"/>
+      <c r="CD2" s="37"/>
+      <c r="CE2" s="37"/>
+      <c r="CF2" s="37"/>
+      <c r="CG2" s="37"/>
+      <c r="CH2" s="37"/>
     </row>
     <row r="3" spans="1:86" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="47">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40">
         <v>2020</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="47">
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="40">
         <v>2021</v>
       </c>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="45">
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="38">
         <v>2022</v>
       </c>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="42"/>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="45">
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="38">
         <v>2023</v>
       </c>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="42"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="42"/>
-      <c r="AS3" s="42"/>
-      <c r="AT3" s="42"/>
-      <c r="AU3" s="42"/>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="45">
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="38">
         <v>2024</v>
       </c>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
-      <c r="BB3" s="42"/>
-      <c r="BC3" s="42"/>
-      <c r="BD3" s="42"/>
-      <c r="BE3" s="42"/>
-      <c r="BF3" s="42"/>
-      <c r="BG3" s="42"/>
-      <c r="BH3" s="42"/>
-      <c r="BI3" s="42"/>
-      <c r="BJ3" s="42"/>
-      <c r="BK3" s="45">
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="38">
         <v>2025</v>
       </c>
-      <c r="BL3" s="42"/>
-      <c r="BM3" s="42"/>
-      <c r="BN3" s="42"/>
-      <c r="BO3" s="42"/>
-      <c r="BP3" s="42"/>
-      <c r="BQ3" s="42"/>
-      <c r="BR3" s="42"/>
-      <c r="BS3" s="42"/>
-      <c r="BT3" s="42"/>
-      <c r="BU3" s="42"/>
-      <c r="BV3" s="42"/>
-      <c r="BW3" s="45">
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="38">
         <v>2026</v>
       </c>
-      <c r="BX3" s="42"/>
-      <c r="BY3" s="42"/>
-      <c r="BZ3" s="42"/>
-      <c r="CA3" s="42"/>
-      <c r="CB3" s="42"/>
-      <c r="CC3" s="42"/>
-      <c r="CD3" s="42"/>
-      <c r="CE3" s="42"/>
-      <c r="CF3" s="42"/>
-      <c r="CG3" s="42"/>
-      <c r="CH3" s="42"/>
+      <c r="BX3" s="39"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
     </row>
     <row r="4" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1542,7 +1542,7 @@
       </c>
     </row>
     <row r="5" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="41" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1802,7 +1802,7 @@
       </c>
     </row>
     <row r="6" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
@@ -2060,7 +2060,7 @@
       </c>
     </row>
     <row r="7" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
@@ -2318,7 +2318,7 @@
       </c>
     </row>
     <row r="8" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+      <c r="A8" s="42"/>
       <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2576,7 @@
       </c>
     </row>
     <row r="9" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
+      <c r="A9" s="42"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
     </row>
     <row r="10" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="39"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -3092,7 +3092,7 @@
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
@@ -3350,7 +3350,7 @@
       </c>
     </row>
     <row r="12" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
@@ -3608,7 +3608,7 @@
       </c>
     </row>
     <row r="13" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
     </row>
     <row r="14" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
@@ -4124,7 +4124,7 @@
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="16" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
@@ -4640,7 +4640,7 @@
       </c>
     </row>
     <row r="17" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
@@ -4898,7 +4898,7 @@
       </c>
     </row>
     <row r="18" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
     </row>
     <row r="19" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="8" t="s">
         <v>22</v>
       </c>
@@ -5414,7 +5414,7 @@
       </c>
     </row>
     <row r="20" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
@@ -5672,7 +5672,7 @@
       </c>
     </row>
     <row r="21" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
@@ -5930,7 +5930,7 @@
       </c>
     </row>
     <row r="22" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="8" t="s">
         <v>25</v>
       </c>
@@ -6188,7 +6188,7 @@
       </c>
     </row>
     <row r="23" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="42"/>
       <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
@@ -6446,7 +6446,7 @@
       </c>
     </row>
     <row r="24" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+      <c r="A24" s="42"/>
       <c r="B24" s="8" t="s">
         <v>27</v>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
     </row>
     <row r="25" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="42"/>
       <c r="B25" s="8" t="s">
         <v>28</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
     </row>
     <row r="26" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="42"/>
       <c r="B26" s="8" t="s">
         <v>29</v>
       </c>
@@ -7220,7 +7220,7 @@
       </c>
     </row>
     <row r="27" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+      <c r="A27" s="42"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
       </c>
@@ -7478,7 +7478,7 @@
       </c>
     </row>
     <row r="28" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="39"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="8" t="s">
         <v>31</v>
       </c>
@@ -7736,7 +7736,7 @@
       </c>
     </row>
     <row r="29" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="8" t="s">
         <v>32</v>
       </c>
@@ -7994,7 +7994,7 @@
       </c>
     </row>
     <row r="30" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="8" t="s">
         <v>33</v>
       </c>
@@ -8252,7 +8252,7 @@
       </c>
     </row>
     <row r="31" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="8" t="s">
         <v>34</v>
       </c>
@@ -8510,7 +8510,7 @@
       </c>
     </row>
     <row r="32" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+      <c r="A32" s="42"/>
       <c r="B32" s="8" t="s">
         <v>35</v>
       </c>
@@ -8768,7 +8768,7 @@
       </c>
     </row>
     <row r="33" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+      <c r="A33" s="42"/>
       <c r="B33" s="8" t="s">
         <v>36</v>
       </c>
@@ -9026,7 +9026,7 @@
       </c>
     </row>
     <row r="34" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="39"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="8" t="s">
         <v>37</v>
       </c>
@@ -9284,7 +9284,7 @@
       </c>
     </row>
     <row r="35" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="8" t="s">
         <v>38</v>
       </c>
@@ -9520,7 +9520,7 @@
       </c>
     </row>
     <row r="36" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="40"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="8" t="s">
         <v>39</v>
       </c>
@@ -9778,7 +9778,7 @@
       </c>
     </row>
     <row r="37" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="45" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -10038,7 +10038,7 @@
       </c>
     </row>
     <row r="38" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+      <c r="A38" s="42"/>
       <c r="B38" s="9" t="s">
         <v>42</v>
       </c>
@@ -10296,7 +10296,7 @@
       </c>
     </row>
     <row r="39" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
+      <c r="A39" s="42"/>
       <c r="B39" s="9" t="s">
         <v>43</v>
       </c>
@@ -10554,7 +10554,7 @@
       </c>
     </row>
     <row r="40" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="39"/>
+      <c r="A40" s="42"/>
       <c r="B40" s="9" t="s">
         <v>44</v>
       </c>
@@ -10812,7 +10812,7 @@
       </c>
     </row>
     <row r="41" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+      <c r="A41" s="42"/>
       <c r="B41" s="9" t="s">
         <v>45</v>
       </c>
@@ -11070,7 +11070,7 @@
       </c>
     </row>
     <row r="42" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+      <c r="A42" s="42"/>
       <c r="B42" s="9" t="s">
         <v>46</v>
       </c>
@@ -11328,7 +11328,7 @@
       </c>
     </row>
     <row r="43" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+      <c r="A43" s="42"/>
       <c r="B43" s="9" t="s">
         <v>47</v>
       </c>
@@ -11586,7 +11586,7 @@
       </c>
     </row>
     <row r="44" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+      <c r="A44" s="42"/>
       <c r="B44" s="9" t="s">
         <v>48</v>
       </c>
@@ -11844,7 +11844,7 @@
       </c>
     </row>
     <row r="45" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
+      <c r="A45" s="42"/>
       <c r="B45" s="9" t="s">
         <v>49</v>
       </c>
@@ -12102,7 +12102,7 @@
       </c>
     </row>
     <row r="46" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="40"/>
+      <c r="A46" s="43"/>
       <c r="B46" s="9" t="s">
         <v>50</v>
       </c>
@@ -12360,7 +12360,7 @@
       </c>
     </row>
     <row r="47" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="46" t="s">
         <v>51</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -12620,7 +12620,7 @@
       </c>
     </row>
     <row r="48" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="10" t="s">
         <v>53</v>
       </c>
@@ -12878,7 +12878,7 @@
       </c>
     </row>
     <row r="49" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="42"/>
       <c r="B49" s="10" t="s">
         <v>54</v>
       </c>
@@ -13136,7 +13136,7 @@
       </c>
     </row>
     <row r="50" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="42"/>
       <c r="B50" s="10" t="s">
         <v>55</v>
       </c>
@@ -13394,7 +13394,7 @@
       </c>
     </row>
     <row r="51" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="42"/>
       <c r="B51" s="10" t="s">
         <v>56</v>
       </c>
@@ -13652,7 +13652,7 @@
       </c>
     </row>
     <row r="52" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="40"/>
+      <c r="A52" s="43"/>
       <c r="B52" s="10" t="s">
         <v>57</v>
       </c>
@@ -13910,7 +13910,7 @@
       </c>
     </row>
     <row r="53" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="52" t="s">
         <v>58</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -14170,7 +14170,7 @@
       </c>
     </row>
     <row r="54" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="39"/>
+      <c r="A54" s="42"/>
       <c r="B54" s="11" t="s">
         <v>60</v>
       </c>
@@ -14428,7 +14428,7 @@
       </c>
     </row>
     <row r="55" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
+      <c r="A55" s="43"/>
       <c r="B55" s="11" t="s">
         <v>61</v>
       </c>
@@ -14524,7 +14524,7 @@
       <c r="CH55" s="20"/>
     </row>
     <row r="56" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="44" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -14784,7 +14784,7 @@
       </c>
     </row>
     <row r="57" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="39"/>
+      <c r="A57" s="42"/>
       <c r="B57" s="12" t="s">
         <v>64</v>
       </c>
@@ -15032,7 +15032,7 @@
       </c>
     </row>
     <row r="58" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="39"/>
+      <c r="A58" s="42"/>
       <c r="B58" s="12" t="s">
         <v>65</v>
       </c>
@@ -15290,7 +15290,7 @@
       </c>
     </row>
     <row r="59" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="39"/>
+      <c r="A59" s="42"/>
       <c r="B59" s="12" t="s">
         <v>66</v>
       </c>
@@ -15548,7 +15548,7 @@
       </c>
     </row>
     <row r="60" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="39"/>
+      <c r="A60" s="42"/>
       <c r="B60" s="12" t="s">
         <v>67</v>
       </c>
@@ -15806,7 +15806,7 @@
       </c>
     </row>
     <row r="61" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="40"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="12" t="s">
         <v>68</v>
       </c>
@@ -16064,7 +16064,7 @@
       </c>
     </row>
     <row r="62" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="50" t="s">
+      <c r="A62" s="53" t="s">
         <v>69</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -16324,7 +16324,7 @@
       </c>
     </row>
     <row r="63" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="40"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="13" t="s">
         <v>71</v>
       </c>
@@ -16582,7 +16582,7 @@
       </c>
     </row>
     <row r="64" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="49" t="s">
         <v>72</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -16842,7 +16842,7 @@
       </c>
     </row>
     <row r="65" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="39"/>
+      <c r="A65" s="42"/>
       <c r="B65" s="14" t="s">
         <v>74</v>
       </c>
@@ -17100,7 +17100,7 @@
       </c>
     </row>
     <row r="66" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="39"/>
+      <c r="A66" s="42"/>
       <c r="B66" s="14" t="s">
         <v>75</v>
       </c>
@@ -17358,7 +17358,7 @@
       </c>
     </row>
     <row r="67" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="40"/>
+      <c r="A67" s="43"/>
       <c r="B67" s="14" t="s">
         <v>76</v>
       </c>
@@ -17616,7 +17616,7 @@
       </c>
     </row>
     <row r="68" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="51" t="s">
         <v>77</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -17876,7 +17876,7 @@
       </c>
     </row>
     <row r="69" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="39"/>
+      <c r="A69" s="42"/>
       <c r="B69" s="15" t="s">
         <v>79</v>
       </c>
@@ -18134,7 +18134,7 @@
       </c>
     </row>
     <row r="70" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="40"/>
+      <c r="A70" s="43"/>
       <c r="B70" s="15" t="s">
         <v>80</v>
       </c>
@@ -18912,7 +18912,7 @@
       </c>
     </row>
     <row r="73" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="44" t="s">
+      <c r="A73" s="52" t="s">
         <v>85</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -19172,7 +19172,7 @@
       </c>
     </row>
     <row r="74" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="39"/>
+      <c r="A74" s="42"/>
       <c r="B74" s="11" t="s">
         <v>87</v>
       </c>
@@ -19430,7 +19430,7 @@
       </c>
     </row>
     <row r="75" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="39"/>
+      <c r="A75" s="42"/>
       <c r="B75" s="11" t="s">
         <v>88</v>
       </c>
@@ -19688,7 +19688,7 @@
       </c>
     </row>
     <row r="76" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="39"/>
+      <c r="A76" s="42"/>
       <c r="B76" s="11" t="s">
         <v>89</v>
       </c>
@@ -19946,7 +19946,7 @@
       </c>
     </row>
     <row r="77" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="40"/>
+      <c r="A77" s="43"/>
       <c r="B77" s="11" t="s">
         <v>90</v>
       </c>
@@ -20204,7 +20204,7 @@
       </c>
     </row>
     <row r="78" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="47" t="s">
         <v>91</v>
       </c>
       <c r="B78" s="5" t="s">
@@ -20464,7 +20464,7 @@
       </c>
     </row>
     <row r="79" spans="1:86" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
+      <c r="A79" s="48"/>
       <c r="B79" s="5" t="s">
         <v>93</v>
       </c>
@@ -20723,14 +20723,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C2:CH2"/>
-    <mergeCell ref="AY3:BJ3"/>
-    <mergeCell ref="O3:Z3"/>
-    <mergeCell ref="A5:A36"/>
-    <mergeCell ref="BK3:BV3"/>
-    <mergeCell ref="BW3:CH3"/>
-    <mergeCell ref="AA3:AL3"/>
-    <mergeCell ref="AM3:AX3"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="A37:A46"/>
@@ -20742,6 +20734,14 @@
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A73:A77"/>
     <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C2:CH2"/>
+    <mergeCell ref="AY3:BJ3"/>
+    <mergeCell ref="O3:Z3"/>
+    <mergeCell ref="A5:A36"/>
+    <mergeCell ref="BK3:BV3"/>
+    <mergeCell ref="BW3:CH3"/>
+    <mergeCell ref="AA3:AL3"/>
+    <mergeCell ref="AM3:AX3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>
@@ -21700,7 +21700,9 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
+      <c r="W13" s="1">
+        <v>21525</v>
+      </c>
       <c r="X13" t="s">
         <v>98</v>
       </c>
